--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Yoshlik Yu Distribution\Web-service-catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64DEB12-28BB-4BF3-B43F-A8810AFD01D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86D75D9-C2B7-4E8F-95B7-42BB69A5220F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13667" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -387,7 +387,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2852" uniqueCount="1610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2997" uniqueCount="1750">
   <si>
     <t>КАТАЛОГ ПРОДУКЦИИ — RU + UZ</t>
   </si>
@@ -5217,6 +5217,426 @@
   </si>
   <si>
     <t>Magniy malat — olma kislotasining magniy tuzi bo‘lib, gipomagniemiya bilan bog‘liq mushak kramplarini yengillashtiradi, charchoqni kamaytiradi va organizmdagi alyuminiy intoksikatsiyasini bartaraf etishga yordam beradi. Energiya bilan bog‘liq buzilishlarni kamaytirish uchun eng maqbul shakl hisoblanadi. Magniy malat surunkali charchoq yoki depressiyani yengishda yordam beradi.</t>
+  </si>
+  <si>
+    <t>Kalsiy va magniy organizmning asab, mushak va qon aylanish tizimlarining normal faoliyati, shuningdek, suyuqlik muvozanatini me’yorida saqlash uchun zarur. Kalsiy va magniy suyak tizimining shakllanishi va sog‘lom holatini saqlashga ham yordam beradi.</t>
+  </si>
+  <si>
+    <t>Kalsiy sitrati — suyak tizimi salomatligini saqlash uchun zarur bo‘lgan kalsiyning oson o‘zlashtiriladigan shaklidir. Preparat tarkibiga D vitamini, magniy, rux, mis va marganets ham kiritilgan, chunki ular suyak to‘qimasi metabolizmida muhim rol o‘ynaydi.</t>
+  </si>
+  <si>
+    <t>NOW kompaniyasining betain gidroxloridi oshqozonda ovqatning normal hazm bo‘lish jarayonini ta’minlaydi. Xlorid kislota (HCl) oshqozonda tabiiy ravishda ishlab chiqariladi. U oqsillarning hazm bo‘lishiga yordam beradi, pepsinni faollashtiradi, ichak mikroflorasi muvozanatini saqlashni ta’minlaydi va ichak fermentlarining ajralishini rag‘batlantiradi. Pepsin — oshqozonda ishlab chiqariladigan va oziq-ovqat tarkibidagi oqsillarni parchalaydigan proteazadir. Yosh o‘tishi bilan HCl ishlab chiqarilishi kamayadi, shuning uchun uning, shuningdek, pepsinning o‘rnini to‘ldirish ovqat hazm qilish jarayonining normal kechishini ta’minlashga yordam beradi.</t>
+  </si>
+  <si>
+    <t>Garcinia cambogia Janubi-Sharqiy Osiyoda o‘sadi va qadimdan tabiblar tomonidan qo‘llanib kelinadi. Garciniyaning asosiy faol komponenti — gidroksilimon kislotasi (GLK) yog‘ kislotalarining hujayra ichidagi sintezi uchun mas’ul bo‘lgan asosiy ferment — sitratliazaga ta’siri nuqtayi nazaridan chuqur o‘rganilgan. Ilmiy tadqiqotlar shuni ko‘rsatdiki, gidroksilimon kislotasi mavjud bo‘lganda hujayralar uglevodlardan kamroq miqdorda yog‘ kislotalarini ishlab chiqaradi.</t>
+  </si>
+  <si>
+    <t>D3 va K2 vitaminlari — suyaklar, tishlar va yurak-qon tomir tizimi salomatligini saqlashdagi roli batafsil o‘rganilgan ikki muhim oziq moddasidir. Kalsiy bilan o‘zaro ta’sirlashib, D3 vitamini suyak tizimi salomatligini qo‘llab-quvvatlaydi, so‘nggi tadqiqotlarga ko‘ra, u immun tizimi faoliyati uchun ham muhim ahamiyatga ega. MK-7 MenaQ7 — soyasiz ishlab chiqarilgan K2 vitaminining noyob, yuqori bioo‘zlashtiriladigan shakli bo‘lib, qon tomirlari va arteriyalarda kalsiy almashinuvining to‘g‘ri kechishini ta’minlash xususiyati tufayli arteriyalar salomatligini saqlashda muhim rol o‘ynaydi. Bundan tashqari, K2 vitamini mustahkam va sog‘lom suyaklarning shakllanishiga yordam beradi.</t>
+  </si>
+  <si>
+    <t>D3 va K2 vitaminlari suyaklar, tishlar va yurak-qon tomir tizimi salomatligini saqlashdagi roli chuqur o‘rganilgan ikki muhim oziq moddasini o‘zida mujassam etadi. D3 vitamini organizmda kalsiyning tashilishi va o‘zlashtirilishiga yordam beradi. K vitaminining arteriyalar salomatligidagi vazifasi qon tomirlari tuzilmalarida kalsiy almashinuvining normal kechishiga yordam berishdan iborat.</t>
+  </si>
+  <si>
+    <t>Qo‘llash uchun ko‘rsatmalar va foydasi: immun tizimini mustahkamlash; raxitning oldini olish; suyaklar va mushaklarni mustahkamlash; yuqori xavf guruhiga kiruvchi odamlarda D3 vitamini yetishmovchiligining oldini olish; osteomalatsiya va raxitni davolash; gipoparatireozni davolash; osteoporozda qo‘llab-quvvatlash.</t>
+  </si>
+  <si>
+    <t>Temir — kislorodni tana hujayralariga tashuvchi molekula — gemoglobinning eng muhim tarkibiy qismidir. Temir, shuningdek, mushak to‘qimalarida kislorodni bog‘laydigan oqsil — mioglobinning ham tarkibiga kiradi. NOW kompaniyasi Ferrochel temir bisglitsinati shaklidan foydalanadi, chunki klinik tadqiqotlar ma’lumotlariga ko‘ra, u yaxshiroq o‘zlashtiriladi va organizmga yumshoq ta’sir ko‘rsatishi hamda qabziyatni keltirib chiqarmasligi sababli yaxshi o‘zlashtiriladi.</t>
+  </si>
+  <si>
+    <t>Ushbu mahsulotda inozitol sifatida mio-inozitol — ushbu oziq moddasining eng boy shakli qo‘llaniladi. Inozitol barcha hujayra membranalarida, ayniqsa bosh miya hujayralari va butun markaziy asab tizimi hujayralarida mavjud bo‘lib, u yerda neyromediatorlar signallarini uzatishda muhim rol o‘ynaydi. Inozitol, shuningdek, insulinning to‘g‘ri ta’sir qilishi, uglevodlar almashinuvi hamda hujayra darajasida kalsiy muvozanatini saqlash uchun juda muhimdir.</t>
+  </si>
+  <si>
+    <t>Xolin va inozitol B guruhi vitaminlari tarkibiga kiradi. Xolin normal sinaptik uzatish, miya salomatligi, shuningdek, jigarda yog‘ kislotalari almashinuvi uchun zarur. Xolin gepatoprotektor hisoblanadi. Inozitol ham miya va asab tizimi salomatligi uchun zarur. Xolin va inozitol barcha hujayra membranalarining muhim tarkibiy qismlaridir.</t>
+  </si>
+  <si>
+    <t>Selen aritmiya, yurak ishemik kasalligi, gipertoniya, ateroskleroz holatlarida hamda miokard infarkt</t>
+  </si>
+  <si>
+    <t>Spirulina — tarkibida o‘simlik oqsili, shuningdek, vitaminlar, minerallar va gamma-linolen kislotasi kabi boshqa oziq moddalari mavjud bo‘lgan ko‘k-yashil mikroalgadir. Spirulina sayyoramizdagi yuqori sifatli oqsilning eng yuqori miqdoriga ega bo‘lib, uning tarkibida taxminan 60% oqsil mavjud. Ushbu algada ko‘plab foydali moddalar: inson uchun zarur bo‘lgan barcha aminokislotalar, organizmdan toksinlarni chiqarishga yordam beruvchi antioksidantlar, vitaminlar, minerallar va GLK mavjud. Tarkibida yod miqdori me’yorida bo‘lib, qalqonsimon bez giperfunksiyasi va buqoq holatlarida foydali.</t>
+  </si>
+  <si>
+    <t>NOW kompaniyasining GMO tarkibiga ega bo‘lmagan kapsuladagi letsitini tarkibida miya va asab tizimi hujayralarining katta qismini tashkil etuvchi fosfatidilxolin mavjud. Miya faoliyatini yaxshilaydi, asab tizimini mustahkamlaydi va o‘t suyuqligini suyultiradi. Letsitinning xususiyatlari: regenerativ — shikastlangan hujayralarni tiklaydi; antioksidant — erkin radikallarni samarali ravishda zararsizlantiradi va toksinlarni neytrallaydi; gepatoprotektiv — jigarni zararli moddalardan ishonchli himoya qiladi.</t>
+  </si>
+  <si>
+    <t>Letsitin qon hosil bo‘lish jarayonini rag‘batlantiradi; organizmning turli infeksiyalar, viruslar va bakteriyalarga qarshiligini oshirishga yordam beradi; turli xil toksik moddalarning ta’siridan himoya qiladi; ateroskleroz rivojlanishining oldini olishga yordam beradi, qondagi xolesterin miqdorini kamaytirish orqali infarkt va insultlarning oldini olishga ko‘maklashishi mumkin.</t>
+  </si>
+  <si>
+    <t>Rux organizmdagi ko‘plab a’zo va tizimlarning normal faoliyat yuritishi uchun hayotiy muhim ahamiyatga ega. U immun, suyak, asab va endokrin tizimlar, shuningdek, prostata bezining salomatligini qo‘llab-quvvatlaydi.</t>
+  </si>
+  <si>
+    <t>Rux hujayralarning normal o‘sishi va bo‘linishi, to‘qimalarning tiklanishi, teri, soch va tirnoqlar go‘zalligini saqlash, asab, immun va reproduktiv tizimlarning faoliyati uchun zarur. Shuningdek, u hid bilish, ta’mni sezish va ko‘rish qobiliyati uchun muhim ahamiyatga ega.</t>
+  </si>
+  <si>
+    <t>Melatonin — erkin radikallarni samarali ravishda yo‘q qiluvchi modda bo‘lib, tabiiy ravishda epifiz bezida ishlab chiqariladi va oshqozon-ichak traktida katta miqdorda mavjud. U organizm, miya va bezlarning ko‘plab biologik funksiyalarida, jumladan, uyqu va uyg‘oqlikning normal sikllarini tartibga solishda, immun tizimi faoliyatini boshqarishda hamda oshqozon-ichak trakti shilliq qavatining sog‘lom holatini saqlashda ishtirok etadi.</t>
+  </si>
+  <si>
+    <t>B12 vitamini (sianokobalamin) — asab tizimi salomatligini saqlash va yog‘lar hamda oqsillardan energiya hosil qilish uchun zarur bo‘lgan suvda eruvchan vitamindir. B12 vitamini, shuningdek, hujayralar bo‘linishi jarayonida DNK sintezi uchun zarur bo‘lib, shu sababli tez bo‘linadigan hujayralar, masalan, qon hujayralari uchun alohida ahamiyatga ega. B12 vitaminini foliy kislotasi va B6 vitamini bilan birgalikda yetarli miqdorda iste’mol qilish homosisteinning metioninga aylanishi uchun muhim ahamiyatga ega bo‘lib, shu orqali yurak-qon tomir tizimining sog‘lom faoliyatini qo‘llab-quvvatlaydi.</t>
+  </si>
+  <si>
+    <t>B-50 tabletkalari B guruhi vitaminlarining to‘liq majmuasini, shuningdek, xolin va inozitolni o‘z ichiga oladi. Ushbu vitaminlar energiya ishlab chiqarishga, homosisteinning normal almashinuviga yordam beradi va asab tizimi salomatligini mustahkamlaydi. B guruhi vitaminlari suvda eruvchan bo‘lib, B12 vitaminidan tashqari, organizmda to‘planmaydi, shu sababli ularni har kuni to‘ldirib turish talab etiladi. B12 vitamini jigarda to‘planadi. Ushbu vitaminning deyarli barcha manbalari hayvonlardan olinadigan mahsulotlar bo‘lganligi sababli, B12 vitamini qo‘shimchasini qabul qilish qat’iy vegetarianlar uchun ayniqsa muhim bo‘lishi mumkin.</t>
+  </si>
+  <si>
+    <t>Vitamin C — immun tizimining normal faoliyatini ta’minlashda muhim rol o‘ynaydigan suvda eruvchan oziq moddasidir. Vitamin C kollagen (biriktiruvchi to‘qimaning strukturaviy oqsili) ishlab chiqarilishi uchun ham zarur va shu sababli teri, suyaklar va bo‘g‘imlar salomatligi uchun muhim ahamiyatga ega. Ushbu formulaga askorbin kislotaning tabiiy manbai bo‘lgan na’matak mevalari ham qo‘shilgan.</t>
+  </si>
+  <si>
+    <t>Vitamin C — immun tizimi faoliyatidagi hayotiy muhim roli bilan mashhur bo‘lgan suvda eruvchan oziq moddasidir. Vitamin C kollagen ishlab chiqarilishi uchun ham zarur va shu sababli teri, suyaklar va bo‘g‘imlar salomatligi uchun muhim ahamiyatga ega. Vitamin C aminokislotalar almashinuvi, neyrotransmitterlar sintezi hamda foliy kislotasi va temir kabi ko‘plab oziq moddalarining o‘zlashtirilishi uchun zarur. Shuningdek, u yuqori samarali antioksidant hisoblanadi. Ushbu noyob aralashma tarkibida na’matak mevalari va vitamin C bilan sinergik ta’sir qiluvchi bioflavonoidlar mavjud.</t>
+  </si>
+  <si>
+    <t>E-200 — kuchli antioksidant ta’sirga ega tabiiy biologik faol qo‘shimcha (d-alfa tokoferil). U hujayralarni oksidlovchi stressdan himoya qiladi, yurak-qon tomir tizimi, teri va sochlar salomatligini qo‘llab-quvvatlaydi hamda reproduktiv tizim faoliyatini yaxshilaydi. Zaytun moyi qo‘shilgan yumshoq jel kapsulalar shaklida ishlab chiqariladi. Hujayra membranalarini himoya qiladi, gormonal muvozanatni me’yorlashtiradi, ko‘rish qobiliyatini yaxshilaydi, charchoqni kamaytiradi va teri salomatligini qo‘llab-quvvatlaydi.</t>
+  </si>
+  <si>
+    <t>Vitamin E qon tomirlari salomatligi uchun zarur bo‘lib, ularning kengayishiga yordam beradi va trombotsitlar agregatsiyasini (trombotsitlarning bir-biriga yopishishini) bostirish orqali qon ivishining oldini oladi, arterial qon bosimini pasaytirishga yordam beradi.</t>
+  </si>
+  <si>
+    <t>Glutation uchta aminokislotadan: sistein, glutamin kislotasi va glitsindan tashkil topgan kichik peptid molekulasi hisoblanadi. U organizmning har bir hujayrasida ishlab chiqariladi, ayniqsa jigarda ishlab chiqarilish darajasi yuqori. Glutation immun tizimining normal faoliyati uchun nihoyatda muhim va detoksikatsiya jarayonlari uchun zarur. U erkin radikallarni bevosita zararsizlantirish, shuningdek, C va E vitaminlarining faolligini saqlab turish orqali hujayra darajasida salomatlikni qo‘llab-quvvatlashda muhim rol o‘ynaydi.</t>
+  </si>
+  <si>
+    <t>L-arginin — shartli ravishda almashtirib bo‘lmaydigan aminokislota bo‘lib, mochevina hosil bo‘lish siklida va toksinlarni chiqarishda, shuningdek, DNK va oqsillar sintezida ishtirok etadi. U qon tomirlarini kengaytirishda muhim ahamiyatga ega bo‘lgan azot oksidi (NO) ning asosiy prekursoridir. L-arginin mushak to‘qimalarining o‘sishiga samarali ta’sir qiladi, jismoniy chidamlilikni oshiradi va yog‘larni yoqishga yordam beradi, shuningdek, miya faoliyatiga ta’sir qiluvchi kreatin hosil bo‘lishi uchun zarur bo‘lgan insulin ishlab chiqarilishini rag‘batlantiradi.</t>
+  </si>
+  <si>
+    <t>L-arginin sport ovqatlanishida qon oqimini yaxshilash, mushaklarning “pamp” effektini kuchaytirish va tiklanish jarayonini tezlashtirish uchun azot oksidi (NO) prekursor sifatida qo‘llaniladigan almashtiriladigan aminokislotadir. U mushaklarning kislorod bilan ta’minlanishini yaxshilaydi, oqsil sinteziga yordam beradi, chidamlilikni oshiradi va yurak-qon tomir tizimini qo‘llab-quvvatlaydi; odatda mashg‘ulotdan oldin 1000–3000 mg miqdorida qabul qilinadi. To‘qimalarning bitishini tezlashtiradi va ammiak kabi parchalanish mahsulotlarini chiqarishga yordam beradi. Qon tomirlarining kengayishiga va qon bosimining pasayishiga ko‘maklashadi.</t>
+  </si>
+  <si>
+    <t>Sport ovqatlanishi uchun aminokislotalar kukuni. Sistein — metionin, taurin va glutation almashinuvida muhim rol o‘ynaydigan, oltingugurt saqlovchi almashtiriladigan aminokislotadir. U soch, tirnoq va terining tarkibiy qismidir. Sistein oqsil tuzilishini barqarorlashtiradi va kollagen ishlab chiqarilishiga yordam beradi, shu sababli teri, soch va tirnoqlar salomatligi uchun muhim hisoblanadi.</t>
+  </si>
+  <si>
+    <t>Sistein — metionin, taurin va glutation almashinuvida muhim rol o‘ynaydigan, oltingugurt saqlovchi almashtiriladigan aminokislotadir. U soch, tirnoq va terining tarkibiy qismidir. Sistein oqsil tuzilishini barqarorlashtiradi va kollagen ishlab chiqarilishiga yordam beradi, shu sababli teri, soch va tirnoqlar salomatligi uchun muhim hisoblanadi.</t>
+  </si>
+  <si>
+    <t>Toza L-karnitin — sog‘liqni mustahkamlashga yordam beradigan, yog‘ kislotalari guruhlarining mitoxondrial membranaga ko‘chirilishini yengillashtirib, hujayralarda energiya ishlab chiqarish jarayonini qo‘llab-quvvatlaydigan almashtiriladigan aminokislotadir. U tabiiy ravishda qizil go‘sht va hayvonlardan olinadigan boshqa mahsulotlar tarkibida mavjud, biroq ushbu zarur aminokislotaning optimal darajasini ta’minlash uchun karnitin saqlovchi qo‘shimchalarni qabul qilish tavsiya etiladi.</t>
+  </si>
+  <si>
+    <t>Taurin — oqsil sintezi uchun ishlatilmaydigan, shartli ravishda almashtirib bo‘lmaydigan aminokislota bo‘lib, asosan ko‘pchilik to‘qimalarda, ayniqsa asab tizimida erkin shaklda mavjud. Ushbu modda to‘qimalarning hujayra membranalarini barqarorlashtiradi, kaliy, natriy, kalsiy va magniyning hujayralarga kirishi va hujayralardan chiqishi jarayonini yengillashtiradi. Taurin nerv impulslarining hosil bo‘lishi va tartibga solinishiga yordam beradi, shuningdek, normal suv muvozanatini ta’minlaydi.</t>
+  </si>
+  <si>
+    <t>Xrom — muhim mikroelement bo‘lib, insulin kofaktori sifatidagi roli bilan eng ko‘p tanilgan. Shu sababli xrom glyukoza va uglevodlar almashinuvining sog‘lom kechishini ta’minlash uchun nihoyatda muhimdir. Bundan tashqari, u yog‘lar va oqsillarning o‘zlashtirilishida katta ahamiyatga ega. Ilmiy tadqiqotlar xrom yurak-qon tomir kasalliklarining oldini olishda muayyan rol o‘ynashi mumkinligini ko‘rsatadi. Sog‘lom ovqatlanish va jismoniy mashqlar dasturi bilan birgalikda xrom pikolinat qondagi qand miqdorini me’yorida saqlashga, shuningdek, tana to‘qimalarining sog‘lom tarkibini ta’minlashga yordam beradi.</t>
+  </si>
+  <si>
+    <t>Sutqaymoq o‘simligi asrlar davomida an’anaviy tabiblar tomonidan qo‘llanib kelingan. Ilmiy tadqiqotlar sutqaymoq jigarning sog‘lom faoliyatini qo‘llab-quvvatlashga yordam berishi mumkinligini ko‘rsatgan. Ushbu vegetarian vosita qo‘shimcha qo‘llab-quvvatlash uchun artishok va momaqaymoqni ham o‘z ichiga oladi.</t>
+  </si>
+  <si>
+    <t>Sigir kollagenidan olingan 1 va 3 turdagi kollagen peptidlari suyaklar, bo‘g‘imlar va teri salomatligini qo‘llab-quvvatlashdagi roli bilan yaxshi tanilgan. Sutemizuvchilar organizmida eng ko‘p uchraydigan oqsil bo‘lgan kollagen organizmdagi oqsillarning taxminan 30 foizini tashkil etadi. Tadqiqotlar gidrolizlangan kollagen mustahkam suyaklar va sog‘lom bo‘g‘imlarni qo‘llab-quvvatlashi, shuningdek, terini silliq va namlangan holda saqlashga yordam berishi mumkinligini ko‘rsatadi.</t>
+  </si>
+  <si>
+    <t>Tog‘ay — organizmdagi asosiy biriktiruvchi to‘qimalardan biri bo‘lib, bo‘g‘imlarning egiluvchanligi va tayanchini ta’minlaydi. Denaturatsiyalanmagan II turdagi kollagen tog‘ayning asosiy tarkibiy oqsili bo‘lib, uning cho‘zilishga chidamliligi va zichligini ta’minlaydi. Tovuq ko‘krak qafasi tog‘ayidan olingan UC-II ingrediyenti denaturatsiyalanmagan (tabiiy) II turdagi kollagenni o‘z ichiga olgan kollagenning noyob shakli bo‘lib, immun tizimi bilan o‘zaro ta’sirlashib, bo‘g‘imlar salomatligini qo‘llab-quvvatlaydi. Insonlar ishtirokidagi klinik tadqiqotlar shuni ko‘rsatdiki, kuniga atigi bitta UC-II (40 mg) kapsulasini iste’mol qilish bo‘g‘imlardagi qulaylikni, shuningdek, ularning sog‘lom faoliyati va egiluvchanligini ta’minlashga yordam berishi mumkin.</t>
+  </si>
+  <si>
+    <t>Alfa-lipoik kislota (ALK) inson organizmida juda oz miqdorda ishlab chiqariladi, biroq uni oziq-ovqat orqali ham olish mumkin. Alfa-lipoik kislota o‘ziga xos bo‘lib, organizmdagi erkin radikallarni zararsizlantirish tizimlarini qo‘llab-quvvatlaydi va ham suvli, ham yog‘li muhitda faoliyat ko‘rsata oladi. Alfa-lipoik kislota moddalar almashinuvida ishtirok etadi, oziq-ovqat tarkibida qo‘llanganda qondagi qand miqdorini me’yorida saqlashga hamda glyukozani organizm ehtiyojlari uchun energiyaga aylantirishga (energiya almashinuvi) yordam beradi; shuningdek, detoksikatsiya, nuklein kislotalar sintezi va organizmdagi boshqa biokimyoviy reaksiyalarda ishtirok etadi. U asab tizimi, immun tizimi va jigar salomatligini qo‘llab-quvvatlaydi.</t>
+  </si>
+  <si>
+    <t>Foliy kislotasi — B guruhi vitaminlari oilasining juda muhim vakili. U DNK sintezi va genetik shikastlanishlarni tiklash uchun zarur. Ushbu moddaning normal ishlab chiqarilishi eritrotsitlar kabi tez bo‘linadigan hujayralar uchun muhimdir. Foliy kislotasi homosisteindan metionin sintezi uchun zarur, shuningdek, yurak-qon tomir va asab tizimlarining normal faoliyatini qo‘llab-quvvatlashga yordam beradi. U suyak ko‘migi uchun zarur bo‘lib, normal ishtaha, uyqu va kayfiyatni ta’minlovchi neyrotransmitterlar sintezida ishtirok etadi.</t>
+  </si>
+  <si>
+    <t>Metilfolat — hujayralarning normal bo‘linishi, neyrotransmitterlar va DNK sintezida muhim rol o‘ynaydigan, tabiiy ravishda mavjud bo‘lgan folatning biologik faol shaklidir. Oddiy foliy kislotasidan farqli ravishda, tadqiqotlar metilfolat gematoensefalik to‘siqdan o‘tib, asab tizimi salomatligini qo‘llab-quvvatlashini ko‘rsatgan. Metilfolat qon plazmasidagi homosistein va xolesterin miqdorini nazorat qilishga yordam beradi, yurak-qon tomir kasalliklarining oldini olishda qo‘llaniladi, ovqat hazm qilish traktining faoliyatini yaxshilashga va immun tizimini mustahkamlashga yordam beradi.</t>
+  </si>
+  <si>
+    <t>Ko‘rsatmalar: xotiraning susayishi; intellektual qobiliyatlarning pasayishi; qo‘rquv hissi; uyqu buzilishlari; periferik qon aylanishi va mikrosirkulyatsiyaning buzilishi (jumladan, Reyno sindromi); neyrosensor buzilishlar (bosh aylanishi, quloqlarda shang‘illash, eshitish qobiliyatining pasayishi).</t>
+  </si>
+  <si>
+    <t>Berberin — sariq ildiz, Oregon uzumi va zirk kabi o‘simliklarda uchraydigan tabiiy komponent. Klinik tadqiqotlar berberin glyukoza va lipidlarning normal almashinuvini qo‘llab-quvvatlashga yordam berishini ko‘rsatgan. Berberin cheklangan bioo‘zlashtirilishi bilan tanilganligi sababli, ushbu mahsulot tarkibida kaprat (C10, o‘rta zanjirli triglitserid) mavjud bo‘lib, u berberinning optimal o‘zlashtirilishiga va uni qabul qilish vaqtida oshqozon-ichak tizimida qulaylikni saqlashga yordam beradi.</t>
+  </si>
+  <si>
+    <t>Echinacea streptokokk, stafilokokk, ichak tayoqchasi, gripp va gerpes viruslari, stomatitning o‘sishi va ko‘payishini bostirish, ruhiy va jismoniy zo‘riqish, depressiya, moddalar almashinuvi buzilishi bilan bog‘liq kasalliklarda (qandli diabet, semirish, jigar kasalliklari) kompleks davolash tarkibida qo‘llaniladi.</t>
+  </si>
+  <si>
+    <t>Gamma-aminomoy kislota (GAMK) — inson miyasida neyrotransmitter vazifasini bajaradigan oqsil tarkibiga kirmaydigan aminokislotadir. GAMK organizmda tabiiy ravishda sintez qilinadi va uning markaziy asab tizimida mavjudligi bo‘shashish va asabiy zo‘riqishni kamaytirishga yordam berishi mumkin.</t>
+  </si>
+  <si>
+    <t>PABK (para-aminobenzoy kislotasi) don mahsulotlari, tuxum, sut va go‘sht kabi oziq-ovqat mahsulotlarida mavjud. U foliy kislotasining prekursori hisoblanadi. Ichak mikrofloramiz undan foliy kislotasini sintez qilishi mumkin. PABK shuningdek, hujayralarga oksidlovchi stressga qarshi kurashishda yordam berishi mumkin.</t>
+  </si>
+  <si>
+    <t>Kelp — sovuq okean suvlarining tubida o‘sadigan, qo‘ng‘ir suvo‘tlar oilasiga mansub yirik, keng bargli dengiz suvo‘tlaridir. Asrlar davomida kelp Xitoy, Yaponiya va Koreya oshxonalarida ratsionning muhim qismi bo‘lib kelgan. Shuningdek, u qalqonsimon bezning normal faoliyati uchun zarur bo‘lgan yodning ajoyib manbai hisoblanadi.</t>
+  </si>
+  <si>
+    <t>Xlorofill fotosintezda, ya’ni quyosh nurini kimyoviy energiyaga aylantirish jarayonida muhim rol o‘ynaydi. Xlorofill erkin radikallarni zararsizlantiruvchi vosita sifatida ta’sir qilishi, organizmdagi detoksikatsiya jarayonlariga yordam berishi va an’anaviy ravishda ichki dezodorant sifatida qo‘llanilishi mumkin. Ushbu suvda eruvchan ekstrakt natriy-mis xlorofillini shaklida mavjud.</t>
+  </si>
+  <si>
+    <t>NOW Kid Vits Berry Lemonade — bolalar uchun yoqimli rezavor meva ta’miga ega, immunitet, suyaklar va umumiy rivojlanishni qo‘llab-quvvatlash uchun ishlab chiqilgan kompleks vitamin-mineral biologik faol qo‘shimcha. Tarkibida 11 ta vitamin, 9 ta mineral, tabiiy xushbo‘ylashtiruvchi moddalar mavjud bo‘lib, shakar qo‘shilmagan. Tarkibiga A, C, D, E vitaminlari, B guruhi vitaminlari, shuningdek, kalsiy, magniy, rux va yod kiradi.</t>
+  </si>
+  <si>
+    <t>NOW Foods Elderberry Liquid for Kids (bolalar uchun suyuq buzina ekstrakti) — bolalarda immunitetni mustahkamlash uchun mo‘ljallangan, buzina ekstrakti, rux va astragalni o‘z ichiga olgan tabiiy qo‘shimcha. Sirop shamollash mavsumida salomatlikni qo‘llab-quvvatlaydi, yoqimli ta’mga ega va shakar saqlamaydi. Immun tizimini mustahkamlash va mavsumiy kasalliklardan himoya qilishga yordam beradi.</t>
+  </si>
+  <si>
+    <t>NOW bolalar uchun kalsiyli chaynash tabletkalari — bolalarga yoqadigan mazali chaynash pastilkalari bo‘lib, ularni zarur kalsiy, magniy va D vitamini bilan ta’minlaydi.</t>
+  </si>
+  <si>
+    <t>Bolalarda aqliy rivojlanishni qo‘llab-quvvatlash. Diqqatni jamlashni oshirish va xotirani yaxshilash. Immunitetni mustahkamlash. Yurak-qon tomir kasalliklarining oldini olish.</t>
+  </si>
+  <si>
+    <t>NOW Foods rozmarin efir moyi (100% Pure Rosemary Oil) — barglarni bug‘li distillatsiya qilish orqali olingan, aromaterapiya va kosmetik parvarish uchun mo‘ljallangan tabiiy, yuqori konsentratsiyali vosita. Yangi, kamforaga xos hidga ega, tetiklashtiradi, diqqatni jamlashni yaxshilaydi, sochlarni mustahkamlaydi va terini tozalaydi. Diqqatni jamlashni oshiradi, aqliy faoliyatni rag‘batlantiradi, tetiklashtiradi va charchoqni kamaytiradi.</t>
+  </si>
+  <si>
+    <t>Choy daraxti efir moyi (Tea Tree Oil) — Melaleuca alternifolia barglaridan bug‘li distillatsiya usuli orqali olingan 100% tabiiy, sof mahsulot. Kuchli antiseptik, zamburug‘larga qarshi va antimikrob ta’siri bilan mashhur bo‘lib, muammoli terini (akne, gerpes) parvarish qilish, yaralarni bitirish, shuningdek, aromaterapiyada samarali qo‘llaniladi. Husnbuzar, akne, furunkulyoz va ekzemada yordam beradi, tirnash xususiyati va qichishishni kamaytiradi hamda toshmalarni quritadi.</t>
+  </si>
+  <si>
+    <t>Evkalipt efir moyi (100% Pure Eucalyptus Oil) — evkalipt barglaridan olinadigan, aromaterapiya, ingalyatsiya va massajda keng qo‘llaniladigan tabiiy konsentrlangan mahsulot. U antiseptik, viruslarga qarshi va balg‘am ko‘chiruvchi xususiyatlari bilan mashhur bo‘lib, shamollash, yo‘tal, burun oqishi holatlarida va nafas olishni yaxshilashda yordam beradi. Kuchli yallig‘lanishga qarshi, antiseptik, mukolitik (balg‘amni suyultiruvchi) va tetiklashtiruvchi ta’sir ko‘rsatadi. Sinusit, gaymorit va bronxitda yordam beradi.</t>
+  </si>
+  <si>
+    <t>California Gold Nutrition Gold C — C vitamini (askorbin kislotasi, Quali-C) organizmda sintez qilinmaydi va oziq-ovqat yoki biologik faol qo‘shimchalar orqali olinadi. U meva va sabzavotlarda, jumladan, sitrus mevalari, qora smorodina, qalampir, yashil sabzavotlar (brokkoli), Bryussel karami, qulupnay, guava, mango va kivida ko‘p miqdorda mavjud. C vitamini antioksidant xususiyatlarga ega bo‘lib, erkin radikallarni zararsizlantiradi, zararli moddalar va toksinlar konsentratsiyasini kamaytiradi. Tarkibida oshqozonga yumshoqroq ta’sir qiluvchi askorbat natriy (kislotali bo‘lmagan shakl) mavjud. C vitamini organizmning himoya kuchlarini mustahkamlash va teri salomatligini qo‘llab-quvvatlashga yordam beruvchi kuchli antioksidant hisoblanadi.</t>
+  </si>
+  <si>
+    <t>California Gold Nutrition Vitamin D3 5000 IU — suyaklar, tishlar va immun tizimi salomatligini qo‘llab-quvvatlash uchun mo‘ljallangan yuqori dozali qo‘shimcha. D vitamini yog‘da eruvchan bo‘lganligi sababli, kapsulalar tarkibida yaxshiroq o‘zlashtirilishini ta’minlash uchun maxsar moyi mavjud. D3 vitamini — immun tizimi va moddalar almashinuvining normal faoliyati uchun zarur bo‘lgan “quyosh” vitaminining ajoyib manbai. D vitamini yetishmovchiligi osteoporoz, ko‘p skleroz, astma, migren va psoriaz kabi kasalliklarning rivojlanishiga olib kelishi mumkin. Kuz-qish davrida kunduzgi yorug‘lik vaqtining qisqarishi sababli vitaminlarni qabul qilish muhimligini unutmaslik kerak.</t>
+  </si>
+  <si>
+    <t>California Gold Nutrition Vitamin D3 for Babies, Liquid tarkibida atigi ikkita ingredient — D3 vitamini va fraksiyalangan kokos moyi (o‘rta zanjirli triglitseridlar) mavjud. Tarkibida spirt, glyuten va GMO mavjud emas. Sog‘lom skeletning o‘sishi uchun zarur bo‘lgan kalsiy va fosforning organizm tomonidan o‘zlashtirilishiga yordam beradi. Hayvonlardan olinadigan vitamin bo‘lib, uning bevosita prekursor moddasi 7-degidroxolesterin (D3 provitamini) hisoblanadi. Tomchilar kuchli ta’m va hidga ega emas, shuning uchun bolalar odatda ularni muammosiz qabul qiladilar.</t>
+  </si>
+  <si>
+    <t>California Gold Nutrition LactoBif 5 Billion probiotics — ovqat hazm qilish va immun tizimlari salomatligini qo‘llab-quvvatlash uchun mo‘ljallangan probiotik qo‘shimcha. Uning tarkibida oshqozonning kislotali muhitiga chidamli, ovqat hazm qilish tizimi salomatligini qo‘llab-quvvatlovchi va oshqozon buzilishi, gaz, qabziyat, diareya hamda qorin dam bo‘lishi kabi keng tarqalgan ovqat hazm qilish muammolarini bartaraf etishga yordam beruvchi 8 ta faol bakteriya shtammining muvozanatli aralashmasi (5 turdagi laktobakteriyalar va 3 turdagi bifidobakteriyalar) mavjud. Tarkibida Lactobacillus acidophilus (immunitetni qo‘llab-quvvatlash) va Bifidobacterium longum (sut va sirka kislotalarini ishlab chiqarish orqali ichak salomatligini qo‘llab-quvvatlash) mavjud.</t>
+  </si>
+  <si>
+    <t>California Gold Nutrition LactoBif 30 Billion probiotics — ovqat hazm qilish va immun tizimlari salomatligini qo‘llab-quvvatlash uchun mo‘ljallangan probiotik qo‘shimcha. Uning tarkibida oshqozonning kislotali muhitiga chidamli 8 ta faol bakteriya shtammining muvozanatli aralashmasi (5 turdagi laktobakteriyalar va 3 turdagi bifidobakteriyalar) mavjud. Oshqozon buzilishi, gaz, qabziyat, diareya va qorin dam bo‘lishi kabi keng tarqalgan ovqat hazm qilish muammolarini bartaraf etishga yordam beradi. Tarkibida Lactobacillus acidophilus (immunitetni qo‘llab-quvvatlash) va Bifidobacterium longum (sut va sirka kislotalarini ishlab chiqarish orqali ichak salomatligini qo‘llab-quvvatlash) mavjud.</t>
+  </si>
+  <si>
+    <t>California Gold Nutrition CollagenUP — kollagen saqlovchi eng mashhur qo‘shimchalardan biri bo‘lib, dengiz kollageni peptidlari, gialuron kislotasi va C vitaminini o‘zida mujassam etadi. U soch, teri, tirnoq, bo‘g‘imlar va suyaklar salomatligini qo‘llab-quvvatlash uchun ishlab chiqilgan. Tarkibida baliqdan olingan gidrolizlangan kollagen peptidlari mavjud. Dengiz kollageni mol kollageniga qaraganda bioo‘zlashtirilishi yuqoriroq (yaxshiroq o‘zlashtiriladi) deb hisoblanadi. Gialuron kislotasi terida namlikni ushlab turishga va bo‘g‘imlarni moylashga yordam beradi. C vitamini organizmda o‘z kollagenining sintezi uchun zarur bo‘lib, antioksidant sifatida ham ta’sir ko‘rsatadi.</t>
+  </si>
+  <si>
+    <t>California Gold Nutrition CollagenUP — kollagen saqlovchi eng mashhur qo‘shimchalardan biri bo‘lib, dengiz kollageni peptidlari, gialuron kislotasi va C vitaminini o‘zida mujassam etadi. U soch, teri, tirnoq, bo‘g‘imlar va suyaklar salomatligini qo‘llab-quvvatlash uchun ishlab chiqilgan. Tarkibida baliqdan olingan gidrolizlangan kollagen peptidlari mavjud. Dengiz kollageni mol kollageniga qaraganda bioo‘zlashtirilishi yuqoriroq deb hisoblanadi. Gialuron kislotasi terida namlikni ushlab turishga va bo‘g‘imlarni moylashga yordam beradi. C vitamini o‘z kollagenining sintezi uchun zarur bo‘lib, antioksidant sifatida ham ta’sir ko‘rsatadi.</t>
+  </si>
+  <si>
+    <t>NaturesPlus Hema-Plex Slow-Release Tablets — temir tanqisligining oldini olish va uni to‘g‘rilash uchun mo‘ljallangan, temirni uzaytirilgan (sekin) chiqarilish xususiyatiga ega kompleks preparat. Bir tabletkada xelat shaklidagi 85 mg temir, shuningdek, eritrotsitlar hosil bo‘lishida ishtirok etadigan va temirning o‘zlashtirilishini yaxshilaydigan C vitamini, folat (foliy kislotasining faol shakli), B12 vitamini, mis va boshqa kofaktorlar mavjud. Slow-release texnologiyasi tufayli temir asta-sekin ajralib chiqadi, bu oshqozonning tirnash xususiyatini kamaytirishga va preparatning o‘zlashtirilishini yaxshilashga yordam beradi.</t>
+  </si>
+  <si>
+    <t>NaturesPlus Hema-Plex Iron, 60 ta tez ta’sir qiluvchi kapsula — qon hosil bo‘lishini qo‘llab-quvvatlash uchun mo‘ljallangan, yuqori dozadagi temir hamda qo‘shimcha vitamin va minerallarni o‘z ichiga olgan kompleks. Kunlik porsiyada (2 kapsula) xelat shaklidagi 85 mg temir, shuningdek, C vitamini, faol folat (metilfolat), B12 vitamini (metilkobalamin), mis va B guruhi vitaminlari mavjud. Preparat temirning organizmga tez yetib borishini ta’minlash uchun ishlab chiqilgan bo‘lib, odatda temir tanqisligi, ferritin darajasining pastligi yoki temir tanqisligi anemiyasida qo‘llaniladi.</t>
+  </si>
+  <si>
+    <t>NaturesPlus Hema-Plex Iron with Essential Nutrients for Healthy Red Blood Cells — sekin chiqariladigan (Slow Release) tabletkalar shaklidagi kompleks temir preparati. Bir tabletkada xelat shaklidagi 85 mg temir mavjud. Temirdan tashqari, tarkibida gemoglobin va eritrotsitlar hosil bo‘lishi uchun zarur bo‘lgan C vitamini, faol folat, B12 vitamini, mis va boshqa B guruhi vitaminlari mavjud. Sekin chiqarilish texnologiyasi temirning bir necha soat davomida asta-sekin ajralib chiqishini ta’minlaydi, bu oshqozon va ichaklarning tirnash xususiyatini kamaytirishga, shuningdek, ko‘ngil aynishi va qabziyat xavfini pasaytirishga yordam beradi.</t>
+  </si>
+  <si>
+    <t>NaturesPlus Hema-Plex Iron Chewables — tabletkalar yoki kapsulalarni yutishda qiynaladigan odamlar uchun mo‘ljallangan, rezavor meva ta’miga ega chaynash shaklidagi temir preparatidir. Preparat tarkibida temir bilan birga gemoglobin va sog‘lom eritrotsitlar hosil bo‘lishini qo‘llab-quvvatlovchi C vitamini, folat, B12 vitamini va boshqa oziq moddalar mavjud. Ushbu vosita temir tanqisligining oldini olish va uni to‘g‘rilash, ferritin darajasi past bo‘lganda, temir tanqisligi anemiyasida hamda organizmning temirga bo‘lgan ehtiyoji oshgan holatlarda qo‘llaniladi.</t>
+  </si>
+  <si>
+    <t>NaturesPlus Hema-Plex Liquid Iron &amp; Essential Nutrients — temir tanqisligini to‘ldirish va eritrotsitlarning normal hosil bo‘lishini qo‘llab-quvvatlash uchun mo‘ljallangan, rezavor meva ta’miga ega suyuq temir shaklidir. Preparat tarkibida gemoglobin sintezida ishtirok etadigan temir, C vitamini, B guruhi vitaminlari, folat va boshqa oziq moddalar mavjud. Suyuq shakli tabletkalarni yutishda qiynaladigan odamlar uchun qulay bo‘lib, dozani oson tartibga solish imkonini beradi.</t>
+  </si>
+  <si>
+    <t>Bu teri, soch, tirnoqlar, bo‘g‘imlar va biriktiruvchi to‘qimalarni qo‘llab-quvvatlash uchun mo‘ljallangan, gidrolizlangan kollagen peptidlarini o‘z ichiga olgan kukun shaklidagi qo‘shimcha. Ko‘plab kollagen mahsulotlaridan farqli ravishda, tarkibida bir vaqtning o‘zida kollagenning 6 ta asosiy turi (I, II, III, IV, V va X) mavjud bo‘lib, ular bir nechta manbalardan: o‘t bilan boqilgan qoramol, baliq, tovuq va tuxum po‘chog‘i membranasidan olingan. Tarkibiga kollagenning hazm bo‘lishi va o‘zlashtirilishini yaxshilash uchun fermentlar ham kiritilgan. Kukun o‘ziga xos kuchli ta’m va hidga ega emas, suv, sharbat, qahva, choy yoki smuzi bilan oson aralashtiriladi.</t>
+  </si>
+  <si>
+    <t>NaturesPlus Collagen Peptides Vanilla Flavor — teri, soch, tirnoqlar, bo‘g‘imlar, bog‘lamlar va suyaklarni qo‘llab-quvvatlash uchun mo‘ljallangan, tabiiy vanil ta’miga ega kollagen peptidlari kukunidir. Mahsulot tarkibida gidrolizlangan kollagen mavjud bo‘lib, u allaqachon kichik peptidlarga parchalanganligi sababli suvda yaxshi eriydi va organizm tomonidan yaxshi o‘zlashtiriladi. Tarkibida kollagenning bir nechta turlari, jumladan, teri va biriktiruvchi to‘qimalar uchun eng muhim bo‘lgan I, II va III turdagi kollagen mavjud.</t>
+  </si>
+  <si>
+    <t>NaturesPlus Collagen Peptides Chocolate Flavor — gidrolizlangan kollagen peptidlari va tabiiy shokolad ta’miga ega kukun shaklidagi qo‘shimcha. Mahsulot teri, soch, tirnoqlar, bo‘g‘imlar, bog‘lamlar va suyak to‘qimasini qo‘llab-quvvatlash uchun mo‘ljallangan. Tarkibidagi kollagen allaqachon qisqa peptidlarga parchalangan bo‘lib, shu sababli suvda oson eriydi va organizm tomonidan yaxshi o‘zlashtiriladi. Qo‘shimcha aminokislotalar, avvalo glitsin, prolin va gidroksiprolinning manbai hisoblanadi.</t>
+  </si>
+  <si>
+    <t>NaturesPlus MagKidz Animal Parade Magnesium — hayvonlarning qiziqarli shaklidagi va olcha ta’miga ega, bolalar uchun mo‘ljallangan magniyli chaynash qo‘shimchasi. Bir dona chaynash tabletkasida mushaklar, asab tizimining normal faoliyati, energiya ishlab chiqarish, suyaklarni qo‘llab-quvvatlash va organizmdagi umumiy mineral muvozanat uchun zarur bo‘lgan 50 mg magniy mavjud. Magniy ratsion orqali minerallar yetarli darajada olinmaganda, yuqori jismoniy yuklamalarda, asabiylashish va mushaklarning taranglashuvi holatlarida foydali bo‘lishi mumkin.</t>
+  </si>
+  <si>
+    <t>NaturesPlus Animal Parade MagKidz — olcha ta’miga ega, bolalar uchun mo‘ljallangan magniyli qo‘shimcha. Mahsulot maxsus bolalar uchun ishlab chiqilgan bo‘lib, asab tizimi, mushaklar, suyaklarning normal faoliyati va energiya almashinuvi uchun muhim mineral bo‘lgan magniyni o‘z ichiga oladi. Magniy mushaklarning bo‘shashishi, nerv impulslarining normal uzatilishi va organizmdagi umumiy mineral muvozanatni ta’minlash jarayonlarida ishtirok etadi.</t>
+  </si>
+  <si>
+    <t>NaturesPlus Animal Parade Gold — oddiy Animal Parade seriyasiga nisbatan tarkibi kengaytirilgan, bolalar uchun mo‘ljallangan takomillashtirilgan chaynash multivitamin kompleksidir. Tabletkalar hayvonlar shaklida tayyorlangan bo‘lib, olcha, uzum va apelsin ta’miga ega. Tarkibida bolaning o‘sishi, immun tizimi, energiyasi, asab tizimi, ko‘rish qobiliyati, suyaklari va umumiy rivojlanishini qo‘llab-quvvatlash uchun zarur bo‘lgan vitaminlar va minerallar mavjud.</t>
+  </si>
+  <si>
+    <t>NaturesPlus Animal Parade Children's Chewable Multivitamin — olcha, uzum va apelsin ta’miga ega, hayvonlar shaklidagi, bolalar uchun mo‘ljallangan chaynash multivitamin kompleksidir. Qo‘shimcha maxsus bolalar uchun ishlab chiqilgan bo‘lib, normal o‘sish, rivojlanish, immun himoyasi, energiya almashinuvi, suyaklar salomatligi va organizmning umumiy holati uchun zarur bo‘lgan vitaminlar va minerallar kompleksini o‘z ichiga oladi. Tarkibida odatda A, C, D, E vitaminlari, B guruhi vitaminlari, shuningdek, minerallar (rux, yod va boshqa mikroelementlar) mavjud.</t>
+  </si>
+  <si>
+    <t>NaturesPlus Animal Parade Gold — olcha, uzum va apelsin ta’miga ega, hayvonlar shaklidagi, bolalar uchun mo‘ljallangan chaynash multivitamin kompleksidir. Gold versiyasi Animal Parade seriyasining kengaytirilgan formulasi bo‘lib, bolalarning o‘sishi, rivojlanishi, immun tizimi, energiya darajasi, suyaklar salomatligi, ko‘rish qobiliyati va umumiy moddalar almashinuvini qo‘llab-quvvatlash uchun ishlab chiqilgan. Tarkibida A, C, D, E vitaminlari, B guruhi vitaminlari va zarur mikroelementlarni o‘z ichiga olgan vitaminlar va minerallar kompleksi mavjud.</t>
+  </si>
+  <si>
+    <t>NaturesPlus Animal Parade Children's Chewable Multivitamin — olcha, uzum va apelsin ta’miga ega, hayvonlar shaklidagi, bolalar uchun mo‘ljallangan chaynash multivitamin kompleksidir. Preparat bolaning o‘sishi va rivojlanishi davrida organizmni qo‘llab-quvvatlash uchun yaratilgan: ratsiondagi vitaminlar va minerallar yetishmovchiligini to‘ldirishga yordam beradi, immun tizimi, normal moddalar almashinuvi, energiya, suyaklar, ko‘rish qobiliyati va asab tizimi salomatligini qo‘llab-quvvatlaydi.</t>
+  </si>
+  <si>
+    <t>NaturesPlus Animal Parade Children's Chewable Multivitamin tarvuz ta’miga ega — hayvonlar shaklidagi, bolalar uchun mo‘ljallangan chaynash multivitamin kompleksidir. Qo‘shimcha bolaning o‘sishi va rivojlanishi, immuniteti, normal moddalar almashinuvi, energiyasi, asab tizimi, ko‘rish qobiliyati va suyaklar salomatligini qo‘llab-quvvatlash uchun ishlab chiqilgan. Tarkibida A, C, D, E vitaminlari, B guruhi vitaminlari va boshqa oziq moddalarni o‘z ichiga olgan vitaminlar va minerallar kompleksi mavjud.</t>
+  </si>
+  <si>
+    <t>ChildLife Essentials Vitamin D3 — chaqaloqlar va bolalar uchun maxsus ishlab chiqilgan mashhur suyuq biologik faol qo‘shimcha. Rezavor meva ta’miga ega bo‘lib, organik o‘simlik glitseriniga asoslangan. Immun tizimini qo‘llab-quvvatlaydi, mustahkam suyaklar va tishlarning o‘sishi uchun kalsiy va fosforning o‘zlashtirilishiga yordam beradi.</t>
+  </si>
+  <si>
+    <t>ChildLife Essentials Vitamin C — 6 oylikdan 12 yoshgacha bo‘lgan bolalar uchun maxsus ishlab chiqilgan mashhur oziq-ovqat qo‘shimchasi. U immun tizimini qo‘llab-quvvatlash va organizmni antioksidant himoya bilan ta’minlash uchun mo‘ljallangan. Immunitetni mustahkamlaydi, kollagen sinteziga yordam beradi va organizmning kasalliklardan keyin tiklanishiga ko‘maklashadi.</t>
+  </si>
+  <si>
+    <t>ChildLife Essentials Vitamin Zinc Plus — 6 oylikdan o‘smirlik yoshigacha bo‘lgan bolalar uchun maxsus ishlab chiqilgan suyuq oziq-ovqat qo‘shimchasi. Mahsulot tarkibida optimal o‘zlashtirilishi uchun glyukonat shaklidagi rux va mis mavjud. Immun tizimini qo‘llab-quvvatlaydi, normal o‘sish, rivojlanish va kognitiv funksiyalarni ta’minlashga yordam beradi. Misning qo‘shilishi mineral muvozanatni saqlash uchun zarur, chunki ruxning yuqori dozalari uning o‘zlashtirilishiga to‘sqinlik qilishi mumkin.</t>
+  </si>
+  <si>
+    <t>ChildLife Essentials Vitamin Iron — bolalar uchun maxsus ishlab chiqilgan temir moddasi saqlovchi mashhur suyuq oziq-ovqat qo‘shimchasi. Mahsulot tarkibida yaxshi o‘zlashtiriladigan va bolaning oshqozoniga yumshoq ta’sir qiluvchi xelatli bisglitsin shaklidagi temir mavjud. Gemoglobin darajasini qo‘llab-quvvatlaydi, sog‘lom qon hosil bo‘lishiga va hujayralarni kislorod bilan ta’minlashga yordam beradi.</t>
+  </si>
+  <si>
+    <t>ChildLife Essentials Vitamin Calcium with Magnesium — bolalarda suyaklar va tishlarning sog‘lom o‘sishini qo‘llab-quvvatlash uchun ishlab chiqilgan, suyuq shakldagi kompleks biologik faol qo‘shimcha. U birgalikda yaxshiroq o‘zlashtiriladigan minerallar va vitaminlarning muvozanatli kombinatsiyasini o‘z ichiga oladi. Faol o‘sish davrlarida mustahkam suyak to‘qimasi va sog‘lom tishlarning shakllanishini qo‘llab-quvvatlaydi. Tarkibidagi magniy tinch uyquga va bolalardagi asabiylikni kamaytirishga yordam beradi.</t>
+  </si>
+  <si>
+    <t>ChildLife Essentials Multi Vitamin &amp; Mineral oson o‘zlashtiriladigan shaklda 12 ta asosiy vitamin va muhim minerallarning muvozanatli majmuasini o‘z ichiga oladi. Tarkibida immunitetni, suyaklarning o‘sishi va miya rivojlanishini qo‘llab-quvvatlash uchun vitaminlar, minerallar va qo‘shimcha oziq moddalar mavjud.</t>
+  </si>
+  <si>
+    <t>ChildLife Essentials Vitamin Echinacea — chaqaloqlar va bolalarda immunitetni mustahkamlash uchun maxsus ishlab chiqilgan, tomchi shaklidagi tabiiy biologik faol qo‘shimcha. Yoqimli tabiiy apelsin ta’miga ega (shirin apelsin efir moyi hisobiga), bu bolalarga uni qabul qilishni osonlashtiradi.</t>
+  </si>
+  <si>
+    <t>“Kuniga ikki kapsula”, Two-Per-Day Capsules, Life Extension — asosiy vitaminlar, minerallar va mikroelementlarni o‘z ichiga olgan kompleks, yuqori konsentratsiyali qo‘shimcha. Bu tabiiy beta-karotin va tabiiy E vitamini saqlovchi kuchli antioksidant formuladir. Shuningdek, mahsulot bioo‘zlashtirilishi yuqori bo‘lgan kalsiy va magniyning muhim manbai hisoblanadi. Oziq moddalarining yetarli miqdori va to‘g‘ri muvozanati salomatlikni mustahkamlash, ovqat hazm qilishni yaxshilash va to‘qimalarning tiklanishiga yordam beradi. Har bir ingredient uning o‘zlashtirilish qobiliyati, boshqa moddalar bilan o‘zaro ta’siri, allergenlik ehtimoli va uzoq muddatli xavfsizligi hisobga olingan holda tanlangan.</t>
+  </si>
+  <si>
+    <t>Life Extension Two-Per-Day Multivitamin — muhim oziq moddalarining kunlik ehtiyojini to‘ldirish uchun ishlab chiqilgan, kapsula shaklidagi kompleks multivitamin mahsulot. Bir qadoqda 120 ta kapsula mavjud bo‘lib, bu ikki oylik qabul qilish uchun mo‘ljallangan. Formula bioo‘zlashtirilishi yuqori bo‘lgan shakldagi vitaminlar, minerallar va qo‘shimcha o‘simlik komponentlarini o‘z ichiga oladi. Mahsulot ingredientlarning sinergiyasiga, ya’ni oziq moddalarining birgalikda ishlashi va bir-birini to‘ldirishiga alohida e’tibor qaratilgan holda ishlab chiqilgan.</t>
+  </si>
+  <si>
+    <t>Life Extension BioActive B-Complex — organizmni yuqori yuklama sharoitida qo‘llab-quvvatlash uchun ishlab chiqilgan innovatsion B guruhi vitaminlari kompleksi. Mahsulot organizm tomonidan qo‘shimcha o‘zgarishlarsiz bevosita o‘zlashtiriladigan bioaktiv vitamin shakllarini o‘z ichiga oladi. Kompleks vegetarianlar uchun mos bo‘lib, GMO, sun’iy qo‘shimchalar va boshqa keraksiz komponentlarni o‘z ichiga olmaydi.</t>
+  </si>
+  <si>
+    <t>Life Extension Magnesium L-Threonate — tropik ta’mga ega kukun shaklidagi noyob oziq-ovqat qo‘shimchasi. Mahsulot tabiiy magniy manbalarini izlaydigan, faol hayot tarzini olib boradigan yoki yuqori stressni boshdan kechiradigan insonlar uchun mo‘ljallangan. Kognitiv salomatlikni qo‘llab-quvvatlash va xotirani yaxshilashga yordam beradi. Magniy L-treonat xotira, diqqat va konsentratsiyani qo‘llab-quvvatlaydi. Ushbu magniy shakli miya plastisiyasiga ijobiy ta’sir ko‘rsatib, neyron tarmoqlarining rivojlanishi va tiklanishiga yordam beradi.</t>
+  </si>
+  <si>
+    <t>Life Extension Neuro-Mag — asab tizimi va kognitiv jarayonlarni qo‘llab-quvvatlashga yo‘naltirilgan, magniyning L-treonat shakliga asoslangan maxsus formula. Magniy ko‘plab fiziologik jarayonlarda, jumladan, asab tizimi faoliyati va energiya almashinuvida ishtirok etadigan muhim mineraldir. Magniy L-treonatning o‘ziga xosligi uning miya metabolizmi bilan bog‘liq jarayonlarda ishtirok etishidadir. Neuro-Mag formulasi barqaror aqliy faoliyat, diqqatni jamlash va kognitiv barqarorlik muhim bo‘lgan insonlar uchun mo‘ljallangan.</t>
+  </si>
+  <si>
+    <t>Life Extension Inositol — har bir kapsulasida 1000 mg mio-inozitol saqlovchi yuqori sifatli qo‘shimcha. Inozitol (B8 vitamini) hujayra membranalari tarkibida mavjud bo‘lib, to‘g‘ri hujayra signalizatsiyasini, xususan, insulin ajralishiga sog‘lom javob reaksiyasini qo‘llab-quvvatlaydi. Shuningdek, glyukoza almashinuvini qo‘llab-quvvatlashga yordam beradi. Inozitol polikistik tuxumdonlar sindromi (PCOS) bilan bog‘liq holatlarda va hayz sikli hamda reproduktiv funksiyani qo‘llab-quvvatlashda qo‘llanadi, shuningdek, folatlar bilan birgalikda ishlaydi.</t>
+  </si>
+  <si>
+    <t>Life Extension Super Selenium Complex — organizmni oksidlovchi zararlanishdan himoya qilishda muhim rol o‘ynaydigan selen kompleksidir. Selen organizmdagi kuchli antioksidant fermentlardan biri — glutation peroksidazaning normal faoliyati uchun zarur. Shuningdek, sog‘lom odamlarda qalqonsimon bez va immun tizimining normal ishlashini qo‘llab-quvvatlaydi. Selen sog‘lom hujayra bo‘linishi uchun ham muhim oziq modda hisoblanadi. Uning sog‘lom yallig‘lanish reaksiyasini qo‘llab-quvvatlash va erkin radikallarni zararsizlantirish xususiyatlari yurak va miya salomatligi bilan bog‘liq holda o‘rganilmoqda.</t>
+  </si>
+  <si>
+    <t>Nature's Answer Liquid Magnesium, Malate and Glycinate — suyuq shakldagi magniy qo‘shimchasi bo‘lib, tarkibida magniy malat va magniy glitsinati mavjud. Magniy energiya ishlab chiqarishni qo‘llab-quvvatlaydi, suyaklar va yurak-qon tomir tizimining normal faoliyatiga yordam beradi. Magniyning tabiiy manbalariga to‘q yashil bargli sabzavotlar, dukkaklilar, yong‘oqlar va tozalanmagan butun don mahsulotlari kiradi. Magniy malat va magniy glitsinati organizm uchun nisbatan yumshoq shakllar bo‘lib, aminokislotalar bilan xelatlangan birikmalar hisoblanadi.</t>
+  </si>
+  <si>
+    <t>Nature's Answer Liquid Vitamin C — immun tizimini qo‘llab-quvvatlash, hayotiy energiyani oshirish va organizmni oksidlovchi stressdan himoya qilish uchun mo‘ljallangan yuqori samarali suyuq oziq-ovqat qo‘shimchasi. Suyuq shakldagi vitamin C oson o‘zlashtiriladi. U immunitetni qo‘llab-quvvatlashga, charchoqni kamaytirishga, organizmning tiklanish jarayonini qo‘llab-quvvatlashga va hujayralarni erkin radikallardan himoya qilishga yordam beradi.</t>
+  </si>
+  <si>
+    <t>Nature's Answer mandarin ta’miga ega suyuq B guruhi vitaminlari kompleksi — C vitamini, niatsin va folatga boy multivitaminlar aralashmasidir. U antioksidant xususiyatlarga ega. Nature's Answer 1972-yildan beri sog‘lom turmush tarzini qo‘llab-quvvatlash uchun yuqori sifatli mahsulotlar ishlab chiqarib keladi.</t>
+  </si>
+  <si>
+    <t>Nature's Answer Liquid Chlorophyll — barcha o‘simliklarda mavjud bo‘lgan va o‘simliklarga quyosh nuridan oziqa olishda yordam beradigan yashil pigmentdir. Xlorofill juda to‘yimli bo‘lib, sog‘liq uchun foydali ko‘plab tabiiy komponentlarni o‘z ichiga oladi. U umumiy energiya darajasini qo‘llab-quvvatlashga, nafasni yangilashga va tanadagi tabiiy hidlarni neytrallashga yordam beradi. Shuningdek, sog‘lom teri va yaltiroq sochlarni qo‘llab-quvvatlaydi hamda organizmning umumiy salomatligi uchun zarur mikroelementlarni o‘z ichiga oladi. Sog‘lom tozalanish va detoksikatsiya jarayonlarini qo‘llab-quvvatlash uchun ishlatiladi.</t>
+  </si>
+  <si>
+    <t>Solaray Magnesium Citrate 400 mg — magniy sitrat shaklidagi, yaxshi o‘zlashtiriladigan magniyni o‘z ichiga olgan yuqori sifatli biologik faol qo‘shimcha. Mahsulot asab tizimi, mushaklar faoliyati, suyaklar va yurak-qon tomir tizimini kundalik qo‘llab-quvvatlash uchun ishlab chiqilgan. Tarkibida shuningdek o‘simlik komponentlari — beda, petrushka, kress-salat va momaqaymoq ildizi mavjud. Muntazam qabul qilish asab tizimining normal faoliyatini qo‘llab-quvvatlash, charchoqni kamaytirish, mushaklar salomatligini saqlash va mushak spazmlari xavfini kamaytirish, suyak va tishlarni qo‘llab-quvvatlash, yurakning normal faoliyatini ta’minlash hamda uyqu sifatini yaxshilashga yordam beradi.</t>
+  </si>
+  <si>
+    <t>Solaray Magnesium Citrate 400 mg — magniyning bioo‘zlashtirilishi va yaxshi so‘rilishi yuqori bo‘lgan shakllaridan biri — sitrat ko‘rinishidagi magniyni o‘z ichiga olgan yuqori sifatli biologik faol qo‘shimcha. Formula qo‘shimcha ravishda beda, petrushka, kress-salat va momaqaymoq ildizi kabi o‘simlik komponentlarini o‘z ichiga oladi. Magniy organizmdagi 300 dan ortiq biokimyoviy reaksiyalarda ishtirok etadi. U nerv impulslarini uzatish, mushaklarning qisqarishi, energiya ishlab chiqarish, oqsil sintezi, yurak ritmining me’yorida bo‘lishi va suyak to‘qimasi salomatligini saqlash uchun zarur.</t>
+  </si>
+  <si>
+    <t>Solaray Zinc Citrate 50 mg — ruxning yaxshi o‘zlashtiriladigan shakllaridan biri bo‘lgan sitrat ko‘rinishidagi ruxni o‘z ichiga olgan yuqori sifatli biologik faol qo‘shimcha. Tarkibida rux va boshqa foydali fitonutrientlarning tabiiy manbai bo‘lgan qovoq urug‘lari ham mavjud. Rux organizmdagi 300 dan ortiq fermentativ reaksiyalarda ishtirok etadi. Ruxni muntazam qabul qilish immun tizimining normal faoliyatini qo‘llab-quvvatlash, hujayralarni oksidlovchi stressdan himoya qilish, teri, soch va tirnoqlar salomatligini saqlash, to‘qimalarning tiklanishini qo‘llab-quvvatlash hamda ta’m va hid bilish qobiliyatining normal faoliyatini saqlashga yordam beradi.</t>
+  </si>
+  <si>
+    <t>Solaray Magnesium Glycinate 350 mg — magniyning bisglitsin shakliga asoslangan, oson o‘zlashtiriladigan va oshqozon-ichak tizimiga yumshoq ta’sir qiluvchi yuqori sifatli biologik faol qo‘shimcha. Formulaning o‘ziga xosligi magniyning glitsin aminokislotasi bilan bog‘langan shaklda bo‘lishidadir. Glitsin tinchlantiruvchi xususiyatlarga ega bo‘lgani sababli, magniy bisglitsinati stress, yuqori asabiy yuklama, uyqu muammolari yoki mushaklar tarangligini boshdan kechiradigan insonlar orasida mashhur. Tarkibida oziq moddalarining yaxshiroq o‘zlashtirilishiga yordam beruvchi BioPerine (qora murch ekstrakti) ham mavjud.</t>
+  </si>
+  <si>
+    <t>Solaray Magnesium Glycinate 350 mg — magniyning bisglitsin shakliga ega, oson o‘zlashtiriladigan va oshqozon-ichak tizimiga yumshoq ta’sir qiluvchi yuqori sifatli biologik faol qo‘shimcha. Glitsin tinchlantiruvchi xususiyatlarga ega bo‘lgani sababli, magniy bisglitsinati stress, yuqori asabiy yuklama, uyqu muammolari yoki mushaklar tarangligini boshdan kechiradigan insonlar orasida mashhur. Tarkibida oziq moddalarining yaxshiroq o‘zlashtirilishiga yordam beruvchi BioPerine (qora murch ekstrakti) mavjud.</t>
+  </si>
+  <si>
+    <t>Solaray Vitamin D3 + K2 — suyaklar, tishlar, yurak-qon tomir tizimi va immunitet salomatligini qo‘llab-quvvatlash uchun D3 vitamini (xolekalsiferol) va K2 vitamini (menaxinon-7, MK-7) ni birlashtirgan yuqori sifatli biologik faol qo‘shimcha. Formula D3 vitaminining kalsiyning samarali o‘zlashtirilishiga yordam berishi, K2 vitaminining esa kalsiyning suyak to‘qimasiga yo‘naltirilishini qo‘llab-quvvatlashi uchun ishlab chiqilgan.</t>
+  </si>
+  <si>
+    <t>Solaray Vitamin D3 + K2 — D3 vitamini (xolekalsiferol) va K2 vitaminini (menaxinon-7, MK-7) birlashtirgan yuqori sifatli biologik faol qo‘shimcha. D3 vitamini D vitaminining yaxshi o‘zlashtiriladigan shakli bo‘lib, immun tizimi, mushaklar faoliyati va suyaklar salomatligini qo‘llab-quvvatlashda muhim rol o‘ynaydi. Nohatdan olingan K2 vitamini (MK-7) kalsiyning suyak to‘qimasi bilan bog‘lanishida ishtirok etuvchi osteokalsin oqsilining faollashuviga yordam beradi.</t>
+  </si>
+  <si>
+    <t>Solaray Selenium 200 mcg — selenning L-selenometionin shaklini o‘z ichiga olgan, yuqori bioo‘zlashtirilishi va yaxshi so‘rilishi bilan ajralib turadigan yuqori sifatli biologik faol qo‘shimcha. Ushbu mikroelement hujayralarni antioksidant himoya qilish, immun tizimi faoliyati va qalqonsimon bezning normal ishlashini qo‘llab-quvvatlashda ishtirok etadigan selenoproteinlar tarkibiga kiradi. Selen E vitamini bilan birgalikda ta’sir qilib, organizmning antioksidant himoyasini kuchaytirishga yordam beradi.</t>
+  </si>
+  <si>
+    <t>Solaray Vital Extracts Artichoke — artishok barglari ekstraktini (Cynara scolymus) o‘z ichiga olgan yuqori sifatli biologik faol qo‘shimcha bo‘lib, tarkibida 5% kofeoyl kislotalari hosilalari mavjudligi kafolatlangan. Artishok qadimdan Yevropa an’anaviy fitoterapiyasida jigar va ovqat hazm qilish tizimi salomatligini qo‘llab-quvvatlash uchun ishlatilgan. O‘simlikning asosiy biologik faol moddalari — tsinarin, kofeoylxinna kislotalari va tabiiy antioksidantlar bo‘lib, ular o‘tning normal ishlab chiqarilishi va oqimini qo‘llab-quvvatlashga yordam beradi.</t>
+  </si>
+  <si>
+    <t>Solaray 1:1 Ratio L-Lysine Monolaurin — L-lizin va monolaurinni 1:1 nisbatda birlashtirgan yuqori sifatli biologik faol qo‘shimcha bo‘lib, immun tizimini kompleks qo‘llab-quvvatlash uchun ishlab chiqilgan. L-lizin — oqsil sintezi, kollagen hosil bo‘lishi, teri, bog‘lamlar va suyaklar salomatligini qo‘llab-quvvatlashda ishtirok etadigan muhim aminokislotadir. Monolaurin esa kokos moyidagi laurin kislotasidan olinadigan tabiiy birikma bo‘lib, organizmning tabiiy himoya funksiyalarini qo‘llab-quvvatlash va mikroflora muvozanatini saqlashga yordam beradi.</t>
+  </si>
+  <si>
+    <t>Solaray Chromium Picolinate 200 mcg — xromning yaxshi o‘zlashtiriladigan shakllaridan biri bo‘lgan pikolinat ko‘rinishidagi xromni o‘z ichiga olgan yuqori sifatli biologik faol qo‘shimcha. Xrom uglevodlar, yog‘lar va oqsillar almashinuvida ishtirok etadi, glyukozaning normal metabolizmini va hujayralarning insulinga sezgirligini qo‘llab-quvvatlashga yordam beradi. Muntazam qabul qilish muvozanatli ovqatlanish sharoitida uglevodlar almashinuvi, qondagi glyukozaning me’yoriy darajasi va energiya almashinuvini qo‘llab-quvvatlashga, shuningdek, shirinlikka bo‘lgan ishtiyoqni kamaytirishga yordam beradi.</t>
+  </si>
+  <si>
+    <t>Solaray Vital Extracts Berberine &amp; Curcumin — hind zirk daraxti ildizidan olingan berberin va mikronizatsiyalangan kurkuma ekstraktini birlashtirgan yuqori sifatli biologik faol qo‘shimcha. Ushbu kombinatsiya moddalar almashinuvi, ovqat hazm qilish tizimi, jigar salomatligi va organizmning antioksidant himoyasini kompleks qo‘llab-quvvatlash uchun mo‘ljallangan. Berberin uglevodlar va lipidlarning normal almashinuvini qo‘llab-quvvatlashga yordam beradi. Kurkuma tarkibidagi kurkuminoidlar deb ataluvchi tabiiy polifenollar antioksidant xususiyatlari bilan mashhur.</t>
+  </si>
+  <si>
+    <t>Life-flo Liquid Iodine Plus — kaliy yodid shaklidagi yodni o‘z ichiga olgan, suyuq ko‘rinishdagi yuqori sifatli biologik faol qo‘shimcha. Mahsulot organizmning yodga bo‘lgan kunlik ehtiyojini to‘ldirish va qalqonsimon bezning normal faoliyatini qo‘llab-quvvatlash uchun ishlab chiqilgan. Suyuq shakli foydalanish uchun qulay bo‘lib, suv bilan oson aralashtiriladi va tomizgich yordamida aniq dozalash imkonini beradi. Yod qalqonsimon bez gormonlari — tiroksin (T4) va triyodtironin (T3) sintezi uchun zarur bo‘lib, ular moddalar almashinuvini tartibga soladi, energiya ishlab chiqarishda ishtirok etadi hamda asab va yurak-qon tomir tizimlarining normal faoliyatini qo‘llab-quvvatlaydi.</t>
+  </si>
+  <si>
+    <t>Biotin — organizmning normal o‘sishi va faoliyati uchun zarur bo‘lgan, suvda eriydigan vitamin. Soch to‘kilishi, soch va tirnoqlarning o‘sishi buzilganda qo‘llaniladi. Biotin organizmda glyukoza sintezi, insulin ishlab chiqarish, asab hujayralari va ter bezlarining normal faoliyati uchun zarur. Shuningdek, biotin immun tizimining normal ishlashini qo‘llab-quvvatlaydi va teri salomatligini saqlashda muhim rol o‘ynaydi.</t>
+  </si>
+  <si>
+    <t>Omega-3 yog‘ kislotalari — EPA (EYK) va DHA (DHA) ni iste’mol qilish yurak ishemik kasalligi rivojlanish xavfini kamaytirishga yordam berishi mumkin. Omega-3 yog‘ kislotalari yurak va qon tomirlari, immun tizimi, ko‘rish qobiliyati hamda kognitiv funksiyalarni qo‘llab-quvvatlash uchun muhim.</t>
+  </si>
+  <si>
+    <t>Omega-3 yog‘ kislotalari — EPA (EYK) va DHA ni iste’mol qilish yurak ishemik kasalligi rivojlanish xavfini kamaytirishga yordam berishi mumkin. Omega-3 yurak va qon tomirlari, immun tizimi, ko‘rish qobiliyati hamda kognitiv funksiyalarni qo‘llab-quvvatlash uchun muhim.</t>
+  </si>
+  <si>
+    <t>Zamonaviy hayot tarzi har kuni yuqori darajada diqqat, energiya va samaradorlikni talab qiladi. O‘qish, ish va doimiy axborot oqimi vaqt o‘tishi bilan organizm va asab tizimini charchatishi mumkin. Ushbu noyob tabiiy qo‘ziqorin miya, xotira va asab tizimini qo‘llab-quvvatlashdagi foydali xususiyatlari bilan mashhur. U xotira va diqqatni qo‘llab-quvvatlash, ma’lumotni yaxshiroq o‘zlashtirishga yordam berish, charchoq va ortiqcha yuklama hissini kamaytirish, “boshdagi tuman” hissiga qarshi kurashish hamda stress paytida asab tizimini qo‘llab-quvvatlashga yordam beradi. Shuningdek, samaradorlik va fikrlash ravshanligini qo‘llab-quvvatlaydi. Ayniqsa, talabalar va maktab o‘quvchilari, tadbirkorlar, ofis xodimlari hamda yuqori aqliy yuklama bilan ishlaydigan insonlar uchun tavsiya etiladi.</t>
+  </si>
+  <si>
+    <t>ECOVITA Coenzyme Q10 100 MG — organizmning energiya darajasini, yurak faoliyatini va umumiy tonusini qo‘llab-quvvatlash uchun mo‘ljallangan koenzim Q10 manbai. Zamonaviy hayot tarzi, stress, charchoq va doimiy yuklamalar organizmning energiya zaxirasiga ta’sir qilishi mumkin. Koenzim Q10 hujayralarda energiya ishlab chiqarish jarayonida ishtirok etib, organizmning faol ishlashini va umumiy energiya almashinuvini qo‘llab-quvvatlashga yordam beradi.</t>
+  </si>
+  <si>
+    <t>Kalsiy va magniy organizmning asab, mushak va qon aylanish tizimlarining normal faoliyati uchun zarur. Shuningdek, ular organizmdagi suyuqlik muvozanatini saqlashga yordam beradi. Kalsiy va magniy suyak tizimining shakllanishi va uning mustahkamligini saqlashda ham muhim rol o‘ynaydi.</t>
+  </si>
+  <si>
+    <t>ECOVITA Calcium Citrate — organizmni har kuni qo‘llab-quvvatlash va kalsiy yetishmovchiligini to‘ldirish uchun mo‘ljallangan, oson o‘zlashtiriladigan kalsiy sitrat shaklidagi qo‘shimcha. Kalsiy mustahkam suyaklar va tishlar, mushaklar hamda asab tizimining normal faoliyati uchun muhim. Ayniqsa, ratsionida kalsiy yetishmaydigan insonlar, ayollar, sportchilar va 30 yoshdan oshganlar uchun tavsiya etiladi.</t>
+  </si>
+  <si>
+    <t>ECOVITA Magnesium Citrate + Vitamin B6 — oson o‘zlashtiriladigan magniy sitrati va B6 vitaminini birlashtirgan, organizmni har kuni qo‘llab-quvvatlash uchun mo‘ljallangan samarali kompleks. Doimiy stress, charchoq, uyqusizlik va yuqori yuklamalar organizmda magniy yetishmovchiligiga olib kelishi mumkin. Magniy asab tizimi, mushaklar va umumiy holatni qo‘llab-quvvatlashda muhim rol o‘ynaydi. Kompleks asab tizimini qo‘llab-quvvatlash, charchoq va taranglikni kamaytirish, bo‘shashish va xotirjamlikka yordam berish, mushaklar va yurak faoliyatini qo‘llab-quvvatlash hamda uyqu sifatini yaxshilashga yordam beradi. B6 vitamini magniyning o‘zlashtirilishini yaxshilashga ko‘maklashadi.</t>
+  </si>
+  <si>
+    <t>D3 va K2 vitaminlari suyaklar, tishlar hamda yurak-qon tomir tizimi salomatligini qo‘llab-quvvatlashda muhim bo‘lgan ikki oziq moddasini birlashtiradi. Vitamin D3 organizmda kalsiyning tashilishi va o‘zlashtirilishiga yordam beradi. Vitamin K esa tomirlar tuzilmalarida kalsiyning normal almashinuvini qo‘llab-quvvatlab, arteriyalar salomatligini saqlashda muhim rol o‘ynaydi.</t>
+  </si>
+  <si>
+    <t>Ko‘rsatmalar va foydasi: immun tizimini mustahkamlashni qo‘llab-quvvatlaydi, raxitning oldini olishga yordam beradi, suyaklar va mushaklarni mustahkamlashga ko‘maklashadi, yuqori xavf guruhidagi insonlarda D3 vitamini yetishmovchiligining oldini olishga yordam beradi. Shuningdek, osteomalyatsiya va raxitni davolashda, gipoparatireozda hamda osteoporozni qo‘llab-quvvatlovchi terapiya sifatida qo‘llanadi.</t>
+  </si>
+  <si>
+    <t>Ko‘rsatmalar va foydasi: immun tizimini mustahkamlash, raxitning oldini olish, suyaklar va mushaklarni mustahkamlash, yuqori xavf guruhidagi insonlarda D3 vitamini yetishmovchiligining oldini olish, osteomalyatsiya va raxitni davolash, gipoparatireozda qo‘llash hamda osteoporozda qo‘llab-quvvatlash uchun ishlatiladi.</t>
+  </si>
+  <si>
+    <t>Ushbu mahsulot tarkibida inozitolning eng boy shakli hisoblangan mio-inozitol ishlatiladi. Inozitol barcha hujayralar membranalarida, ayniqsa bosh miya va markaziy asab tizimi hujayralarida mavjud bo‘lib, neyromediatorlar signallarini uzatishda muhim rol o‘ynaydi. Shuningdek, inozitol insulinning to‘g‘ri ishlashi, uglevodlar almashinuvi hamda hujayra darajasida kalsiy muvozanatini saqlash uchun muhim ahamiyatga ega.</t>
+  </si>
+  <si>
+    <t>Selen aritmiya, yurak ishemik kasalligi, gipertoniya, ateroskleroz hamda miokard infarktidan keyingi tiklanish davrida muhim ahamiyatga ega. Selen yog‘lar almashinuvi va qondagi xolesterin miqdorini me’yorlashtirishga, qon tomirlari va yurak mushagini shikastlanishdan himoya qilishga hamda gipertoniya rivojlanish ehtimolini kamaytirishga yordam beradi. Selenning organizmdagi asosiy vazifasi antioksidant tizimlar faoliyatida va qalqonsimon bez gormonlari almashinuvida ishtirok etishdan iborat.</t>
+  </si>
+  <si>
+    <t>Letsitin qon hosil bo‘lish jarayonini qo‘llab-quvvatlaydi, organizmning turli infeksiyalar, viruslar va bakteriyalarga qarshi tabiiy himoya kuchini oshirishga yordam beradi hamda turli toksik moddalar ta’siridan himoya qilishda ko‘maklashadi. Shuningdek, qondagi xolesterin miqdorini kamaytirish orqali aterosklerozning oldini olishga, yurak xuruji va insultlar xavfini kamaytirishga yordam berishi mumkin.</t>
+  </si>
+  <si>
+    <t>Rux organizmning normal o‘sishi va hujayralarning bo‘linishi, to‘qimalarning tiklanishi, teri, soch va tirnoqlar salomatligini saqlash, asab, immun va reproduktiv tizimlarning normal faoliyati uchun zarur. Shuningdek, rux hid bilish, ta’mni sezish va ko‘rish qobiliyatini qo‘llab-quvvatlashda muhim rol o‘ynaydi.</t>
+  </si>
+  <si>
+    <t>Vitamin C — immun tizimining normal faoliyatini qo‘llab-quvvatlashda muhim rol o‘ynaydigan, suvda eriydigan oziq moddasidir. Vitamin C biriktiruvchi to‘qimalarning tarkibiy oqsili bo‘lgan kollagen ishlab chiqarish uchun ham zarur bo‘lib, shu sababli teri, suyaklar va bo‘g‘imlar salomatligi uchun muhim hisoblanadi. Ushbu formula tarkibiga askorbin kislotaning tabiiy manbai bo‘lgan na’matak ham qo‘shilgan.</t>
+  </si>
+  <si>
+    <t>Kollagen peptidlari suyaklar, bo‘g‘imlar va teri salomatligini qo‘llab-quvvatlashdagi foydali xususiyatlari bilan mashhur. Kollagen sutemizuvchilar organizmidagi eng ko‘p uchraydigan oqsil bo‘lib, tanadagi umumiy oqsilning taxminan 30 foizini tashkil qiladi. Tadqiqotlar gidrolizlangan kollagen mustahkam suyaklar va sog‘lom bo‘g‘imlarni qo‘llab-quvvatlashi, shuningdek terining silliq va namlangan bo‘lishiga yordam berishi mumkinligini ko‘rsatadi.</t>
+  </si>
+  <si>
+    <t>ECOVITA Type 1–3 Collagen — tarkibida organizmda eng ko‘p uchraydigan I va III turdagi gidrolizlangan kollagen mavjud bo‘lgan biologik faol qo‘shimcha. Ushbu kollagen turlari teri, soch, tirnoqlar, suyaklar, bog‘lamlar va biriktiruvchi to‘qimalarning asosiy tarkibiy oqsillari hisoblanadi. Gidrolizlangan kollagen kichik hajmdagi kollagen peptidlaridan iborat bo‘lib, shu sababli organizm tomonidan osonroq o‘zlashtiriladi. Yosh o‘tishi bilan organizmning tabiiy kollagen ishlab chiqarishi asta-sekin kamayadi, bu esa teri, soch, tirnoqlar va biriktiruvchi to‘qimalarning holatiga ta’sir qilishi mumkin.</t>
+  </si>
+  <si>
+    <t>Erkak organizmini har kuni qo‘llab-quvvatlash. Zamonaviy hayot tarzi, stress, ish, sport va doimiy yuklamalar erkak organizmidan katta miqdorda energiya va resurslarni talab qiladi. Har kuni faol, samarali va o‘ziga ishongan holda bo‘lish uchun organizmga vitamin va minerallarning to‘liq majmuasi zarur. ECOVITA erkaklar uchun multivitaminlari — energiya, immunitet va erkaklar umumiy salomatligini qo‘llab-quvvatlashga mo‘ljallangan muvozanatli vitamin va minerallar kompleksidir. Ayniqsa faol hayot tarzini olib boradigan, yuqori jismoniy va aqliy yuklamalarga ega bo‘lgan erkaklar hamda sportchilar uchun tavsiya etiladi.</t>
+  </si>
+  <si>
+    <t>Go‘zallik, energiya va har kuni o‘ziga g‘amxo‘rlik. Ayol organizmi har kuni stress, turli yuklamalar, uyqu yetishmasligi va tezkor hayot ritmiga duch keladi. Energiya, yaxshi kayfiyat va tabiiy go‘zallikni saqlash uchun organizmga vitamin va minerallarning to‘liq majmuasi zarur. ECOVITA ayollar uchun multivitaminlari — ayollar salomatligi, energiyasi va ichki muvozanatini qo‘llab-quvvatlash uchun mo‘ljallangan muvozanatli vitamin va minerallar kompleksidir. Ayniqsa faol hayot tarzini olib boradigan, charchoq va energiya yetishmovchiligini his qiladigan ayollar uchun tavsiya etiladi.</t>
+  </si>
+  <si>
+    <t>Energiya, faollik va mashg‘ulotlar vaqtida qo‘llab-quvvatlash. Faol hayot tarzi, sport va doimiy jismoniy yuklamalar organizmdan katta miqdorda energiya talab qiladi. L-karnitin organizmga yog‘larni energiyaga aylantirish jarayonida ishtirok etishga va jismoniy faollikni qo‘llab-quvvatlashga yordam beradi. ECOVITA L-Carnitine — energiya, chidamlilik va faol hayot tarzini qo‘llab-quvvatlash uchun qulay formula. Ayniqsa sportchilar, faol hayot tarzini olib boradigan insonlar, jismoniy yuklamalar, mashg‘ulotlar va kardio mashqlar vaqtida tavsiya etiladi.</t>
+  </si>
+  <si>
+    <t>Moddalar almashinuvi va organizm muvozanatini qo‘llab-quvvatlash. Zamonaviy hayot tarzi, stress, tartibsiz ovqatlanish va jismoniy faollikning yetishmasligi moddalar almashinuvi hamda umumiy holatga ta’sir qilishi mumkin. Shu sababli tobora ko‘proq insonlar metabolizm va organizmning ichki muvozanatini qo‘llab-quvvatlashi bilan mashhur bo‘lgan tabiiy komponent — berberinni tanlamoqda. ECOVITA Berberine 500 MG — organizmni har kuni qo‘llab-quvvatlash va faol hayot tarzini olib borish uchun qulay formula. Ayniqsa ovqatlanishiga e’tibor beradigan, faol hayot tarzini olib boradigan, yuqori jismoniy yoki aqliy yuklamalarga ega bo‘lgan hamda stressni boshdan kechiradigan insonlar uchun tavsiya etiladi.</t>
+  </si>
+  <si>
+    <t>Bo‘g‘imlar, bog‘lamlar va faol harakatni qo‘llab-quvvatlash. Faol hayot tarzi, sport, jismoniy yuklamalar va yoshga bog‘liq o‘zgarishlar bo‘g‘imlar hamda bog‘lamlarga qo‘shimcha yuk tushishiga olib kelishi mumkin. Shu sababli harakatlanish qulayligi va bo‘g‘imlar harakatchanligini saqlash uchun organizmga kompleks qo‘llab-quvvatlash zarur. ECOVITA Glucosamine + Chondroitin + MSM — bo‘g‘imlar, tog‘ay va biriktiruvchi to‘qimalarni har kuni qo‘llab-quvvatlash uchun mo‘ljallangan kuchli formula. Ayniqsa sportchilar, faol hayot tarzini olib boradigan insonlar, jismoniy yuklamalari yuqori bo‘lganlar va 30 yoshdan oshganlar uchun tavsiya etiladi.</t>
+  </si>
+  <si>
+    <t>Energiya, asab tizimi va kundalik faollikni qo‘llab-quvvatlash. Stress, charchoq, uyqu yetishmasligi va hayotning yuqori sur’ati organizmni holdan toydirib, energiya darajasini pasaytirishi mumkin. B guruhi vitaminlari asab tizimi, mehnat qobiliyati va umumiy holatni qo‘llab-quvvatlashda muhim rol o‘ynaydi. ECOVITA B guruhi vitaminlari kompleksi — energiya, diqqatni jamlash va organizmning ichki muvozanatini har kuni qo‘llab-quvvatlash uchun mo‘ljallangan muvozanatli formula. Ayniqsa yuqori aqliy va jismoniy yuklamalarda, stress va charchoq paytida, talabalar hamda ofis xodimlari uchun tavsiya etiladi.</t>
+  </si>
+  <si>
+    <t>Energiya, kuch va kundalik holatni qo‘llab-quvvatlash. Temir organizm uchun eng muhim minerallardan biri bo‘lib, kislorod tashilishi, energiya va umumiy tetiklikni qo‘llab-quvvatlashda ishtirok etadi. Temir yetishmovchiligi charchoq, holsizlik va ish qobiliyatining pasayishi bilan kechishi mumkin. ECOVITA Temir xelati — yaxshi o‘zlashtiriladigan va organizmga yumshoq ta’sir qiluvchi zamonaviy temir shaklidir. Ayniqsa tez-tez charchaydigan, faol hayot tarzini olib boradigan insonlar va ayollar uchun tavsiya etiladi.</t>
+  </si>
+  <si>
+    <t>Organizmni har kuni qo‘llab-quvvatlash uchun muhim vosita. Foliy kislotasi umumiy salomatlik, energiya va organizmning normal faoliyatini qo‘llab-quvvatlash uchun zarur bo‘lgan B guruhi vitaminlaridan biridir. ECOVITA Foliy kislotasi 400 mkg — organizmni har kuni qo‘llab-quvvatlash va faol hayot tarzini olib borish uchun B9 vitaminining qulay manbai. Ayniqsa ayollar, faol hayot tarzini olib boradigan, yuqori aqliy va jismoniy yuklamalarga ega bo‘lgan hamda muvozanatsiz ovqatlanadigan insonlar uchun tavsiya etiladi.</t>
+  </si>
+  <si>
+    <t>Moddalar almashinuvi va ishtahani nazorat qilishni qo‘llab-quvvatlash. Zamonaviy hayot sur’ati, tartibsiz ovqatlanish va doimiy tamaddi qilish moddalar almashinuvi hamda umumiy holatga ta’sir qilishi mumkin. Xrom organizmdagi moddalar almashinuvi jarayonlarida ishtirok etadigan va energiya muvozanatini qo‘llab-quvvatlaydigan muhim mikroelement hisoblanadi. Ayniqsa ovqatlanishiga e’tibor beradigan, faol hayot tarzini olib boradigan va shirinlikka bo‘lgan ishtiyoqini kamaytirishni istaydigan insonlar uchun tavsiya etiladi.</t>
+  </si>
+  <si>
+    <t>Vita Garden Biotin 5000 mcg — soch, teri va tirnoqlar salomatligini qo‘llab-quvvatlash uchun mo‘ljallangan, biotin (B7 vitamini)ning yuqori dozasi saqlangan oziq-ovqat qo‘shimchasidir. Biotin moddalar almashinuvi jarayonlarida muhim rol o‘ynab, organizmga oqsillar, yog‘lar va uglevodlarni energiyaga aylantirishga yordam beradi. Biotin ko‘pincha «go‘zallik vitamini» deb ataladi, chunki u sochlarning normal holatini saqlashga, tirnoq plastinkasini mustahkamlashga va teri salomatligini qo‘llab-quvvatlashga yordam beradi. Bundan tashqari, B7 vitamini soch va tirnoqlarning asosiy tarkibiy oqsili bo‘lgan keratin sintezida ishtirok etadi.</t>
+  </si>
+  <si>
+    <t>Vita Garden Omega-3 Fish Oil — tozalangan baliq yog‘idan olingan, organizm uchun zarur bo‘lgan Omega-3 yog‘ kislotalarining yuqori konsentratsiyali kompleksidir. Mahsulot tarkibida Omega-3 ning eng qimmatli ikki turi — EPA (eikozapentaen kislota) va DHA (dokozageksaen kislota) optimal nisbatda mavjud bo‘lib, ular yurak-qon tomir tizimi, bosh miya va ko‘rish organlari salomatligini qo‘llab-quvvatlash uchun zarur. Inson organizmi Omega-3 yog‘ kislotalarini yetarli miqdorda mustaqil ravishda ishlab chiqara olmaydi.</t>
+  </si>
+  <si>
+    <t>Vita Garden Magnesium B6 — magniy yetishmovchiligini to‘ldirish hamda asab, mushak va yurak-qon tomir tizimlarini qo‘llab-quvvatlash uchun ishlab chiqilgan biologik faol qo‘shimcha. Kompleks tarkibida sitrat shaklidagi magniy va organizm tomonidan magniyning yaxshiroq o‘zlashtirilishiga yordam beruvchi B6 vitamini mavjud. Magniy 300 dan ortiq biokimyoviy jarayonlarda ishtirok etadi, nerv impulslarining normal uzatilishi, mushaklarning qisqarishi, yurak ritmini saqlash, oqsil sintezi va energiya ishlab chiqarish uchun zarur.</t>
+  </si>
+  <si>
+    <t>Vita Garden Calcium Citrate — tarkibida kalsiy sitrati shaklidagi kalsiy mavjud bo‘lgan biologik faol qo‘shimcha bo‘lib, bu mineralning eng oson o‘zlashtiriladigan shakllaridan biridir. Kalsiy sitrati organizm tomonidan, shu jumladan, oshqozon kislotaliligi pasaygan holatlarda ham yaxshi o‘zlashtiriladi. Kalsiyning qariyb 99 foizi suyaklar va tishlarda joylashgan bo‘lib, ularning mustahkamligi va zichligini ta’minlaydi, qolgan qismi esa mushaklar, asab tizimi va yurak faoliyatida, shuningdek, qon ivishi jarayonlarida ishtirok etadi.</t>
+  </si>
+  <si>
+    <t>Vita Garden Vitamin D3 2000 ME — tarkibida D3 vitamini (xolekalsiferol) mavjud bo‘lgan biologik faol qo‘shimcha bo‘lib, u D vitaminining eng yuqori darajada o‘zlashtiriladigan va tabiiy shaklidir. D3 vitamini immun tizimini, suyaklar, tishlar va mushaklar salomatligini hamda umumiy farovonlikni ta’minlashda muhim rol o‘ynaydi. D vitamini «quyosh vitamini» deb ataladi, chunki u quyosh nurlari ta’sirida terida hosil bo‘ladi. Biroq quyoshda yetarlicha bo‘lmaslik, quyoshdan himoyalovchi vositalardan foydalanish, ovqatlanish xususiyatlari va yil fasli sababli ko‘plab insonlarda ushbu vitamin yetishmovchiligi kuzatiladi.</t>
+  </si>
+  <si>
+    <t>Vita Garden MYO-Inositol 500 mg — tarkibida inozitolning eng keng tarqalgan va biologik faol shakli bo‘lgan mio-inozitol mavjud bo‘lgan biologik faol qo‘shimcha. Mio-inozitol hujayralar o‘rtasidagi signallar uzatilishida muhim rol o‘ynaydi, asab tizimi faoliyatida ishtirok etadi, uglevod almashinuvini qo‘llab-quvvatlaydi va hujayralarning insulinga normal sezgirligini ta’minlashga yordam beradi. Shuningdek, u ayollar va erkaklarda gormonal muvozanat hamda reproduktiv funksiyani tartibga solishda ishtirok etadi.</t>
+  </si>
+  <si>
+    <t>Vita Garden Selenium 100 mcg — tarkibida 100 mkg selen mavjud bo‘lgan biologik faol qo‘shimcha bo‘lib, selen hayotiy muhim mikroelement hisoblanadi. Selen 20 dan ortiq selenoproteinlar tarkibiga kiradi va ular hujayralarni antioksidant himoya qilish, immun tizimi, qalqonsimon bez faoliyati hamda reproduktiv funksiyada ishtirok etadi. Selen kuchli tabiiy antioksidant bo‘lib, organizm hujayralarini erkin radikallar va oksidlovchi stress ta’siridan himoya qilishga yordam beradi.</t>
+  </si>
+  <si>
+    <t>Vita Garden Zinc Picolinate — tarkibida ruxning eng yaxshi o‘zlashtiriladigan shakllaridan biri bo‘lgan pikolinat shaklidagi rux mavjud bo‘lgan biologik faol qo‘shimcha. Rux pikolinati yuqori biokirishuvchanligi bilan ajralib turadi. Rux organizmdagi 300 dan ortiq fermentativ reaksiyalarda ishtirok etadi. U immun tizimini qo‘llab-quvvatlash, moddalar almashinuvi, oqsil va DNK sintezida muhim rol o‘ynaydi, shuningdek, to‘qimalarning normal o‘sishi va tiklanishiga yordam beradi.</t>
+  </si>
+  <si>
+    <t>5-gidroksitriptofan (triptofan aminokislotasi va serotonin o‘rtasidagi oraliq metabolit) Afrika qit’asida o‘sadigan griffoniya (Griffonia simplicifolia) o‘simligining urug‘laridan olinadi. 5-gidroksitriptofan (5-HTP) — oqsillar tarkibiga kiruvchi tabiiy aminokislota. U organizmda «baxt gormoni» deb ataladigan serotoninni ishlab chiqarish uchun zarur bo‘lgan eng muhim komponentlardan biridir. 5-HTP ning eng mashhur ta’sirlaridan biri — kayfiyatni me’yorlashtirishdir. Serotonin bo‘shashish va xotirjamlik hissini uyg‘otadi, xavotir darajasini kamaytiradi va kayfiyatni barqarorlashtiradi.</t>
   </si>
 </sst>
 </file>
@@ -6832,7 +7252,9 @@
       <c r="N14" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="O14" s="14"/>
+      <c r="O14" t="s">
+        <v>1610</v>
+      </c>
       <c r="P14" s="12" t="s">
         <v>197</v>
       </c>
@@ -6893,7 +7315,9 @@
       <c r="N15" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="O15" s="14"/>
+      <c r="O15" t="s">
+        <v>1611</v>
+      </c>
       <c r="P15" s="12" t="s">
         <v>207</v>
       </c>
@@ -6958,7 +7382,9 @@
       <c r="N16" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="O16" s="14"/>
+      <c r="O16" t="s">
+        <v>1612</v>
+      </c>
       <c r="P16" s="12" t="s">
         <v>217</v>
       </c>
@@ -7023,7 +7449,9 @@
       <c r="N17" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="O17" s="14"/>
+      <c r="O17" t="s">
+        <v>1613</v>
+      </c>
       <c r="P17" s="12" t="s">
         <v>227</v>
       </c>
@@ -7090,7 +7518,9 @@
       <c r="N18" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="O18" s="14"/>
+      <c r="O18" t="s">
+        <v>1614</v>
+      </c>
       <c r="P18" s="12" t="s">
         <v>237</v>
       </c>
@@ -7157,7 +7587,9 @@
       <c r="N19" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="O19" s="14"/>
+      <c r="O19" t="s">
+        <v>1615</v>
+      </c>
       <c r="P19" s="12" t="s">
         <v>247</v>
       </c>
@@ -7222,7 +7654,9 @@
       <c r="N20" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="O20" s="14"/>
+      <c r="O20" t="s">
+        <v>1616</v>
+      </c>
       <c r="P20" s="12" t="s">
         <v>256</v>
       </c>
@@ -7287,7 +7721,9 @@
       <c r="N21" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="O21" s="14"/>
+      <c r="O21" t="s">
+        <v>1616</v>
+      </c>
       <c r="P21" s="12" t="s">
         <v>264</v>
       </c>
@@ -7352,7 +7788,9 @@
       <c r="N22" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="O22" s="14"/>
+      <c r="O22" t="s">
+        <v>1616</v>
+      </c>
       <c r="P22" s="12" t="s">
         <v>272</v>
       </c>
@@ -7417,7 +7855,9 @@
       <c r="N23" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="O23" s="14"/>
+      <c r="O23" t="s">
+        <v>1616</v>
+      </c>
       <c r="P23" s="12" t="s">
         <v>283</v>
       </c>
@@ -7484,7 +7924,9 @@
       <c r="N24" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="O24" s="14"/>
+      <c r="O24" t="s">
+        <v>1617</v>
+      </c>
       <c r="P24" s="12" t="s">
         <v>294</v>
       </c>
@@ -7551,7 +7993,9 @@
       <c r="N25" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="O25" s="14"/>
+      <c r="O25" t="s">
+        <v>1618</v>
+      </c>
       <c r="P25" s="12" t="s">
         <v>303</v>
       </c>
@@ -7614,7 +8058,9 @@
       <c r="N26" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="O26" s="14"/>
+      <c r="O26" t="s">
+        <v>1619</v>
+      </c>
       <c r="P26" s="12" t="s">
         <v>313</v>
       </c>
@@ -7681,7 +8127,9 @@
       <c r="N27" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="O27" s="14"/>
+      <c r="O27" t="s">
+        <v>1620</v>
+      </c>
       <c r="P27" s="12" t="s">
         <v>323</v>
       </c>
@@ -7748,7 +8196,9 @@
       <c r="N28" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="O28" s="14"/>
+      <c r="O28" t="s">
+        <v>1621</v>
+      </c>
       <c r="P28" s="12" t="s">
         <v>331</v>
       </c>
@@ -7815,7 +8265,9 @@
       <c r="N29" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="O29" s="14"/>
+      <c r="O29" t="s">
+        <v>1622</v>
+      </c>
       <c r="P29" s="12" t="s">
         <v>340</v>
       </c>
@@ -7876,7 +8328,9 @@
       <c r="N30" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="O30" s="14"/>
+      <c r="O30" t="s">
+        <v>1623</v>
+      </c>
       <c r="P30" s="12" t="s">
         <v>351</v>
       </c>
@@ -7943,7 +8397,9 @@
       <c r="N31" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="O31" s="14"/>
+      <c r="O31" t="s">
+        <v>1624</v>
+      </c>
       <c r="P31" s="12" t="s">
         <v>362</v>
       </c>
@@ -8010,7 +8466,9 @@
       <c r="N32" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="O32" s="14"/>
+      <c r="O32" t="s">
+        <v>1625</v>
+      </c>
       <c r="P32" s="12" t="s">
         <v>372</v>
       </c>
@@ -8075,7 +8533,9 @@
       <c r="N33" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="O33" s="14"/>
+      <c r="O33" t="s">
+        <v>1626</v>
+      </c>
       <c r="P33" s="12" t="s">
         <v>381</v>
       </c>
@@ -8140,7 +8600,9 @@
       <c r="N34" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="O34" s="14"/>
+      <c r="O34" t="s">
+        <v>1626</v>
+      </c>
       <c r="P34" s="12" t="s">
         <v>390</v>
       </c>
@@ -8205,7 +8667,9 @@
       <c r="N35" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="O35" s="14"/>
+      <c r="O35" t="s">
+        <v>1627</v>
+      </c>
       <c r="P35" s="12" t="s">
         <v>398</v>
       </c>
@@ -8266,7 +8730,9 @@
       <c r="N36" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="O36" s="14"/>
+      <c r="O36" t="s">
+        <v>1628</v>
+      </c>
       <c r="P36" s="12" t="s">
         <v>408</v>
       </c>
@@ -8333,7 +8799,9 @@
       <c r="N37" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="O37" s="14"/>
+      <c r="O37" t="s">
+        <v>1629</v>
+      </c>
       <c r="P37" s="12" t="s">
         <v>416</v>
       </c>
@@ -8400,7 +8868,9 @@
       <c r="N38" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="O38" s="14"/>
+      <c r="O38" t="s">
+        <v>1630</v>
+      </c>
       <c r="P38" s="12" t="s">
         <v>426</v>
       </c>
@@ -8467,7 +8937,9 @@
       <c r="N39" s="12" t="s">
         <v>434</v>
       </c>
-      <c r="O39" s="14"/>
+      <c r="O39" t="s">
+        <v>1631</v>
+      </c>
       <c r="P39" s="12" t="s">
         <v>435</v>
       </c>
@@ -8534,7 +9006,9 @@
       <c r="N40" s="12" t="s">
         <v>444</v>
       </c>
-      <c r="O40" s="14"/>
+      <c r="O40" t="s">
+        <v>1632</v>
+      </c>
       <c r="P40" s="12" t="s">
         <v>445</v>
       </c>
@@ -8599,7 +9073,9 @@
       <c r="N41" s="12" t="s">
         <v>453</v>
       </c>
-      <c r="O41" s="14"/>
+      <c r="O41" t="s">
+        <v>1633</v>
+      </c>
       <c r="P41" s="12" t="s">
         <v>454</v>
       </c>
@@ -8666,7 +9142,9 @@
       <c r="N42" s="12" t="s">
         <v>462</v>
       </c>
-      <c r="O42" s="14"/>
+      <c r="O42" t="s">
+        <v>1634</v>
+      </c>
       <c r="P42" s="12" t="s">
         <v>463</v>
       </c>
@@ -8733,7 +9211,9 @@
       <c r="N43" s="12" t="s">
         <v>472</v>
       </c>
-      <c r="O43" s="14"/>
+      <c r="O43" t="s">
+        <v>1635</v>
+      </c>
       <c r="P43" s="12" t="s">
         <v>473</v>
       </c>
@@ -8796,7 +9276,9 @@
       <c r="N44" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="O44" s="14"/>
+      <c r="O44" t="s">
+        <v>1636</v>
+      </c>
       <c r="P44" s="12" t="s">
         <v>482</v>
       </c>
@@ -8863,7 +9345,9 @@
       <c r="N45" s="12" t="s">
         <v>491</v>
       </c>
-      <c r="O45" s="14"/>
+      <c r="O45" t="s">
+        <v>1637</v>
+      </c>
       <c r="P45" s="12" t="s">
         <v>492</v>
       </c>
@@ -8930,7 +9414,9 @@
       <c r="N46" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="O46" s="14"/>
+      <c r="O46" t="s">
+        <v>1638</v>
+      </c>
       <c r="P46" s="12" t="s">
         <v>502</v>
       </c>
@@ -8997,7 +9483,9 @@
       <c r="N47" s="12" t="s">
         <v>511</v>
       </c>
-      <c r="O47" s="14"/>
+      <c r="O47" t="s">
+        <v>1639</v>
+      </c>
       <c r="P47" s="12" t="s">
         <v>512</v>
       </c>
@@ -9062,7 +9550,9 @@
       <c r="N48" s="12" t="s">
         <v>521</v>
       </c>
-      <c r="O48" s="14"/>
+      <c r="O48" t="s">
+        <v>1640</v>
+      </c>
       <c r="P48" s="12" t="s">
         <v>522</v>
       </c>
@@ -9129,7 +9619,9 @@
       <c r="N49" s="12" t="s">
         <v>530</v>
       </c>
-      <c r="O49" s="14"/>
+      <c r="O49" t="s">
+        <v>1641</v>
+      </c>
       <c r="P49" s="12" t="s">
         <v>531</v>
       </c>
@@ -9192,7 +9684,9 @@
       <c r="N50" s="12" t="s">
         <v>540</v>
       </c>
-      <c r="O50" s="14"/>
+      <c r="O50" t="s">
+        <v>1642</v>
+      </c>
       <c r="P50" s="12" t="s">
         <v>541</v>
       </c>
@@ -9257,7 +9751,9 @@
       <c r="N51" s="12" t="s">
         <v>549</v>
       </c>
-      <c r="O51" s="14"/>
+      <c r="O51" t="s">
+        <v>1643</v>
+      </c>
       <c r="P51" s="12" t="s">
         <v>550</v>
       </c>
@@ -9322,7 +9818,9 @@
       <c r="N52" s="12" t="s">
         <v>558</v>
       </c>
-      <c r="O52" s="14"/>
+      <c r="O52" t="s">
+        <v>1644</v>
+      </c>
       <c r="P52" s="12" t="s">
         <v>559</v>
       </c>
@@ -9387,7 +9885,9 @@
       <c r="N53" s="12" t="s">
         <v>566</v>
       </c>
-      <c r="O53" s="14"/>
+      <c r="O53" t="s">
+        <v>1645</v>
+      </c>
       <c r="P53" s="12" t="s">
         <v>567</v>
       </c>
@@ -9452,7 +9952,9 @@
       <c r="N54" s="12" t="s">
         <v>574</v>
       </c>
-      <c r="O54" s="14"/>
+      <c r="O54" t="s">
+        <v>1646</v>
+      </c>
       <c r="P54" s="12" t="s">
         <v>575</v>
       </c>
@@ -9519,7 +10021,9 @@
       <c r="N55" s="12" t="s">
         <v>583</v>
       </c>
-      <c r="O55" s="14"/>
+      <c r="O55" t="s">
+        <v>1749</v>
+      </c>
       <c r="P55" s="12" t="s">
         <v>584</v>
       </c>
@@ -9586,7 +10090,9 @@
       <c r="N56" s="12" t="s">
         <v>593</v>
       </c>
-      <c r="O56" s="14"/>
+      <c r="O56" t="s">
+        <v>1647</v>
+      </c>
       <c r="P56" s="12" t="s">
         <v>594</v>
       </c>
@@ -9653,7 +10159,9 @@
       <c r="N57" s="12" t="s">
         <v>602</v>
       </c>
-      <c r="O57" s="14"/>
+      <c r="O57" t="s">
+        <v>1648</v>
+      </c>
       <c r="P57" s="12" t="s">
         <v>603</v>
       </c>
@@ -9720,7 +10228,9 @@
       <c r="N58" s="12" t="s">
         <v>611</v>
       </c>
-      <c r="O58" s="14"/>
+      <c r="O58" t="s">
+        <v>1649</v>
+      </c>
       <c r="P58" s="12" t="s">
         <v>612</v>
       </c>
@@ -9787,7 +10297,9 @@
       <c r="N59" s="12" t="s">
         <v>620</v>
       </c>
-      <c r="O59" s="14"/>
+      <c r="O59" t="s">
+        <v>1650</v>
+      </c>
       <c r="P59" s="12" t="s">
         <v>621</v>
       </c>
@@ -9852,7 +10364,9 @@
       <c r="N60" s="12" t="s">
         <v>629</v>
       </c>
-      <c r="O60" s="14"/>
+      <c r="O60" t="s">
+        <v>1651</v>
+      </c>
       <c r="P60" s="12" t="s">
         <v>630</v>
       </c>
@@ -9919,7 +10433,9 @@
       <c r="N61" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="O61" s="14"/>
+      <c r="O61" t="s">
+        <v>1652</v>
+      </c>
       <c r="P61" s="12" t="s">
         <v>638</v>
       </c>
@@ -9984,7 +10500,9 @@
       <c r="N62" s="12" t="s">
         <v>646</v>
       </c>
-      <c r="O62" s="14"/>
+      <c r="O62" t="s">
+        <v>1653</v>
+      </c>
       <c r="P62" s="12" t="s">
         <v>647</v>
       </c>
@@ -10047,7 +10565,9 @@
       <c r="N63" s="12" t="s">
         <v>659</v>
       </c>
-      <c r="O63" s="14"/>
+      <c r="O63" t="s">
+        <v>1654</v>
+      </c>
       <c r="P63" s="12" t="s">
         <v>660</v>
       </c>
@@ -10110,7 +10630,9 @@
       <c r="N64" s="12" t="s">
         <v>669</v>
       </c>
-      <c r="O64" s="14"/>
+      <c r="O64" t="s">
+        <v>1655</v>
+      </c>
       <c r="P64" s="12" t="s">
         <v>670</v>
       </c>
@@ -10173,7 +10695,9 @@
       <c r="N65" s="12" t="s">
         <v>679</v>
       </c>
-      <c r="O65" s="14"/>
+      <c r="O65" t="s">
+        <v>1656</v>
+      </c>
       <c r="P65" s="12" t="s">
         <v>680</v>
       </c>
@@ -10240,7 +10764,9 @@
       <c r="N66" s="12" t="s">
         <v>689</v>
       </c>
-      <c r="O66" s="14"/>
+      <c r="O66" t="s">
+        <v>1657</v>
+      </c>
       <c r="P66" s="12" t="s">
         <v>690</v>
       </c>
@@ -10301,7 +10827,9 @@
       <c r="N67" s="12" t="s">
         <v>699</v>
       </c>
-      <c r="O67" s="14"/>
+      <c r="O67" t="s">
+        <v>1658</v>
+      </c>
       <c r="P67" s="12" t="s">
         <v>700</v>
       </c>
@@ -10362,7 +10890,9 @@
       <c r="N68" s="12" t="s">
         <v>709</v>
       </c>
-      <c r="O68" s="14"/>
+      <c r="O68" t="s">
+        <v>1659</v>
+      </c>
       <c r="P68" s="12" t="s">
         <v>710</v>
       </c>
@@ -10423,7 +10953,9 @@
       <c r="N69" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="O69" s="14"/>
+      <c r="O69" t="s">
+        <v>1660</v>
+      </c>
       <c r="P69" s="12" t="s">
         <v>719</v>
       </c>
@@ -10490,7 +11022,9 @@
       <c r="N70" s="12" t="s">
         <v>729</v>
       </c>
-      <c r="O70" s="14"/>
+      <c r="O70" t="s">
+        <v>1661</v>
+      </c>
       <c r="P70" s="12" t="s">
         <v>730</v>
       </c>
@@ -10555,7 +11089,9 @@
       <c r="N71" s="12" t="s">
         <v>739</v>
       </c>
-      <c r="O71" s="14"/>
+      <c r="O71" t="s">
+        <v>1662</v>
+      </c>
       <c r="P71" s="12" t="s">
         <v>740</v>
       </c>
@@ -10618,7 +11154,9 @@
       <c r="N72" s="12" t="s">
         <v>749</v>
       </c>
-      <c r="O72" s="14"/>
+      <c r="O72" t="s">
+        <v>1663</v>
+      </c>
       <c r="P72" s="12" t="s">
         <v>750</v>
       </c>
@@ -10685,7 +11223,9 @@
       <c r="N73" s="12" t="s">
         <v>761</v>
       </c>
-      <c r="O73" s="14"/>
+      <c r="O73" t="s">
+        <v>1664</v>
+      </c>
       <c r="P73" s="12" t="s">
         <v>762</v>
       </c>
@@ -10752,7 +11292,9 @@
       <c r="N74" s="12" t="s">
         <v>771</v>
       </c>
-      <c r="O74" s="14"/>
+      <c r="O74" t="s">
+        <v>1665</v>
+      </c>
       <c r="P74" s="12" t="s">
         <v>772</v>
       </c>
@@ -10815,7 +11357,9 @@
       <c r="N75" s="12" t="s">
         <v>779</v>
       </c>
-      <c r="O75" s="14"/>
+      <c r="O75" t="s">
+        <v>1666</v>
+      </c>
       <c r="P75" s="12" t="s">
         <v>780</v>
       </c>
@@ -10878,7 +11422,9 @@
       <c r="N76" s="12" t="s">
         <v>789</v>
       </c>
-      <c r="O76" s="14"/>
+      <c r="O76" t="s">
+        <v>1667</v>
+      </c>
       <c r="P76" s="12" t="s">
         <v>780</v>
       </c>
@@ -10945,7 +11491,9 @@
       <c r="N77" s="12" t="s">
         <v>799</v>
       </c>
-      <c r="O77" s="14"/>
+      <c r="O77" t="s">
+        <v>1668</v>
+      </c>
       <c r="P77" s="12" t="s">
         <v>800</v>
       </c>
@@ -11012,7 +11560,9 @@
       <c r="N78" s="12" t="s">
         <v>809</v>
       </c>
-      <c r="O78" s="14"/>
+      <c r="O78" t="s">
+        <v>1669</v>
+      </c>
       <c r="P78" s="12" t="s">
         <v>810</v>
       </c>
@@ -11079,7 +11629,9 @@
       <c r="N79" s="12" t="s">
         <v>819</v>
       </c>
-      <c r="O79" s="14"/>
+      <c r="O79" t="s">
+        <v>1670</v>
+      </c>
       <c r="P79" s="12" t="s">
         <v>820</v>
       </c>
@@ -11142,7 +11694,9 @@
       <c r="N80" s="12" t="s">
         <v>829</v>
       </c>
-      <c r="O80" s="14"/>
+      <c r="O80" t="s">
+        <v>1671</v>
+      </c>
       <c r="P80" s="12" t="s">
         <v>830</v>
       </c>
@@ -11205,7 +11759,9 @@
       <c r="N81" s="12" t="s">
         <v>839</v>
       </c>
-      <c r="O81" s="14"/>
+      <c r="O81" t="s">
+        <v>1672</v>
+      </c>
       <c r="P81" s="12" t="s">
         <v>840</v>
       </c>
@@ -11268,7 +11824,9 @@
       <c r="N82" s="12" t="s">
         <v>849</v>
       </c>
-      <c r="O82" s="14"/>
+      <c r="O82" t="s">
+        <v>1673</v>
+      </c>
       <c r="P82" s="12" t="s">
         <v>850</v>
       </c>
@@ -11331,7 +11889,9 @@
       <c r="N83" s="12" t="s">
         <v>859</v>
       </c>
-      <c r="O83" s="14"/>
+      <c r="O83" t="s">
+        <v>1674</v>
+      </c>
       <c r="P83" s="12" t="s">
         <v>860</v>
       </c>
@@ -11394,7 +11954,9 @@
       <c r="N84" s="12" t="s">
         <v>869</v>
       </c>
-      <c r="O84" s="14"/>
+      <c r="O84" t="s">
+        <v>1675</v>
+      </c>
       <c r="P84" s="12" t="s">
         <v>870</v>
       </c>
@@ -11461,7 +12023,9 @@
       <c r="N85" s="12" t="s">
         <v>879</v>
       </c>
-      <c r="O85" s="14"/>
+      <c r="O85" t="s">
+        <v>1676</v>
+      </c>
       <c r="P85" s="12" t="s">
         <v>880</v>
       </c>
@@ -11524,7 +12088,9 @@
       <c r="N86" s="12" t="s">
         <v>889</v>
       </c>
-      <c r="O86" s="14"/>
+      <c r="O86" t="s">
+        <v>1677</v>
+      </c>
       <c r="P86" s="12" t="s">
         <v>890</v>
       </c>
@@ -11587,7 +12153,9 @@
       <c r="N87" s="12" t="s">
         <v>899</v>
       </c>
-      <c r="O87" s="14"/>
+      <c r="O87" t="s">
+        <v>1678</v>
+      </c>
       <c r="P87" s="12" t="s">
         <v>900</v>
       </c>
@@ -11650,7 +12218,9 @@
       <c r="N88" s="12" t="s">
         <v>909</v>
       </c>
-      <c r="O88" s="14"/>
+      <c r="O88" t="s">
+        <v>1679</v>
+      </c>
       <c r="P88" s="12" t="s">
         <v>910</v>
       </c>
@@ -11713,7 +12283,9 @@
       <c r="N89" s="12" t="s">
         <v>919</v>
       </c>
-      <c r="O89" s="14"/>
+      <c r="O89" t="s">
+        <v>1680</v>
+      </c>
       <c r="P89" s="12" t="s">
         <v>920</v>
       </c>
@@ -11776,7 +12348,9 @@
       <c r="N90" s="12" t="s">
         <v>928</v>
       </c>
-      <c r="O90" s="14"/>
+      <c r="O90" t="s">
+        <v>1681</v>
+      </c>
       <c r="P90" s="12" t="s">
         <v>929</v>
       </c>
@@ -11839,7 +12413,9 @@
       <c r="N91" s="12" t="s">
         <v>938</v>
       </c>
-      <c r="O91" s="14"/>
+      <c r="O91" t="s">
+        <v>1682</v>
+      </c>
       <c r="P91" s="12" t="s">
         <v>939</v>
       </c>
@@ -11902,7 +12478,9 @@
       <c r="N92" s="12" t="s">
         <v>949</v>
       </c>
-      <c r="O92" s="14"/>
+      <c r="O92" t="s">
+        <v>1683</v>
+      </c>
       <c r="P92" s="12" t="s">
         <v>950</v>
       </c>
@@ -11965,7 +12543,9 @@
       <c r="N93" s="12" t="s">
         <v>959</v>
       </c>
-      <c r="O93" s="14"/>
+      <c r="O93" t="s">
+        <v>1684</v>
+      </c>
       <c r="P93" s="12" t="s">
         <v>960</v>
       </c>
@@ -12028,7 +12608,9 @@
       <c r="N94" s="12" t="s">
         <v>968</v>
       </c>
-      <c r="O94" s="14"/>
+      <c r="O94" t="s">
+        <v>1685</v>
+      </c>
       <c r="P94" s="12" t="s">
         <v>969</v>
       </c>
@@ -12091,7 +12673,9 @@
       <c r="N95" s="12" t="s">
         <v>977</v>
       </c>
-      <c r="O95" s="14"/>
+      <c r="O95" t="s">
+        <v>1686</v>
+      </c>
       <c r="P95" s="12" t="s">
         <v>978</v>
       </c>
@@ -12154,7 +12738,9 @@
       <c r="N96" s="12" t="s">
         <v>987</v>
       </c>
-      <c r="O96" s="14"/>
+      <c r="O96" t="s">
+        <v>1687</v>
+      </c>
       <c r="P96" s="12" t="s">
         <v>988</v>
       </c>
@@ -12217,7 +12803,9 @@
       <c r="N97" s="12" t="s">
         <v>996</v>
       </c>
-      <c r="O97" s="14"/>
+      <c r="O97" t="s">
+        <v>1688</v>
+      </c>
       <c r="P97" s="12" t="s">
         <v>997</v>
       </c>
@@ -12280,7 +12868,9 @@
       <c r="N98" s="12" t="s">
         <v>1004</v>
       </c>
-      <c r="O98" s="14"/>
+      <c r="O98" t="s">
+        <v>1689</v>
+      </c>
       <c r="P98" s="12" t="s">
         <v>1005</v>
       </c>
@@ -12343,7 +12933,9 @@
       <c r="N99" s="12" t="s">
         <v>1014</v>
       </c>
-      <c r="O99" s="14"/>
+      <c r="O99" t="s">
+        <v>1690</v>
+      </c>
       <c r="P99" s="12" t="s">
         <v>1015</v>
       </c>
@@ -12406,7 +12998,9 @@
       <c r="N100" s="12" t="s">
         <v>1024</v>
       </c>
-      <c r="O100" s="14"/>
+      <c r="O100" t="s">
+        <v>1691</v>
+      </c>
       <c r="P100" s="12" t="s">
         <v>1025</v>
       </c>
@@ -12467,7 +13061,9 @@
       <c r="N101" s="12" t="s">
         <v>1033</v>
       </c>
-      <c r="O101" s="14"/>
+      <c r="O101" t="s">
+        <v>1692</v>
+      </c>
       <c r="P101" s="12" t="s">
         <v>1034</v>
       </c>
@@ -12530,7 +13126,9 @@
       <c r="N102" s="12" t="s">
         <v>1043</v>
       </c>
-      <c r="O102" s="14"/>
+      <c r="O102" t="s">
+        <v>1693</v>
+      </c>
       <c r="P102" s="12" t="s">
         <v>1044</v>
       </c>
@@ -12593,7 +13191,9 @@
       <c r="N103" s="12" t="s">
         <v>1053</v>
       </c>
-      <c r="O103" s="14"/>
+      <c r="O103" t="s">
+        <v>1694</v>
+      </c>
       <c r="P103" s="12" t="s">
         <v>1054</v>
       </c>
@@ -12658,7 +13258,9 @@
       <c r="N104" s="12" t="s">
         <v>1063</v>
       </c>
-      <c r="O104" s="14"/>
+      <c r="O104" t="s">
+        <v>1695</v>
+      </c>
       <c r="P104" s="12" t="s">
         <v>1064</v>
       </c>
@@ -12721,7 +13323,9 @@
       <c r="N105" s="12" t="s">
         <v>1073</v>
       </c>
-      <c r="O105" s="14"/>
+      <c r="O105" t="s">
+        <v>1696</v>
+      </c>
       <c r="P105" s="12" t="s">
         <v>1074</v>
       </c>
@@ -12782,7 +13386,9 @@
       <c r="N106" s="12" t="s">
         <v>1084</v>
       </c>
-      <c r="O106" s="14"/>
+      <c r="O106" t="s">
+        <v>1697</v>
+      </c>
       <c r="P106" s="12" t="s">
         <v>1085</v>
       </c>
@@ -12845,7 +13451,9 @@
       <c r="N107" s="12" t="s">
         <v>1094</v>
       </c>
-      <c r="O107" s="14"/>
+      <c r="O107" t="s">
+        <v>1698</v>
+      </c>
       <c r="P107" s="12" t="s">
         <v>1095</v>
       </c>
@@ -12906,7 +13514,9 @@
       <c r="N108" s="12" t="s">
         <v>1104</v>
       </c>
-      <c r="O108" s="14"/>
+      <c r="O108" t="s">
+        <v>1699</v>
+      </c>
       <c r="P108" s="12" t="s">
         <v>1105</v>
       </c>
@@ -12967,7 +13577,9 @@
       <c r="N109" s="12" t="s">
         <v>1114</v>
       </c>
-      <c r="O109" s="14"/>
+      <c r="O109" t="s">
+        <v>1700</v>
+      </c>
       <c r="P109" s="12" t="s">
         <v>1115</v>
       </c>
@@ -13032,7 +13644,9 @@
       <c r="N110" s="12" t="s">
         <v>1125</v>
       </c>
-      <c r="O110" s="14"/>
+      <c r="O110" t="s">
+        <v>1701</v>
+      </c>
       <c r="P110" s="12" t="s">
         <v>1126</v>
       </c>
@@ -13097,7 +13711,9 @@
       <c r="N111" s="12" t="s">
         <v>1135</v>
       </c>
-      <c r="O111" s="14"/>
+      <c r="O111" t="s">
+        <v>1702</v>
+      </c>
       <c r="P111" s="12" t="s">
         <v>1136</v>
       </c>
@@ -13164,7 +13780,9 @@
       <c r="N112" s="12" t="s">
         <v>1144</v>
       </c>
-      <c r="O112" s="14"/>
+      <c r="O112" t="s">
+        <v>1703</v>
+      </c>
       <c r="P112" s="12" t="s">
         <v>1145</v>
       </c>
@@ -13231,7 +13849,9 @@
       <c r="N113" s="12" t="s">
         <v>1154</v>
       </c>
-      <c r="O113" s="14"/>
+      <c r="O113" t="s">
+        <v>1704</v>
+      </c>
       <c r="P113" s="12" t="s">
         <v>1155</v>
       </c>
@@ -13298,7 +13918,9 @@
       <c r="N114" s="12" t="s">
         <v>1164</v>
       </c>
-      <c r="O114" s="14"/>
+      <c r="O114" t="s">
+        <v>1705</v>
+      </c>
       <c r="P114" s="12" t="s">
         <v>1155</v>
       </c>
@@ -13365,7 +13987,9 @@
       <c r="N115" s="12" t="s">
         <v>1172</v>
       </c>
-      <c r="O115" s="14"/>
+      <c r="O115" t="s">
+        <v>1706</v>
+      </c>
       <c r="P115" s="12" t="s">
         <v>1173</v>
       </c>
@@ -13432,7 +14056,9 @@
       <c r="N116" s="12" t="s">
         <v>1182</v>
       </c>
-      <c r="O116" s="14"/>
+      <c r="O116" t="s">
+        <v>1707</v>
+      </c>
       <c r="P116" s="12" t="s">
         <v>1173</v>
       </c>
@@ -13499,7 +14125,9 @@
       <c r="N117" s="12" t="s">
         <v>1191</v>
       </c>
-      <c r="O117" s="14"/>
+      <c r="O117" t="s">
+        <v>1708</v>
+      </c>
       <c r="P117" s="12" t="s">
         <v>1192</v>
       </c>
@@ -13566,7 +14194,9 @@
       <c r="N118" s="12" t="s">
         <v>1201</v>
       </c>
-      <c r="O118" s="14"/>
+      <c r="O118" t="s">
+        <v>1709</v>
+      </c>
       <c r="P118" s="12" t="s">
         <v>1202</v>
       </c>
@@ -13633,7 +14263,9 @@
       <c r="N119" s="12" t="s">
         <v>1211</v>
       </c>
-      <c r="O119" s="14"/>
+      <c r="O119" t="s">
+        <v>1710</v>
+      </c>
       <c r="P119" s="12" t="s">
         <v>1212</v>
       </c>
@@ -13698,7 +14330,9 @@
       <c r="N120" s="12" t="s">
         <v>1221</v>
       </c>
-      <c r="O120" s="14"/>
+      <c r="O120" t="s">
+        <v>1711</v>
+      </c>
       <c r="P120" s="12" t="s">
         <v>1222</v>
       </c>
@@ -13765,7 +14399,9 @@
       <c r="N121" s="12" t="s">
         <v>1231</v>
       </c>
-      <c r="O121" s="14"/>
+      <c r="O121" t="s">
+        <v>1712</v>
+      </c>
       <c r="P121" s="12" t="s">
         <v>1232</v>
       </c>
@@ -13830,7 +14466,9 @@
       <c r="N122" s="12" t="s">
         <v>1241</v>
       </c>
-      <c r="O122" s="14"/>
+      <c r="O122" t="s">
+        <v>1713</v>
+      </c>
       <c r="P122" s="12" t="s">
         <v>1242</v>
       </c>
@@ -13897,7 +14535,9 @@
       <c r="N123" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="O123" s="14"/>
+      <c r="O123" t="s">
+        <v>1714</v>
+      </c>
       <c r="P123" s="12" t="s">
         <v>1252</v>
       </c>
@@ -13960,7 +14600,9 @@
       <c r="N124" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O124" s="14"/>
+      <c r="O124" t="s">
+        <v>1715</v>
+      </c>
       <c r="P124" s="12" t="s">
         <v>1259</v>
       </c>
@@ -14023,7 +14665,9 @@
       <c r="N125" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O125" s="14"/>
+      <c r="O125" t="s">
+        <v>1716</v>
+      </c>
       <c r="P125" s="12" t="s">
         <v>1266</v>
       </c>
@@ -14084,7 +14728,9 @@
       <c r="N126" s="12" t="s">
         <v>1273</v>
       </c>
-      <c r="O126" s="14"/>
+      <c r="O126" t="s">
+        <v>1717</v>
+      </c>
       <c r="P126" s="12" t="s">
         <v>1274</v>
       </c>
@@ -14147,7 +14793,9 @@
       <c r="N127" s="12" t="s">
         <v>1283</v>
       </c>
-      <c r="O127" s="14"/>
+      <c r="O127" t="s">
+        <v>1718</v>
+      </c>
       <c r="P127" s="12" t="s">
         <v>1284</v>
       </c>
@@ -14206,7 +14854,9 @@
       <c r="N128" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="O128" s="14"/>
+      <c r="O128" t="s">
+        <v>1719</v>
+      </c>
       <c r="P128" s="12" t="s">
         <v>197</v>
       </c>
@@ -14269,7 +14919,9 @@
       <c r="N129" s="12" t="s">
         <v>1299</v>
       </c>
-      <c r="O129" s="14"/>
+      <c r="O129" t="s">
+        <v>1720</v>
+      </c>
       <c r="P129" s="12" t="s">
         <v>1300</v>
       </c>
@@ -14330,7 +14982,9 @@
       <c r="N130" s="12" t="s">
         <v>1309</v>
       </c>
-      <c r="O130" s="14"/>
+      <c r="O130" t="s">
+        <v>1721</v>
+      </c>
       <c r="P130" s="12" t="s">
         <v>1310</v>
       </c>
@@ -14395,7 +15049,9 @@
       <c r="N131" s="12" t="s">
         <v>1318</v>
       </c>
-      <c r="O131" s="14"/>
+      <c r="O131" t="s">
+        <v>1722</v>
+      </c>
       <c r="P131" s="12" t="s">
         <v>247</v>
       </c>
@@ -14458,7 +15114,9 @@
       <c r="N132" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="O132" s="14"/>
+      <c r="O132" t="s">
+        <v>1723</v>
+      </c>
       <c r="P132" s="12" t="s">
         <v>256</v>
       </c>
@@ -14521,7 +15179,9 @@
       <c r="N133" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="O133" s="14"/>
+      <c r="O133" t="s">
+        <v>1723</v>
+      </c>
       <c r="P133" s="12" t="s">
         <v>264</v>
       </c>
@@ -14584,7 +15244,9 @@
       <c r="N134" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="O134" s="14"/>
+      <c r="O134" t="s">
+        <v>1724</v>
+      </c>
       <c r="P134" s="12" t="s">
         <v>272</v>
       </c>
@@ -14649,7 +15311,9 @@
       <c r="N135" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="O135" s="14"/>
+      <c r="O135" t="s">
+        <v>1725</v>
+      </c>
       <c r="P135" s="12" t="s">
         <v>303</v>
       </c>
@@ -14714,7 +15378,9 @@
       <c r="N136" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="O136" s="14"/>
+      <c r="O136" t="s">
+        <v>1726</v>
+      </c>
       <c r="P136" s="12" t="s">
         <v>1346</v>
       </c>
@@ -14779,7 +15445,9 @@
       <c r="N137" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="O137" s="14"/>
+      <c r="O137" t="s">
+        <v>1727</v>
+      </c>
       <c r="P137" s="12" t="s">
         <v>1353</v>
       </c>
@@ -14844,7 +15512,9 @@
       <c r="N138" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="O138" s="14"/>
+      <c r="O138" t="s">
+        <v>1728</v>
+      </c>
       <c r="P138" s="12" t="s">
         <v>372</v>
       </c>
@@ -14909,7 +15579,9 @@
       <c r="N139" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="O139" s="14"/>
+      <c r="O139" t="s">
+        <v>1729</v>
+      </c>
       <c r="P139" s="12" t="s">
         <v>416</v>
       </c>
@@ -14970,7 +15642,9 @@
       <c r="N140" s="12" t="s">
         <v>1373</v>
       </c>
-      <c r="O140" s="14"/>
+      <c r="O140" t="s">
+        <v>1730</v>
+      </c>
       <c r="P140" s="12" t="s">
         <v>1374</v>
       </c>
@@ -15035,7 +15709,9 @@
       <c r="N141" s="12" t="s">
         <v>1381</v>
       </c>
-      <c r="O141" s="14"/>
+      <c r="O141" t="s">
+        <v>1731</v>
+      </c>
       <c r="P141" s="12" t="s">
         <v>1382</v>
       </c>
@@ -15096,7 +15772,9 @@
       <c r="N142" s="12" t="s">
         <v>1391</v>
       </c>
-      <c r="O142" s="14"/>
+      <c r="O142" t="s">
+        <v>1732</v>
+      </c>
       <c r="P142" s="12" t="s">
         <v>1392</v>
       </c>
@@ -15157,7 +15835,9 @@
       <c r="N143" s="12" t="s">
         <v>1401</v>
       </c>
-      <c r="O143" s="14"/>
+      <c r="O143" t="s">
+        <v>1733</v>
+      </c>
       <c r="P143" s="12" t="s">
         <v>1402</v>
       </c>
@@ -15222,7 +15902,9 @@
       <c r="N144" s="12" t="s">
         <v>1409</v>
       </c>
-      <c r="O144" s="14"/>
+      <c r="O144" t="s">
+        <v>1734</v>
+      </c>
       <c r="P144" s="12" t="s">
         <v>1410</v>
       </c>
@@ -15287,7 +15969,9 @@
       <c r="N145" s="12" t="s">
         <v>1418</v>
       </c>
-      <c r="O145" s="14"/>
+      <c r="O145" t="s">
+        <v>1735</v>
+      </c>
       <c r="P145" s="12" t="s">
         <v>1419</v>
       </c>
@@ -15352,7 +16036,9 @@
       <c r="N146" s="12" t="s">
         <v>1427</v>
       </c>
-      <c r="O146" s="14"/>
+      <c r="O146" t="s">
+        <v>1736</v>
+      </c>
       <c r="P146" s="12" t="s">
         <v>1428</v>
       </c>
@@ -15413,7 +16099,9 @@
       <c r="N147" s="12" t="s">
         <v>1436</v>
       </c>
-      <c r="O147" s="14"/>
+      <c r="O147" t="s">
+        <v>1737</v>
+      </c>
       <c r="P147" s="12" t="s">
         <v>1437</v>
       </c>
@@ -15478,7 +16166,9 @@
       <c r="N148" s="12" t="s">
         <v>1444</v>
       </c>
-      <c r="O148" s="14"/>
+      <c r="O148" t="s">
+        <v>1738</v>
+      </c>
       <c r="P148" s="12" t="s">
         <v>1445</v>
       </c>
@@ -15541,7 +16231,9 @@
       <c r="N149" s="12" t="s">
         <v>1452</v>
       </c>
-      <c r="O149" s="14"/>
+      <c r="O149" t="s">
+        <v>1739</v>
+      </c>
       <c r="P149" s="12" t="s">
         <v>1453</v>
       </c>
@@ -15604,7 +16296,9 @@
       <c r="N150" s="12" t="s">
         <v>1460</v>
       </c>
-      <c r="O150" s="14"/>
+      <c r="O150" t="s">
+        <v>1740</v>
+      </c>
       <c r="P150" s="12" t="s">
         <v>1461</v>
       </c>
@@ -15669,7 +16363,9 @@
       <c r="N151" s="12" t="s">
         <v>1469</v>
       </c>
-      <c r="O151" s="14"/>
+      <c r="O151" t="s">
+        <v>1741</v>
+      </c>
       <c r="P151" s="12" t="s">
         <v>1470</v>
       </c>
@@ -15732,7 +16428,9 @@
       <c r="N152" s="12" t="s">
         <v>1479</v>
       </c>
-      <c r="O152" s="14"/>
+      <c r="O152" t="s">
+        <v>1742</v>
+      </c>
       <c r="P152" s="12" t="s">
         <v>1480</v>
       </c>
@@ -15797,7 +16495,9 @@
       <c r="N153" s="12" t="s">
         <v>1488</v>
       </c>
-      <c r="O153" s="14"/>
+      <c r="O153" t="s">
+        <v>1743</v>
+      </c>
       <c r="P153" s="12" t="s">
         <v>1489</v>
       </c>
@@ -15860,7 +16560,9 @@
       <c r="N154" s="12" t="s">
         <v>1497</v>
       </c>
-      <c r="O154" s="14"/>
+      <c r="O154" t="s">
+        <v>1744</v>
+      </c>
       <c r="P154" s="12" t="s">
         <v>1498</v>
       </c>
@@ -15923,7 +16625,9 @@
       <c r="N155" s="12" t="s">
         <v>1507</v>
       </c>
-      <c r="O155" s="14"/>
+      <c r="O155" t="s">
+        <v>1745</v>
+      </c>
       <c r="P155" s="12" t="s">
         <v>1508</v>
       </c>
@@ -15988,7 +16692,9 @@
       <c r="N156" s="12" t="s">
         <v>1517</v>
       </c>
-      <c r="O156" s="14"/>
+      <c r="O156" t="s">
+        <v>1746</v>
+      </c>
       <c r="P156" s="12" t="s">
         <v>1518</v>
       </c>
@@ -16053,7 +16759,9 @@
       <c r="N157" s="12" t="s">
         <v>1527</v>
       </c>
-      <c r="O157" s="14"/>
+      <c r="O157" t="s">
+        <v>1747</v>
+      </c>
       <c r="P157" s="12" t="s">
         <v>1528</v>
       </c>
@@ -16118,7 +16826,9 @@
       <c r="N158" s="12" t="s">
         <v>1536</v>
       </c>
-      <c r="O158" s="14"/>
+      <c r="O158" t="s">
+        <v>1748</v>
+      </c>
       <c r="P158" s="12" t="s">
         <v>1537</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1221,7 +1221,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X2" s="14" t="n"/>
+      <c r="X2" s="14" t="inlineStr">
+        <is>
+          <t>images/now-vitamin-a-25000-100-sgels.jpg</t>
+        </is>
+      </c>
       <c r="Y2" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -1340,7 +1344,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X3" s="14" t="n"/>
+      <c r="X3" s="14" t="inlineStr">
+        <is>
+          <t>images/now-biotin-5000-60-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y3" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -1455,7 +1463,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X4" s="14" t="n"/>
+      <c r="X4" s="14" t="inlineStr">
+        <is>
+          <t>images/now-astaxanthin-4mg-60-sgels.jpg</t>
+        </is>
+      </c>
       <c r="Y4" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -1570,7 +1582,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X5" s="14" t="n"/>
+      <c r="X5" s="14" t="inlineStr">
+        <is>
+          <t>images/now-omega-3-1000mg.jpg</t>
+        </is>
+      </c>
       <c r="Y5" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -1685,7 +1701,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X6" s="14" t="n"/>
+      <c r="X6" s="14" t="inlineStr">
+        <is>
+          <t>images/now-super-omega-3-6-9-1000mg.jpg</t>
+        </is>
+      </c>
       <c r="Y6" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -1800,7 +1820,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X7" s="14" t="n"/>
+      <c r="X7" s="14" t="inlineStr">
+        <is>
+          <t>images/now-ultra-omega-3-90-sgels.jpg</t>
+        </is>
+      </c>
       <c r="Y7" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -1909,7 +1933,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X8" s="14" t="n"/>
+      <c r="X8" s="14" t="inlineStr">
+        <is>
+          <t>images/now-clinical-cardio-90-caps.jpg</t>
+        </is>
+      </c>
       <c r="Y8" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -2028,7 +2056,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X9" s="14" t="n"/>
+      <c r="X9" s="14" t="inlineStr">
+        <is>
+          <t>images/now-tribulus-extreme-90-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y9" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -2147,7 +2179,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X10" s="14" t="n"/>
+      <c r="X10" s="14" t="inlineStr">
+        <is>
+          <t>images/now-magnesium-glycinate-180-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y10" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -2262,7 +2298,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X11" s="14" t="n"/>
+      <c r="X11" s="14" t="inlineStr">
+        <is>
+          <t>images/now-magnesium-caps-400mg-180.jpg</t>
+        </is>
+      </c>
       <c r="Y11" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -2377,7 +2417,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X12" s="14" t="n"/>
+      <c r="X12" s="14" t="inlineStr">
+        <is>
+          <t>images/now-magnesium-citrate-120-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y12" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -2492,7 +2536,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X13" s="14" t="n"/>
+      <c r="X13" s="14" t="inlineStr">
+        <is>
+          <t>images/now-magnesium-malate-180-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y13" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -2601,7 +2649,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X14" s="14" t="n"/>
+      <c r="X14" s="14" t="inlineStr">
+        <is>
+          <t>images/now-calcium-magnesium-500-250.jpg</t>
+        </is>
+      </c>
       <c r="Y14" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -2710,7 +2762,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X15" s="14" t="n"/>
+      <c r="X15" s="14" t="inlineStr">
+        <is>
+          <t>images/now-calcium-citrate-w-min-100-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y15" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -2825,7 +2881,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X16" s="14" t="n"/>
+      <c r="X16" s="14" t="inlineStr">
+        <is>
+          <t>images/now-betaine-hcl-648mg-120.jpg</t>
+        </is>
+      </c>
       <c r="Y16" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -2940,7 +3000,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X17" s="14" t="n"/>
+      <c r="X17" s="14" t="inlineStr">
+        <is>
+          <t>images/now-garcinia-1000mg-120-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y17" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -3059,7 +3123,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X18" s="14" t="n"/>
+      <c r="X18" s="14" t="inlineStr">
+        <is>
+          <t>images/now-mega-d3-mk7-5000-180.jpg</t>
+        </is>
+      </c>
       <c r="Y18" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -3178,7 +3246,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X19" s="14" t="n"/>
+      <c r="X19" s="14" t="inlineStr">
+        <is>
+          <t>images/now-vitamin-d3-k2-1000-45.jpg</t>
+        </is>
+      </c>
       <c r="Y19" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -3293,7 +3365,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X20" s="14" t="n"/>
+      <c r="X20" s="14" t="inlineStr">
+        <is>
+          <t>images/now-vitamin-d3-2000iu-120-sgels.jpg</t>
+        </is>
+      </c>
       <c r="Y20" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -3408,7 +3484,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X21" s="14" t="n"/>
+      <c r="X21" s="14" t="inlineStr">
+        <is>
+          <t>images/now-vitamin-d3-5000iu-120-sgels.jpg</t>
+        </is>
+      </c>
       <c r="Y21" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -3523,7 +3603,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X22" s="14" t="n"/>
+      <c r="X22" s="14" t="inlineStr">
+        <is>
+          <t>images/now-vitamin-d3-10000iu-120-sgels.jpg</t>
+        </is>
+      </c>
       <c r="Y22" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -3638,7 +3722,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X23" s="14" t="n"/>
+      <c r="X23" s="14" t="inlineStr">
+        <is>
+          <t>images/now-liquid-vitamin-d3-59ml.jpg</t>
+        </is>
+      </c>
       <c r="Y23" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -3757,7 +3845,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X24" s="14" t="n"/>
+      <c r="X24" s="14" t="inlineStr">
+        <is>
+          <t>images/now-iron-36mg-ferrochel-90.jpg</t>
+        </is>
+      </c>
       <c r="Y24" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -3876,7 +3968,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X25" s="14" t="n"/>
+      <c r="X25" s="14" t="inlineStr">
+        <is>
+          <t>images/now-inositol-500mg-100-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y25" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -3989,7 +4085,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X26" s="14" t="n"/>
+      <c r="X26" s="14" t="inlineStr">
+        <is>
+          <t>images/now-choline-inositol-100-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y26" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -4108,7 +4208,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X27" s="14" t="n"/>
+      <c r="X27" s="14" t="inlineStr">
+        <is>
+          <t>images/now-selenium-200mcg-90-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y27" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -4227,7 +4331,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X28" s="14" t="n"/>
+      <c r="X28" s="14" t="inlineStr">
+        <is>
+          <t>images/now-spirulina-500mg-100-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y28" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -4346,7 +4454,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X29" s="14" t="n"/>
+      <c r="X29" s="14" t="inlineStr">
+        <is>
+          <t>images/now-lecithin-1200mg-100-sgels.jpg</t>
+        </is>
+      </c>
       <c r="Y29" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -4455,7 +4567,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X30" s="14" t="n"/>
+      <c r="X30" s="14" t="inlineStr">
+        <is>
+          <t>images/now-sunflower-lecithin-powder-454g.jpg</t>
+        </is>
+      </c>
       <c r="Y30" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -4574,7 +4690,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X31" s="14" t="n"/>
+      <c r="X31" s="14" t="inlineStr">
+        <is>
+          <t>images/now-zinc-gluconate-50mg-100-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y31" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -4693,7 +4813,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X32" s="14" t="n"/>
+      <c r="X32" s="14" t="inlineStr">
+        <is>
+          <t>images/now-zinc-picolinate-50mg-120.jpg</t>
+        </is>
+      </c>
       <c r="Y32" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -4808,7 +4932,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X33" s="14" t="n"/>
+      <c r="X33" s="14" t="inlineStr">
+        <is>
+          <t>images/now-melatonin-3mg-180-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y33" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -4923,7 +5051,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X34" s="14" t="n"/>
+      <c r="X34" s="14" t="inlineStr">
+        <is>
+          <t>images/now-melatonin-5mg-180-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y34" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -5038,7 +5170,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X35" s="14" t="n"/>
+      <c r="X35" s="14" t="inlineStr">
+        <is>
+          <t>images/now-methyl-b12-1000mcg-250-loz.jpg</t>
+        </is>
+      </c>
       <c r="Y35" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -5147,7 +5283,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X36" s="14" t="n"/>
+      <c r="X36" s="14" t="inlineStr">
+        <is>
+          <t>images/now-b-50-caps-100-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y36" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -5266,7 +5406,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X37" s="14" t="n"/>
+      <c r="X37" s="14" t="inlineStr">
+        <is>
+          <t>images/now-c-500-rose-hips-100-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y37" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -5385,7 +5529,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X38" s="14" t="n"/>
+      <c r="X38" s="14" t="inlineStr">
+        <is>
+          <t>images/now-c-1000-100-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y38" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -5504,7 +5652,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X39" s="14" t="n"/>
+      <c r="X39" s="14" t="inlineStr">
+        <is>
+          <t>images/now-e-200-d-alpha-100-sgels.jpg</t>
+        </is>
+      </c>
       <c r="Y39" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -5623,7 +5775,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X40" s="14" t="n"/>
+      <c r="X40" s="14" t="inlineStr">
+        <is>
+          <t>images/now-e-400-da-100-sgels.jpg</t>
+        </is>
+      </c>
       <c r="Y40" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -5738,7 +5894,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X41" s="14" t="n"/>
+      <c r="X41" s="14" t="inlineStr">
+        <is>
+          <t>images/now-glutathione-500mg-30-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y41" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -5857,7 +6017,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X42" s="14" t="n"/>
+      <c r="X42" s="14" t="inlineStr">
+        <is>
+          <t>images/now-l-arginine-500mg-100-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y42" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -5976,7 +6140,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X43" s="14" t="n"/>
+      <c r="X43" s="14" t="inlineStr">
+        <is>
+          <t>images/now-l-arginine-1000mg-60-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y43" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -6089,7 +6257,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X44" s="14" t="n"/>
+      <c r="X44" s="14" t="inlineStr">
+        <is>
+          <t>images/now-l-arginine-powder-454g.jpg</t>
+        </is>
+      </c>
       <c r="Y44" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -6208,7 +6380,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X45" s="14" t="n"/>
+      <c r="X45" s="14" t="inlineStr">
+        <is>
+          <t>images/now-l-cysteine-500mg-100-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y45" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -6327,7 +6503,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X46" s="14" t="n"/>
+      <c r="X46" s="14" t="inlineStr">
+        <is>
+          <t>images/now-l-carnitine-tartrate-1000mg.jpg</t>
+        </is>
+      </c>
       <c r="Y46" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -6446,7 +6626,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X47" s="14" t="n"/>
+      <c r="X47" s="14" t="inlineStr">
+        <is>
+          <t>images/now-taurine-1000mg-100-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y47" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -6561,7 +6745,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X48" s="14" t="n"/>
+      <c r="X48" s="14" t="inlineStr">
+        <is>
+          <t>images/now-chromium-picolinate-200mcg-250.jpg</t>
+        </is>
+      </c>
       <c r="Y48" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -6680,7 +6868,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X49" s="14" t="n"/>
+      <c r="X49" s="14" t="inlineStr">
+        <is>
+          <t>images/now-milk-thistle-extract-300mg-50.jpg</t>
+        </is>
+      </c>
       <c r="Y49" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -6793,7 +6985,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X50" s="14" t="n"/>
+      <c r="X50" s="14" t="inlineStr">
+        <is>
+          <t>images/now-collagen-peptides-powder-227g.jpg</t>
+        </is>
+      </c>
       <c r="Y50" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -6908,7 +7104,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X51" s="14" t="n"/>
+      <c r="X51" s="14" t="inlineStr">
+        <is>
+          <t>images/now-uc-ii-type-2-collagen-40mg.jpg</t>
+        </is>
+      </c>
       <c r="Y51" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -7023,7 +7223,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X52" s="14" t="n"/>
+      <c r="X52" s="14" t="inlineStr">
+        <is>
+          <t>images/now-alpha-lipoic-acid-100mg-60.jpg</t>
+        </is>
+      </c>
       <c r="Y52" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -7138,7 +7342,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X53" s="14" t="n"/>
+      <c r="X53" s="14" t="inlineStr">
+        <is>
+          <t>images/now-folic-acid-800mcg-250-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y53" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -7253,7 +7461,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X54" s="14" t="n"/>
+      <c r="X54" s="14" t="inlineStr">
+        <is>
+          <t>images/now-methyl-folate-1000mcg-90-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y54" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -7372,7 +7584,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X55" s="14" t="n"/>
+      <c r="X55" s="14" t="inlineStr">
+        <is>
+          <t>images/now-5-htp-50mg-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y55" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -7491,7 +7707,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X56" s="14" t="n"/>
+      <c r="X56" s="14" t="inlineStr">
+        <is>
+          <t>images/now-ginkgo-biloba-120mg-50-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y56" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -7610,7 +7830,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X57" s="14" t="n"/>
+      <c r="X57" s="14" t="inlineStr">
+        <is>
+          <t>images/now-berberine-glucose-support-90.jpg</t>
+        </is>
+      </c>
       <c r="Y57" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -7729,7 +7953,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X58" s="14" t="n"/>
+      <c r="X58" s="14" t="inlineStr">
+        <is>
+          <t>images/now-echinacea-purpurea-400mg-100.jpg</t>
+        </is>
+      </c>
       <c r="Y58" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -7848,7 +8076,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X59" s="14" t="n"/>
+      <c r="X59" s="14" t="inlineStr">
+        <is>
+          <t>images/now-gaba-500mg-100-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y59" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -7963,7 +8195,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X60" s="14" t="n"/>
+      <c r="X60" s="14" t="inlineStr">
+        <is>
+          <t>images/now-paba-500mg-100-caps.jpg</t>
+        </is>
+      </c>
       <c r="Y60" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -8082,7 +8318,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X61" s="14" t="n"/>
+      <c r="X61" s="14" t="inlineStr">
+        <is>
+          <t>images/now-kelp-caps-325mcg-250.jpg</t>
+        </is>
+      </c>
       <c r="Y61" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -8197,7 +8437,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X62" s="14" t="n"/>
+      <c r="X62" s="14" t="inlineStr">
+        <is>
+          <t>images/now-liquid-chlorophyll-mint-473ml.jpg</t>
+        </is>
+      </c>
       <c r="Y62" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -8310,7 +8554,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X63" s="14" t="n"/>
+      <c r="X63" s="14" t="inlineStr">
+        <is>
+          <t>images/now-kid-vits-berry-lemonade-120.jpg</t>
+        </is>
+      </c>
       <c r="Y63" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -8423,7 +8671,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X64" s="14" t="n"/>
+      <c r="X64" s="14" t="inlineStr">
+        <is>
+          <t>images/now-kids-elderberry-liquid-237ml.jpg</t>
+        </is>
+      </c>
       <c r="Y64" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -8536,7 +8788,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X65" s="14" t="n"/>
+      <c r="X65" s="14" t="inlineStr">
+        <is>
+          <t>images/now-kid-cal-chewable-100-loz.jpg</t>
+        </is>
+      </c>
       <c r="Y65" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -8655,7 +8911,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X66" s="14" t="n"/>
+      <c r="X66" s="14" t="inlineStr">
+        <is>
+          <t>images/now-kids-dha-100mg-chewable-60.jpg</t>
+        </is>
+      </c>
       <c r="Y66" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -8764,7 +9024,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X67" s="14" t="n"/>
+      <c r="X67" s="14" t="inlineStr">
+        <is>
+          <t>images/now-essential-oil-rosemary-30ml.jpg</t>
+        </is>
+      </c>
       <c r="Y67" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -8873,7 +9137,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X68" s="14" t="n"/>
+      <c r="X68" s="14" t="inlineStr">
+        <is>
+          <t>images/now-essential-oil-tea-tree-30ml.jpg</t>
+        </is>
+      </c>
       <c r="Y68" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -8982,7 +9250,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X69" s="14" t="n"/>
+      <c r="X69" s="14" t="inlineStr">
+        <is>
+          <t>images/now-essential-oil-eucalyptus-30ml.jpg</t>
+        </is>
+      </c>
       <c r="Y69" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -9101,7 +9373,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X70" s="14" t="n"/>
+      <c r="X70" s="14" t="inlineStr">
+        <is>
+          <t>images/cgn-gold-c-1000mg-60-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y70" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -9216,7 +9492,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X71" s="14" t="n"/>
+      <c r="X71" s="14" t="inlineStr">
+        <is>
+          <t>images/cgn-vitamin-d3-5000iu-90.jpg</t>
+        </is>
+      </c>
       <c r="Y71" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -9329,7 +9609,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X72" s="14" t="n"/>
+      <c r="X72" s="14" t="inlineStr">
+        <is>
+          <t>images/cgn-vitamin-d3-babies-liquid-10ml.jpg</t>
+        </is>
+      </c>
       <c r="Y72" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -9448,7 +9732,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X73" s="14" t="n"/>
+      <c r="X73" s="14" t="inlineStr">
+        <is>
+          <t>images/cgn-lactobif-5-billion-60-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y73" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -9567,7 +9855,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X74" s="14" t="n"/>
+      <c r="X74" s="14" t="inlineStr">
+        <is>
+          <t>images/cgn-lactobif-30-billion-60-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y74" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -9680,7 +9972,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X75" s="14" t="n"/>
+      <c r="X75" s="14" t="inlineStr">
+        <is>
+          <t>images/cgn-collagenup-206g.jpg</t>
+        </is>
+      </c>
       <c r="Y75" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -9793,7 +10089,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X76" s="14" t="n"/>
+      <c r="X76" s="14" t="inlineStr">
+        <is>
+          <t>images/cgn-collagenup-464g.jpg</t>
+        </is>
+      </c>
       <c r="Y76" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -9912,7 +10212,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X77" s="14" t="n"/>
+      <c r="X77" s="14" t="inlineStr">
+        <is>
+          <t>images/np-hema-plex-slow-release-30-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y77" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -10031,7 +10335,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X78" s="14" t="n"/>
+      <c r="X78" s="14" t="inlineStr">
+        <is>
+          <t>images/np-hema-plex-iron-fast-acting-60-caps.jpg</t>
+        </is>
+      </c>
       <c r="Y78" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -10150,7 +10458,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X79" s="14" t="n"/>
+      <c r="X79" s="14" t="inlineStr">
+        <is>
+          <t>images/np-hema-plex-slow-release-60-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y79" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -10263,7 +10575,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X80" s="14" t="n"/>
+      <c r="X80" s="14" t="inlineStr">
+        <is>
+          <t>images/np-hema-plex-iron-chewables-60.jpg</t>
+        </is>
+      </c>
       <c r="Y80" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -10376,7 +10692,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X81" s="14" t="n"/>
+      <c r="X81" s="14" t="inlineStr">
+        <is>
+          <t>images/np-hema-plex-liquid-iron-250ml.jpg</t>
+        </is>
+      </c>
       <c r="Y81" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -10489,7 +10809,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X82" s="14" t="n"/>
+      <c r="X82" s="14" t="inlineStr">
+        <is>
+          <t>images/np-collagen-peptides-294g.jpg</t>
+        </is>
+      </c>
       <c r="Y82" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -10602,7 +10926,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X83" s="14" t="n"/>
+      <c r="X83" s="14" t="inlineStr">
+        <is>
+          <t>images/np-collagen-peptides-vanilla-364g.jpg</t>
+        </is>
+      </c>
       <c r="Y83" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -10715,7 +11043,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X84" s="14" t="n"/>
+      <c r="X84" s="14" t="inlineStr">
+        <is>
+          <t>images/np-collagen-peptides-chocolate-378g.jpg</t>
+        </is>
+      </c>
       <c r="Y84" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -10834,7 +11166,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X85" s="14" t="n"/>
+      <c r="X85" s="14" t="inlineStr">
+        <is>
+          <t>images/np-magkidz-magnesium-cherry-90-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y85" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -10947,7 +11283,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X86" s="14" t="n"/>
+      <c r="X86" s="14" t="inlineStr">
+        <is>
+          <t>images/np-magkidz-magnesium-cherry-171g.jpg</t>
+        </is>
+      </c>
       <c r="Y86" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -11060,7 +11400,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X87" s="14" t="n"/>
+      <c r="X87" s="14" t="inlineStr">
+        <is>
+          <t>images/np-animal-parade-gold-60-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y87" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -11173,7 +11517,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X88" s="14" t="n"/>
+      <c r="X88" s="14" t="inlineStr">
+        <is>
+          <t>images/np-animal-parade-multivitamin-90-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y88" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -11286,7 +11634,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X89" s="14" t="n"/>
+      <c r="X89" s="14" t="inlineStr">
+        <is>
+          <t>images/np-animal-parade-gold-120-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y89" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -11399,7 +11751,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X90" s="14" t="n"/>
+      <c r="X90" s="14" t="inlineStr">
+        <is>
+          <t>images/np-animal-parade-multivitamin-180-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y90" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -11512,7 +11868,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X91" s="14" t="n"/>
+      <c r="X91" s="14" t="inlineStr">
+        <is>
+          <t>images/np-animal-parade-watermelon-180-tabs.jpg</t>
+        </is>
+      </c>
       <c r="Y91" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -11625,7 +11985,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X92" s="14" t="n"/>
+      <c r="X92" s="14" t="inlineStr">
+        <is>
+          <t>images/childlife-liquid-vitamin-d3-30ml.jpg</t>
+        </is>
+      </c>
       <c r="Y92" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -11738,7 +12102,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X93" s="14" t="n"/>
+      <c r="X93" s="14" t="inlineStr">
+        <is>
+          <t>images/childlife-liquid-vitamin-c-118ml.jpg</t>
+        </is>
+      </c>
       <c r="Y93" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -11851,7 +12219,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X94" s="14" t="n"/>
+      <c r="X94" s="14" t="inlineStr">
+        <is>
+          <t>images/childlife-liquid-zinc-plus-118ml.jpg</t>
+        </is>
+      </c>
       <c r="Y94" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -11964,7 +12336,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X95" s="14" t="n"/>
+      <c r="X95" s="14" t="inlineStr">
+        <is>
+          <t>images/childlife-liquid-iron-118ml.jpg</t>
+        </is>
+      </c>
       <c r="Y95" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -12077,7 +12453,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X96" s="14" t="n"/>
+      <c r="X96" s="14" t="inlineStr">
+        <is>
+          <t>images/childlife-liquid-calcium-magnesium-473ml.jpg</t>
+        </is>
+      </c>
       <c r="Y96" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -12190,7 +12570,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X97" s="14" t="n"/>
+      <c r="X97" s="14" t="inlineStr">
+        <is>
+          <t>images/childlife-liquid-multivitamin-237ml.jpg</t>
+        </is>
+      </c>
       <c r="Y97" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -12303,7 +12687,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X98" s="14" t="n"/>
+      <c r="X98" s="14" t="inlineStr">
+        <is>
+          <t>images/childlife-liquid-echinacea-30ml.jpg</t>
+        </is>
+      </c>
       <c r="Y98" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -12416,7 +12804,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X99" s="14" t="n"/>
+      <c r="X99" s="14" t="inlineStr">
+        <is>
+          <t>images/life-extension-two-per-day-60-caps.jpg</t>
+        </is>
+      </c>
       <c r="Y99" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -12529,7 +12921,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X100" s="14" t="n"/>
+      <c r="X100" s="14" t="inlineStr">
+        <is>
+          <t>images/life-extension-two-per-day-120-caps.jpg</t>
+        </is>
+      </c>
       <c r="Y100" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -12638,7 +13034,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X101" s="14" t="n"/>
+      <c r="X101" s="14" t="inlineStr">
+        <is>
+          <t>images/life-extension-bioactive-b-complex-60.jpg</t>
+        </is>
+      </c>
       <c r="Y101" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -12751,7 +13151,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X102" s="14" t="n"/>
+      <c r="X102" s="14" t="inlineStr">
+        <is>
+          <t>images/life-extension-neuro-mag-powder-93g.jpg</t>
+        </is>
+      </c>
       <c r="Y102" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -12864,7 +13268,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X103" s="14" t="n"/>
+      <c r="X103" s="14" t="inlineStr">
+        <is>
+          <t>images/life-extension-neuro-mag-90-vegcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y103" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -12979,7 +13387,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X104" s="14" t="n"/>
+      <c r="X104" s="14" t="inlineStr">
+        <is>
+          <t>images/life-extension-inositol-1000mg-360.jpg</t>
+        </is>
+      </c>
       <c r="Y104" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -13092,7 +13504,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X105" s="14" t="n"/>
+      <c r="X105" s="14" t="inlineStr">
+        <is>
+          <t>images/life-extension-super-selenium-complex-100.jpg</t>
+        </is>
+      </c>
       <c r="Y105" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -13201,7 +13617,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X106" s="14" t="n"/>
+      <c r="X106" s="14" t="inlineStr">
+        <is>
+          <t>images/natures-answer-liquid-magnesium-480ml.jpg</t>
+        </is>
+      </c>
       <c r="Y106" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -13314,7 +13734,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X107" s="14" t="n"/>
+      <c r="X107" s="14" t="inlineStr">
+        <is>
+          <t>images/natures-answer-liquid-vitamin-c-240ml.jpg</t>
+        </is>
+      </c>
       <c r="Y107" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -13423,7 +13847,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X108" s="14" t="n"/>
+      <c r="X108" s="14" t="inlineStr">
+        <is>
+          <t>images/natures-answer-liquid-b-complex-240ml.jpg</t>
+        </is>
+      </c>
       <c r="Y108" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -13532,7 +13960,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X109" s="14" t="n"/>
+      <c r="X109" s="14" t="inlineStr">
+        <is>
+          <t>images/natures-answer-liquid-chlorophyll-480ml.jpg</t>
+        </is>
+      </c>
       <c r="Y109" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -13647,7 +14079,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X110" s="14" t="n"/>
+      <c r="X110" s="14" t="inlineStr">
+        <is>
+          <t>images/solaray-magnesium-citrate-400mg-90.jpg</t>
+        </is>
+      </c>
       <c r="Y110" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -13762,7 +14198,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X111" s="14" t="n"/>
+      <c r="X111" s="14" t="inlineStr">
+        <is>
+          <t>images/solaray-magnesium-citrate-400mg-180.jpg</t>
+        </is>
+      </c>
       <c r="Y111" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -13881,7 +14321,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X112" s="14" t="n"/>
+      <c r="X112" s="14" t="inlineStr">
+        <is>
+          <t>images/solaray-zinc-citrate-50mg-60.jpg</t>
+        </is>
+      </c>
       <c r="Y112" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -14000,7 +14444,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X113" s="14" t="n"/>
+      <c r="X113" s="14" t="inlineStr">
+        <is>
+          <t>images/solaray-magnesium-glycinate-350mg-120.jpg</t>
+        </is>
+      </c>
       <c r="Y113" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -14119,7 +14567,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X114" s="14" t="n"/>
+      <c r="X114" s="14" t="inlineStr">
+        <is>
+          <t>images/solaray-magnesium-glycinate-350mg-240.jpg</t>
+        </is>
+      </c>
       <c r="Y114" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -14238,7 +14690,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X115" s="14" t="n"/>
+      <c r="X115" s="14" t="inlineStr">
+        <is>
+          <t>images/solaray-vitamin-d3-k2-60-vegcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y115" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -14357,7 +14813,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X116" s="14" t="n"/>
+      <c r="X116" s="14" t="inlineStr">
+        <is>
+          <t>images/solaray-vitamin-d3-k2-120-vegcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y116" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -14476,7 +14936,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X117" s="14" t="n"/>
+      <c r="X117" s="14" t="inlineStr">
+        <is>
+          <t>images/solaray-selenium-200mcg-90-vegcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y117" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -14595,7 +15059,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X118" s="14" t="n"/>
+      <c r="X118" s="14" t="inlineStr">
+        <is>
+          <t>images/solaray-vital-extracts-artichoke-600mg.jpg</t>
+        </is>
+      </c>
       <c r="Y118" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -14714,7 +15182,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X119" s="14" t="n"/>
+      <c r="X119" s="14" t="inlineStr">
+        <is>
+          <t>images/solaray-l-lysine-monolaurin-60.jpg</t>
+        </is>
+      </c>
       <c r="Y119" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -14829,7 +15301,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X120" s="14" t="n"/>
+      <c r="X120" s="14" t="inlineStr">
+        <is>
+          <t>images/solaray-chromium-picolinate-200mcg-100.jpg</t>
+        </is>
+      </c>
       <c r="Y120" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -14948,7 +15424,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X121" s="14" t="n"/>
+      <c r="X121" s="14" t="inlineStr">
+        <is>
+          <t>images/solaray-berberine-curcumin-60-vegcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y121" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -15063,7 +15543,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X122" s="14" t="n"/>
+      <c r="X122" s="14" t="inlineStr">
+        <is>
+          <t>images/lifeflo-liquid-iodine-plus-59ml.jpg</t>
+        </is>
+      </c>
       <c r="Y122" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -15178,7 +15662,11 @@
         </is>
       </c>
       <c r="W123" s="12" t="n"/>
-      <c r="X123" s="14" t="n"/>
+      <c r="X123" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-biotin-5000mcg-60-caps.jpg</t>
+        </is>
+      </c>
       <c r="Y123" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -15289,7 +15777,11 @@
         </is>
       </c>
       <c r="W124" s="12" t="n"/>
-      <c r="X124" s="14" t="n"/>
+      <c r="X124" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-omega-3-epa540-dha360-30.jpg</t>
+        </is>
+      </c>
       <c r="Y124" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -15400,7 +15892,11 @@
         </is>
       </c>
       <c r="W125" s="12" t="n"/>
-      <c r="X125" s="14" t="n"/>
+      <c r="X125" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-omega-3-epa540-dha360-100.jpg</t>
+        </is>
+      </c>
       <c r="Y125" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -15509,7 +16005,11 @@
         </is>
       </c>
       <c r="W126" s="12" t="n"/>
-      <c r="X126" s="14" t="n"/>
+      <c r="X126" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-lions-mane-mushroom-90-caps.jpg</t>
+        </is>
+      </c>
       <c r="Y126" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -15620,7 +16120,11 @@
         </is>
       </c>
       <c r="W127" s="12" t="n"/>
-      <c r="X127" s="14" t="n"/>
+      <c r="X127" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-coenzyme-q10-100mg-60.jpg</t>
+        </is>
+      </c>
       <c r="Y127" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -15725,7 +16229,11 @@
         </is>
       </c>
       <c r="W128" s="12" t="n"/>
-      <c r="X128" s="14" t="n"/>
+      <c r="X128" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-calcium-zinc-magnesium-d3-b6-100.jpg</t>
+        </is>
+      </c>
       <c r="Y128" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -15836,7 +16344,11 @@
         </is>
       </c>
       <c r="W129" s="12" t="n"/>
-      <c r="X129" s="14" t="n"/>
+      <c r="X129" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-calcium-citrate-210mg-90.jpg</t>
+        </is>
+      </c>
       <c r="Y129" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -15945,7 +16457,11 @@
         </is>
       </c>
       <c r="W130" s="12" t="n"/>
-      <c r="X130" s="14" t="n"/>
+      <c r="X130" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-magnesium-citrate-b6-60.jpg</t>
+        </is>
+      </c>
       <c r="Y130" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -16060,7 +16576,11 @@
         </is>
       </c>
       <c r="W131" s="12" t="n"/>
-      <c r="X131" s="14" t="n"/>
+      <c r="X131" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-vitamin-d3-k2-2000-50-100.jpg</t>
+        </is>
+      </c>
       <c r="Y131" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -16171,7 +16691,11 @@
         </is>
       </c>
       <c r="W132" s="12" t="n"/>
-      <c r="X132" s="14" t="n"/>
+      <c r="X132" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-vitamin-d3-2000me-100.jpg</t>
+        </is>
+      </c>
       <c r="Y132" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -16282,7 +16806,11 @@
         </is>
       </c>
       <c r="W133" s="12" t="n"/>
-      <c r="X133" s="14" t="n"/>
+      <c r="X133" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-vitamin-d3-5000me-100.jpg</t>
+        </is>
+      </c>
       <c r="Y133" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -16393,7 +16921,11 @@
         </is>
       </c>
       <c r="W134" s="12" t="n"/>
-      <c r="X134" s="14" t="n"/>
+      <c r="X134" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-vitamin-d3-10000me-100.jpg</t>
+        </is>
+      </c>
       <c r="Y134" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -16508,7 +17040,11 @@
         </is>
       </c>
       <c r="W135" s="12" t="n"/>
-      <c r="X135" s="14" t="n"/>
+      <c r="X135" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-myo-inositol-500mg-100.jpg</t>
+        </is>
+      </c>
       <c r="Y135" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -16623,7 +17159,11 @@
         </is>
       </c>
       <c r="W136" s="12" t="n"/>
-      <c r="X136" s="14" t="n"/>
+      <c r="X136" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-selenium-100mcg-90.jpg</t>
+        </is>
+      </c>
       <c r="Y136" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -16738,7 +17278,11 @@
         </is>
       </c>
       <c r="W137" s="12" t="n"/>
-      <c r="X137" s="14" t="n"/>
+      <c r="X137" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-sunflower-lecithin-1000mg-100.jpg</t>
+        </is>
+      </c>
       <c r="Y137" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -16853,7 +17397,11 @@
         </is>
       </c>
       <c r="W138" s="12" t="n"/>
-      <c r="X138" s="14" t="n"/>
+      <c r="X138" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-zinc-picolinate-125mg-60.jpg</t>
+        </is>
+      </c>
       <c r="Y138" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -16968,7 +17516,11 @@
         </is>
       </c>
       <c r="W139" s="12" t="n"/>
-      <c r="X139" s="14" t="n"/>
+      <c r="X139" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-vitamin-c-500mg-100.jpg</t>
+        </is>
+      </c>
       <c r="Y139" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -17077,7 +17629,11 @@
         </is>
       </c>
       <c r="W140" s="12" t="n"/>
-      <c r="X140" s="14" t="n"/>
+      <c r="X140" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-marine-collagen-240g.jpg</t>
+        </is>
+      </c>
       <c r="Y140" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -17192,7 +17748,11 @@
         </is>
       </c>
       <c r="W141" s="12" t="n"/>
-      <c r="X141" s="14" t="n"/>
+      <c r="X141" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-type-1-3-collagen-430mg-60.jpg</t>
+        </is>
+      </c>
       <c r="Y141" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -17301,7 +17861,11 @@
         </is>
       </c>
       <c r="W142" s="12" t="n"/>
-      <c r="X142" s="14" t="n"/>
+      <c r="X142" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-men-active-multivitamin-90.jpg</t>
+        </is>
+      </c>
       <c r="Y142" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -17410,7 +17974,11 @@
         </is>
       </c>
       <c r="W143" s="12" t="n"/>
-      <c r="X143" s="14" t="n"/>
+      <c r="X143" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-women-balance-multivitamin-90.jpg</t>
+        </is>
+      </c>
       <c r="Y143" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -17525,7 +18093,11 @@
         </is>
       </c>
       <c r="W144" s="12" t="n"/>
-      <c r="X144" s="14" t="n"/>
+      <c r="X144" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-l-carnitine-850mg-90.jpg</t>
+        </is>
+      </c>
       <c r="Y144" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -17640,7 +18212,11 @@
         </is>
       </c>
       <c r="W145" s="12" t="n"/>
-      <c r="X145" s="14" t="n"/>
+      <c r="X145" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-berberine-500mg-60.jpg</t>
+        </is>
+      </c>
       <c r="Y145" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -17755,7 +18331,11 @@
         </is>
       </c>
       <c r="W146" s="12" t="n"/>
-      <c r="X146" s="14" t="n"/>
+      <c r="X146" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-glucosamine-chondroitin-msm-120.jpg</t>
+        </is>
+      </c>
       <c r="Y146" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -17864,7 +18444,11 @@
         </is>
       </c>
       <c r="W147" s="12" t="n"/>
-      <c r="X147" s="14" t="n"/>
+      <c r="X147" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-b-complex-60-caps.jpg</t>
+        </is>
+      </c>
       <c r="Y147" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -17979,7 +18563,11 @@
         </is>
       </c>
       <c r="W148" s="12" t="n"/>
-      <c r="X148" s="14" t="n"/>
+      <c r="X148" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-iron-chelate-40mg-60.jpg</t>
+        </is>
+      </c>
       <c r="Y148" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -18090,7 +18678,11 @@
         </is>
       </c>
       <c r="W149" s="12" t="n"/>
-      <c r="X149" s="14" t="n"/>
+      <c r="X149" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-folic-acid-400mcg-60.jpg</t>
+        </is>
+      </c>
       <c r="Y149" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -18201,7 +18793,11 @@
         </is>
       </c>
       <c r="W150" s="12" t="n"/>
-      <c r="X150" s="14" t="n"/>
+      <c r="X150" s="14" t="inlineStr">
+        <is>
+          <t>images/ecovita-chromium-picolinate-200mcg-60.jpg</t>
+        </is>
+      </c>
       <c r="Y150" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -18316,7 +18912,11 @@
         </is>
       </c>
       <c r="W151" s="12" t="n"/>
-      <c r="X151" s="14" t="n"/>
+      <c r="X151" s="14" t="inlineStr">
+        <is>
+          <t>images/vita-garden-biotin-5000mcg-30.jpg</t>
+        </is>
+      </c>
       <c r="Y151" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -18427,7 +19027,11 @@
         </is>
       </c>
       <c r="W152" s="12" t="n"/>
-      <c r="X152" s="14" t="n"/>
+      <c r="X152" s="14" t="inlineStr">
+        <is>
+          <t>images/vita-garden-omega-3-fish-oil-60.jpg</t>
+        </is>
+      </c>
       <c r="Y152" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -18542,7 +19146,11 @@
         </is>
       </c>
       <c r="W153" s="12" t="n"/>
-      <c r="X153" s="14" t="n"/>
+      <c r="X153" s="14" t="inlineStr">
+        <is>
+          <t>images/vita-garden-magnesium-b6-60.jpg</t>
+        </is>
+      </c>
       <c r="Y153" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -18653,7 +19261,11 @@
         </is>
       </c>
       <c r="W154" s="12" t="n"/>
-      <c r="X154" s="14" t="n"/>
+      <c r="X154" s="14" t="inlineStr">
+        <is>
+          <t>images/vita-garden-calcium-citrate-210mg-60.jpg</t>
+        </is>
+      </c>
       <c r="Y154" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -18764,7 +19376,11 @@
         </is>
       </c>
       <c r="W155" s="12" t="n"/>
-      <c r="X155" s="14" t="n"/>
+      <c r="X155" s="14" t="inlineStr">
+        <is>
+          <t>images/vita-garden-vitamin-d3-2000me-60.jpg</t>
+        </is>
+      </c>
       <c r="Y155" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -18879,7 +19495,11 @@
         </is>
       </c>
       <c r="W156" s="12" t="n"/>
-      <c r="X156" s="14" t="n"/>
+      <c r="X156" s="14" t="inlineStr">
+        <is>
+          <t>images/vita-garden-myo-inositol-500mg-60.jpg</t>
+        </is>
+      </c>
       <c r="Y156" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -18994,7 +19614,11 @@
         </is>
       </c>
       <c r="W157" s="12" t="n"/>
-      <c r="X157" s="14" t="n"/>
+      <c r="X157" s="14" t="inlineStr">
+        <is>
+          <t>images/vita-garden-selenium-100mcg-60.jpg</t>
+        </is>
+      </c>
       <c r="Y157" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -19109,7 +19733,11 @@
         </is>
       </c>
       <c r="W158" s="12" t="n"/>
-      <c r="X158" s="14" t="n"/>
+      <c r="X158" s="14" t="inlineStr">
+        <is>
+          <t>images/vita-garden-zinc-picolinate-125mg-60.jpg</t>
+        </is>
+      </c>
       <c r="Y158" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -19224,7 +19852,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X159" s="14" t="n"/>
+      <c r="X159" s="14" t="inlineStr">
+        <is>
+          <t>images/now-vitamin-a-10000iu-100-sgels.jpg</t>
+        </is>
+      </c>
       <c r="Y159" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -19333,7 +19965,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X160" s="14" t="n"/>
+      <c r="X160" s="14" t="inlineStr">
+        <is>
+          <t>images/now-psyllium-husk-whole.jpg</t>
+        </is>
+      </c>
       <c r="Y160" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -19452,7 +20088,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X161" s="14" t="n"/>
+      <c r="X161" s="14" t="inlineStr">
+        <is>
+          <t>images/now-biotin-10000mcg-120-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y161" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -19567,7 +20207,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X162" s="14" t="n"/>
+      <c r="X162" s="14" t="inlineStr">
+        <is>
+          <t>images/now-propolis-1500-300mg-100-caps.jpg</t>
+        </is>
+      </c>
       <c r="Y162" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -19686,7 +20330,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X163" s="14" t="n"/>
+      <c r="X163" s="14" t="inlineStr">
+        <is>
+          <t>images/now-probiotic-10-25-billion-50-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y163" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -19805,7 +20453,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X164" s="14" t="n"/>
+      <c r="X164" s="14" t="inlineStr">
+        <is>
+          <t>images/now-silymarin-milk-thistle-turmeric-150mg-60-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y164" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -19920,7 +20572,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X165" s="14" t="n"/>
+      <c r="X165" s="14" t="inlineStr">
+        <is>
+          <t>images/now-glutathione-250mg-60-vcaps.jpg</t>
+        </is>
+      </c>
       <c r="Y165" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -20033,7 +20689,11 @@
           <t>США</t>
         </is>
       </c>
-      <c r="X166" s="14" t="n"/>
+      <c r="X166" s="14" t="inlineStr">
+        <is>
+          <t>images/now-kids-liquid-echinacea-orange-59ml.jpg</t>
+        </is>
+      </c>
       <c r="Y166" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -20148,7 +20808,11 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X167" s="14" t="n"/>
+      <c r="X167" s="14" t="inlineStr">
+        <is>
+          <t>images/biomagic-iodine-25ml.jpg</t>
+        </is>
+      </c>
       <c r="Y167" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>
@@ -20261,7 +20925,11 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="X168" s="14" t="n"/>
+      <c r="X168" s="14" t="inlineStr">
+        <is>
+          <t>images/biomagic-iodine-selenium-25ml.jpg</t>
+        </is>
+      </c>
       <c r="Y168" s="12" t="inlineStr">
         <is>
           <t>опубликован</t>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1223,7 +1223,7 @@
       </c>
       <c r="X2" s="14" t="inlineStr">
         <is>
-          <t>images/now-vitamin-a-25000-100-sgels.jpg</t>
+          <t>images/now-vitamin-a-25000.jpg</t>
         </is>
       </c>
       <c r="Y2" s="12" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="X3" s="14" t="inlineStr">
         <is>
-          <t>images/now-biotin-5000-60-vcaps.jpg</t>
+          <t>images/now-biotin-5000.jpg</t>
         </is>
       </c>
       <c r="Y3" s="12" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="X4" s="14" t="inlineStr">
         <is>
-          <t>images/now-astaxanthin-4mg-60-sgels.jpg</t>
+          <t>images/now-astaxanthin-4.jpg</t>
         </is>
       </c>
       <c r="Y4" s="12" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="X5" s="14" t="inlineStr">
         <is>
-          <t>images/now-omega-3-1000mg.jpg</t>
+          <t>images/now-omega-3-1000.jpg</t>
         </is>
       </c>
       <c r="Y5" s="12" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="X6" s="14" t="inlineStr">
         <is>
-          <t>images/now-super-omega-3-6-9-1000mg.jpg</t>
+          <t>images/now-super-omega-369.jpg</t>
         </is>
       </c>
       <c r="Y6" s="12" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="X7" s="14" t="inlineStr">
         <is>
-          <t>images/now-ultra-omega-3-90-sgels.jpg</t>
+          <t>images/now-ultra-omega-3.jpg</t>
         </is>
       </c>
       <c r="Y7" s="12" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="X8" s="14" t="inlineStr">
         <is>
-          <t>images/now-clinical-cardio-90-caps.jpg</t>
+          <t>images/now-clinical-cardio.jpg</t>
         </is>
       </c>
       <c r="Y8" s="12" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="X9" s="14" t="inlineStr">
         <is>
-          <t>images/now-tribulus-extreme-90-vcaps.jpg</t>
+          <t>images/now-tribulus-extreme.jpg</t>
         </is>
       </c>
       <c r="Y9" s="12" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="X10" s="14" t="inlineStr">
         <is>
-          <t>images/now-magnesium-glycinate-180-vcaps.jpg</t>
+          <t>images/now-magnesium-glycinate-400.jpg</t>
         </is>
       </c>
       <c r="Y10" s="12" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="X11" s="14" t="inlineStr">
         <is>
-          <t>images/now-magnesium-caps-400mg-180.jpg</t>
+          <t>images/now-magnesium-caps-400.jpg</t>
         </is>
       </c>
       <c r="Y11" s="12" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="X12" s="14" t="inlineStr">
         <is>
-          <t>images/now-magnesium-citrate-120-vcaps.jpg</t>
+          <t>images/now-magnesium-citrate-caps.jpg</t>
         </is>
       </c>
       <c r="Y12" s="12" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="X13" s="14" t="inlineStr">
         <is>
-          <t>images/now-magnesium-malate-180-vcaps.jpg</t>
+          <t>images/now-magnesium-malate.jpg</t>
         </is>
       </c>
       <c r="Y13" s="12" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="X14" s="14" t="inlineStr">
         <is>
-          <t>images/now-calcium-magnesium-500-250.jpg</t>
+          <t>images/now-calcium-magnesium.jpg</t>
         </is>
       </c>
       <c r="Y14" s="12" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="X15" s="14" t="inlineStr">
         <is>
-          <t>images/now-calcium-citrate-w-min-100-tabs.jpg</t>
+          <t>images/now-calcium-citrate-min.jpg</t>
         </is>
       </c>
       <c r="Y15" s="12" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="X16" s="14" t="inlineStr">
         <is>
-          <t>images/now-betaine-hcl-648mg-120.jpg</t>
+          <t>images/now-betaine-hcl.jpg</t>
         </is>
       </c>
       <c r="Y16" s="12" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="X17" s="14" t="inlineStr">
         <is>
-          <t>images/now-garcinia-1000mg-120-tabs.jpg</t>
+          <t>images/now-garcinia-1000.jpg</t>
         </is>
       </c>
       <c r="Y17" s="12" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="X18" s="14" t="inlineStr">
         <is>
-          <t>images/now-mega-d3-mk7-5000-180.jpg</t>
+          <t>images/now-mega-d3-mk7.jpg</t>
         </is>
       </c>
       <c r="Y18" s="12" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="X19" s="14" t="inlineStr">
         <is>
-          <t>images/now-vitamin-d3-k2-1000-45.jpg</t>
+          <t>images/now-vitamin-d3-k2-1000.jpg</t>
         </is>
       </c>
       <c r="Y19" s="12" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="X20" s="14" t="inlineStr">
         <is>
-          <t>images/now-vitamin-d3-2000iu-120-sgels.jpg</t>
+          <t>images/now-vitamin-d3-2000.jpg</t>
         </is>
       </c>
       <c r="Y20" s="12" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="X21" s="14" t="inlineStr">
         <is>
-          <t>images/now-vitamin-d3-5000iu-120-sgels.jpg</t>
+          <t>images/now-vitamin-d3-5000.jpg</t>
         </is>
       </c>
       <c r="Y21" s="12" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="X22" s="14" t="inlineStr">
         <is>
-          <t>images/now-vitamin-d3-10000iu-120-sgels.jpg</t>
+          <t>images/now-vitamin-d3-10000.jpg</t>
         </is>
       </c>
       <c r="Y22" s="12" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="X23" s="14" t="inlineStr">
         <is>
-          <t>images/now-liquid-vitamin-d3-59ml.jpg</t>
+          <t>images/now-liquid-vitamin-d3.jpg</t>
         </is>
       </c>
       <c r="Y23" s="12" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="X24" s="14" t="inlineStr">
         <is>
-          <t>images/now-iron-36mg-ferrochel-90.jpg</t>
+          <t>images/now-iron-36-ferrochel.jpg</t>
         </is>
       </c>
       <c r="Y24" s="12" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="X25" s="14" t="inlineStr">
         <is>
-          <t>images/now-inositol-500mg-100-vcaps.jpg</t>
+          <t>images/now-inositol-500.jpg</t>
         </is>
       </c>
       <c r="Y25" s="12" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="X26" s="14" t="inlineStr">
         <is>
-          <t>images/now-choline-inositol-100-vcaps.jpg</t>
+          <t>images/now-choline-inositol.jpg</t>
         </is>
       </c>
       <c r="Y26" s="12" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="X27" s="14" t="inlineStr">
         <is>
-          <t>images/now-selenium-200mcg-90-vcaps.jpg</t>
+          <t>images/now-selenium-200.jpg</t>
         </is>
       </c>
       <c r="Y27" s="12" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="X28" s="14" t="inlineStr">
         <is>
-          <t>images/now-spirulina-500mg-100-tabs.jpg</t>
+          <t>images/now-spirulina-500.jpg</t>
         </is>
       </c>
       <c r="Y28" s="12" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="X29" s="14" t="inlineStr">
         <is>
-          <t>images/now-lecithin-1200mg-100-sgels.jpg</t>
+          <t>images/now-lecithin-1200.jpg</t>
         </is>
       </c>
       <c r="Y29" s="12" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="X30" s="14" t="inlineStr">
         <is>
-          <t>images/now-sunflower-lecithin-powder-454g.jpg</t>
+          <t>images/now-sunflower-lecithin-powder.jpg</t>
         </is>
       </c>
       <c r="Y30" s="12" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="X31" s="14" t="inlineStr">
         <is>
-          <t>images/now-zinc-gluconate-50mg-100-tabs.jpg</t>
+          <t>images/now-zinc-gluconate-50.jpg</t>
         </is>
       </c>
       <c r="Y31" s="12" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="X32" s="14" t="inlineStr">
         <is>
-          <t>images/now-zinc-picolinate-50mg-120.jpg</t>
+          <t>images/now-zinc-picolinate-50.jpg</t>
         </is>
       </c>
       <c r="Y32" s="12" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="X33" s="14" t="inlineStr">
         <is>
-          <t>images/now-melatonin-3mg-180-vcaps.jpg</t>
+          <t>images/now-melatonin-3.jpg</t>
         </is>
       </c>
       <c r="Y33" s="12" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="X34" s="14" t="inlineStr">
         <is>
-          <t>images/now-melatonin-5mg-180-vcaps.jpg</t>
+          <t>images/now-melatonin-5.jpg</t>
         </is>
       </c>
       <c r="Y34" s="12" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="X35" s="14" t="inlineStr">
         <is>
-          <t>images/now-methyl-b12-1000mcg-250-loz.jpg</t>
+          <t>images/now-b12-1000-loz.jpg</t>
         </is>
       </c>
       <c r="Y35" s="12" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="X36" s="14" t="inlineStr">
         <is>
-          <t>images/now-b-50-caps-100-vcaps.jpg</t>
+          <t>images/now-b50-caps.jpg</t>
         </is>
       </c>
       <c r="Y36" s="12" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="X37" s="14" t="inlineStr">
         <is>
-          <t>images/now-c-500-rose-hips-100-tabs.jpg</t>
+          <t>images/now-c-500-rh.jpg</t>
         </is>
       </c>
       <c r="Y37" s="12" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="X38" s="14" t="inlineStr">
         <is>
-          <t>images/now-c-1000-100-tabs.jpg</t>
+          <t>images/now-c-1000.jpg</t>
         </is>
       </c>
       <c r="Y38" s="12" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="X39" s="14" t="inlineStr">
         <is>
-          <t>images/now-e-200-d-alpha-100-sgels.jpg</t>
+          <t>images/now-e-200.jpg</t>
         </is>
       </c>
       <c r="Y39" s="12" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="X40" s="14" t="inlineStr">
         <is>
-          <t>images/now-e-400-da-100-sgels.jpg</t>
+          <t>images/now-e-400.jpg</t>
         </is>
       </c>
       <c r="Y40" s="12" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="X41" s="14" t="inlineStr">
         <is>
-          <t>images/now-glutathione-500mg-30-vcaps.jpg</t>
+          <t>images/now-glutathione-500.jpg</t>
         </is>
       </c>
       <c r="Y41" s="12" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="X42" s="14" t="inlineStr">
         <is>
-          <t>images/now-l-arginine-500mg-100-vcaps.jpg</t>
+          <t>images/now-l-arginine-500.jpg</t>
         </is>
       </c>
       <c r="Y42" s="12" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="X43" s="14" t="inlineStr">
         <is>
-          <t>images/now-l-arginine-1000mg-60-tabs.jpg</t>
+          <t>images/now-l-arginine-1000.jpg</t>
         </is>
       </c>
       <c r="Y43" s="12" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="X44" s="14" t="inlineStr">
         <is>
-          <t>images/now-l-arginine-powder-454g.jpg</t>
+          <t>images/now-l-arginine-powder.jpg</t>
         </is>
       </c>
       <c r="Y44" s="12" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="X45" s="14" t="inlineStr">
         <is>
-          <t>images/now-l-cysteine-500mg-100-tabs.jpg</t>
+          <t>images/now-cysteine-500.jpg</t>
         </is>
       </c>
       <c r="Y45" s="12" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="X46" s="14" t="inlineStr">
         <is>
-          <t>images/now-l-carnitine-tartrate-1000mg.jpg</t>
+          <t>images/now-carnitine-tartrate.jpg</t>
         </is>
       </c>
       <c r="Y46" s="12" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="X47" s="14" t="inlineStr">
         <is>
-          <t>images/now-taurine-1000mg-100-vcaps.jpg</t>
+          <t>images/now-taurine-1000.jpg</t>
         </is>
       </c>
       <c r="Y47" s="12" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="X48" s="14" t="inlineStr">
         <is>
-          <t>images/now-chromium-picolinate-200mcg-250.jpg</t>
+          <t>images/now-chromium-picolinate-200.jpg</t>
         </is>
       </c>
       <c r="Y48" s="12" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="X49" s="14" t="inlineStr">
         <is>
-          <t>images/now-milk-thistle-extract-300mg-50.jpg</t>
+          <t>images/now-milk-thistle-300.jpg</t>
         </is>
       </c>
       <c r="Y49" s="12" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="X50" s="14" t="inlineStr">
         <is>
-          <t>images/now-collagen-peptides-powder-227g.jpg</t>
+          <t>images/now-collagen-peptides-powder.jpg</t>
         </is>
       </c>
       <c r="Y50" s="12" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="X51" s="14" t="inlineStr">
         <is>
-          <t>images/now-uc-ii-type-2-collagen-40mg.jpg</t>
+          <t>images/now-uc-ii-collagen.jpg</t>
         </is>
       </c>
       <c r="Y51" s="12" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="X52" s="14" t="inlineStr">
         <is>
-          <t>images/now-alpha-lipoic-acid-100mg-60.jpg</t>
+          <t>images/now-alpha-lipoic-acid.jpg</t>
         </is>
       </c>
       <c r="Y52" s="12" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="X53" s="14" t="inlineStr">
         <is>
-          <t>images/now-folic-acid-800mcg-250-tabs.jpg</t>
+          <t>images/now-folic-acid-800.jpg</t>
         </is>
       </c>
       <c r="Y53" s="12" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="X54" s="14" t="inlineStr">
         <is>
-          <t>images/now-methyl-folate-1000mcg-90-tabs.jpg</t>
+          <t>images/now-methyl-folate-1000.jpg</t>
         </is>
       </c>
       <c r="Y54" s="12" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="X55" s="14" t="inlineStr">
         <is>
-          <t>images/now-5-htp-50mg-vcaps.jpg</t>
+          <t>images/now-5-htp-50.jpg</t>
         </is>
       </c>
       <c r="Y55" s="12" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="X56" s="14" t="inlineStr">
         <is>
-          <t>images/now-ginkgo-biloba-120mg-50-vcaps.jpg</t>
+          <t>images/now-ginkgo-biloba-120.jpg</t>
         </is>
       </c>
       <c r="Y56" s="12" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="X57" s="14" t="inlineStr">
         <is>
-          <t>images/now-berberine-glucose-support-90.jpg</t>
+          <t>images/now-berberine-glucose.jpg</t>
         </is>
       </c>
       <c r="Y57" s="12" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="X58" s="14" t="inlineStr">
         <is>
-          <t>images/now-echinacea-purpurea-400mg-100.jpg</t>
+          <t>images/now-echinacea-400.jpg</t>
         </is>
       </c>
       <c r="Y58" s="12" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="X59" s="14" t="inlineStr">
         <is>
-          <t>images/now-gaba-500mg-100-vcaps.jpg</t>
+          <t>images/now-gaba-500.jpg</t>
         </is>
       </c>
       <c r="Y59" s="12" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="X60" s="14" t="inlineStr">
         <is>
-          <t>images/now-paba-500mg-100-caps.jpg</t>
+          <t>images/now-paba-500.jpg</t>
         </is>
       </c>
       <c r="Y60" s="12" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="X61" s="14" t="inlineStr">
         <is>
-          <t>images/now-kelp-caps-325mcg-250.jpg</t>
+          <t>images/now-kelp-325.jpg</t>
         </is>
       </c>
       <c r="Y61" s="12" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="X62" s="14" t="inlineStr">
         <is>
-          <t>images/now-liquid-chlorophyll-mint-473ml.jpg</t>
+          <t>images/now-liquid-chlorophyll.jpg</t>
         </is>
       </c>
       <c r="Y62" s="12" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="X63" s="14" t="inlineStr">
         <is>
-          <t>images/now-kid-vits-berry-lemonade-120.jpg</t>
+          <t>images/now-kids-vits-berry.jpg</t>
         </is>
       </c>
       <c r="Y63" s="12" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="X64" s="14" t="inlineStr">
         <is>
-          <t>images/now-kids-elderberry-liquid-237ml.jpg</t>
+          <t>images/now-kids-elderberry.jpg</t>
         </is>
       </c>
       <c r="Y64" s="12" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="X65" s="14" t="inlineStr">
         <is>
-          <t>images/now-kid-cal-chewable-100-loz.jpg</t>
+          <t>images/now-kid-cal.jpg</t>
         </is>
       </c>
       <c r="Y65" s="12" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="X66" s="14" t="inlineStr">
         <is>
-          <t>images/now-kids-dha-100mg-chewable-60.jpg</t>
+          <t>images/now-kids-dha-chewable.jpg</t>
         </is>
       </c>
       <c r="Y66" s="12" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="X67" s="14" t="inlineStr">
         <is>
-          <t>images/now-essential-oil-rosemary-30ml.jpg</t>
+          <t>images/now-eo-rosemary.jpg</t>
         </is>
       </c>
       <c r="Y67" s="12" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="X68" s="14" t="inlineStr">
         <is>
-          <t>images/now-essential-oil-tea-tree-30ml.jpg</t>
+          <t>images/now-eo-tea-tree.jpg</t>
         </is>
       </c>
       <c r="Y68" s="12" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="X69" s="14" t="inlineStr">
         <is>
-          <t>images/now-essential-oil-eucalyptus-30ml.jpg</t>
+          <t>images/now-eo-eucalyptus.jpg</t>
         </is>
       </c>
       <c r="Y69" s="12" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="X70" s="14" t="inlineStr">
         <is>
-          <t>images/cgn-gold-c-1000mg-60-vcaps.jpg</t>
+          <t>images/cgn-gold-c-1000.jpg</t>
         </is>
       </c>
       <c r="Y70" s="12" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="X71" s="14" t="inlineStr">
         <is>
-          <t>images/cgn-vitamin-d3-5000iu-90.jpg</t>
+          <t>images/cgn-vitamin-d3-5000.jpg</t>
         </is>
       </c>
       <c r="Y71" s="12" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="X72" s="14" t="inlineStr">
         <is>
-          <t>images/cgn-vitamin-d3-babies-liquid-10ml.jpg</t>
+          <t>images/cgn-vitamin-d3-babies.jpg</t>
         </is>
       </c>
       <c r="Y72" s="12" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="X73" s="14" t="inlineStr">
         <is>
-          <t>images/cgn-lactobif-5-billion-60-vcaps.jpg</t>
+          <t>images/cgn-lactobif-5.jpg</t>
         </is>
       </c>
       <c r="Y73" s="12" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="X74" s="14" t="inlineStr">
         <is>
-          <t>images/cgn-lactobif-30-billion-60-vcaps.jpg</t>
+          <t>images/cgn-lactobif-30.jpg</t>
         </is>
       </c>
       <c r="Y74" s="12" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="X75" s="14" t="inlineStr">
         <is>
-          <t>images/cgn-collagenup-206g.jpg</t>
+          <t>images/cgn-collagenup-206.jpg</t>
         </is>
       </c>
       <c r="Y75" s="12" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="X76" s="14" t="inlineStr">
         <is>
-          <t>images/cgn-collagenup-464g.jpg</t>
+          <t>images/cgn-collagenup-464.jpg</t>
         </is>
       </c>
       <c r="Y76" s="12" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="X77" s="14" t="inlineStr">
         <is>
-          <t>images/np-hema-plex-slow-release-30-tabs.jpg</t>
+          <t>images/np-hema-plex-slow-30.jpg</t>
         </is>
       </c>
       <c r="Y77" s="12" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="X78" s="14" t="inlineStr">
         <is>
-          <t>images/np-hema-plex-iron-fast-acting-60-caps.jpg</t>
+          <t>images/np-hema-plex-fast-60.jpg</t>
         </is>
       </c>
       <c r="Y78" s="12" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="X79" s="14" t="inlineStr">
         <is>
-          <t>images/np-hema-plex-slow-release-60-tabs.jpg</t>
+          <t>images/np-hema-plex-slow-60.jpg</t>
         </is>
       </c>
       <c r="Y79" s="12" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="X80" s="14" t="inlineStr">
         <is>
-          <t>images/np-hema-plex-iron-chewables-60.jpg</t>
+          <t>images/np-hema-plex-chewable.jpg</t>
         </is>
       </c>
       <c r="Y80" s="12" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="X81" s="14" t="inlineStr">
         <is>
-          <t>images/np-hema-plex-liquid-iron-250ml.jpg</t>
+          <t>images/np-hema-plex-liquid.jpg</t>
         </is>
       </c>
       <c r="Y81" s="12" t="inlineStr">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="X82" s="14" t="inlineStr">
         <is>
-          <t>images/np-collagen-peptides-294g.jpg</t>
+          <t>images/np-collagen-peptides-294.jpg</t>
         </is>
       </c>
       <c r="Y82" s="12" t="inlineStr">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="X83" s="14" t="inlineStr">
         <is>
-          <t>images/np-collagen-peptides-vanilla-364g.jpg</t>
+          <t>images/np-collagen-vanilla-364.jpg</t>
         </is>
       </c>
       <c r="Y83" s="12" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="X84" s="14" t="inlineStr">
         <is>
-          <t>images/np-collagen-peptides-chocolate-378g.jpg</t>
+          <t>images/np-collagen-chocolate-378.jpg</t>
         </is>
       </c>
       <c r="Y84" s="12" t="inlineStr">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="X85" s="14" t="inlineStr">
         <is>
-          <t>images/np-magkidz-magnesium-cherry-90-tabs.jpg</t>
+          <t>images/np-magkidz-chewable-90.jpg</t>
         </is>
       </c>
       <c r="Y85" s="12" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="X86" s="14" t="inlineStr">
         <is>
-          <t>images/np-magkidz-magnesium-cherry-171g.jpg</t>
+          <t>images/np-magkidz-powder-171.jpg</t>
         </is>
       </c>
       <c r="Y86" s="12" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="X87" s="14" t="inlineStr">
         <is>
-          <t>images/np-animal-parade-gold-60-tabs.jpg</t>
+          <t>images/np-animal-parade-gold-60.jpg</t>
         </is>
       </c>
       <c r="Y87" s="12" t="inlineStr">
@@ -11519,7 +11519,7 @@
       </c>
       <c r="X88" s="14" t="inlineStr">
         <is>
-          <t>images/np-animal-parade-multivitamin-90-tabs.jpg</t>
+          <t>images/np-animal-parade-90.jpg</t>
         </is>
       </c>
       <c r="Y88" s="12" t="inlineStr">
@@ -11636,7 +11636,7 @@
       </c>
       <c r="X89" s="14" t="inlineStr">
         <is>
-          <t>images/np-animal-parade-gold-120-tabs.jpg</t>
+          <t>images/np-animal-parade-gold-120.jpg</t>
         </is>
       </c>
       <c r="Y89" s="12" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="X90" s="14" t="inlineStr">
         <is>
-          <t>images/np-animal-parade-multivitamin-180-tabs.jpg</t>
+          <t>images/np-animal-parade-180.jpg</t>
         </is>
       </c>
       <c r="Y90" s="12" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="X91" s="14" t="inlineStr">
         <is>
-          <t>images/np-animal-parade-watermelon-180-tabs.jpg</t>
+          <t>images/np-animal-parade-watermelon.jpg</t>
         </is>
       </c>
       <c r="Y91" s="12" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="X92" s="14" t="inlineStr">
         <is>
-          <t>images/childlife-liquid-vitamin-d3-30ml.jpg</t>
+          <t>images/childlife-vitamin-d3.jpg</t>
         </is>
       </c>
       <c r="Y92" s="12" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="X93" s="14" t="inlineStr">
         <is>
-          <t>images/childlife-liquid-vitamin-c-118ml.jpg</t>
+          <t>images/childlife-vitamin-c.jpg</t>
         </is>
       </c>
       <c r="Y93" s="12" t="inlineStr">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="X94" s="14" t="inlineStr">
         <is>
-          <t>images/childlife-liquid-zinc-plus-118ml.jpg</t>
+          <t>images/childlife-zinc-plus.jpg</t>
         </is>
       </c>
       <c r="Y94" s="12" t="inlineStr">
@@ -12338,7 +12338,7 @@
       </c>
       <c r="X95" s="14" t="inlineStr">
         <is>
-          <t>images/childlife-liquid-iron-118ml.jpg</t>
+          <t>images/childlife-liquid-iron.jpg</t>
         </is>
       </c>
       <c r="Y95" s="12" t="inlineStr">
@@ -12455,7 +12455,7 @@
       </c>
       <c r="X96" s="14" t="inlineStr">
         <is>
-          <t>images/childlife-liquid-calcium-magnesium-473ml.jpg</t>
+          <t>images/childlife-calcium-magnesium.jpg</t>
         </is>
       </c>
       <c r="Y96" s="12" t="inlineStr">
@@ -12572,7 +12572,7 @@
       </c>
       <c r="X97" s="14" t="inlineStr">
         <is>
-          <t>images/childlife-liquid-multivitamin-237ml.jpg</t>
+          <t>images/childlife-multivitamin.jpg</t>
         </is>
       </c>
       <c r="Y97" s="12" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="X98" s="14" t="inlineStr">
         <is>
-          <t>images/childlife-liquid-echinacea-30ml.jpg</t>
+          <t>images/childlife-echinacea.jpg</t>
         </is>
       </c>
       <c r="Y98" s="12" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="X99" s="14" t="inlineStr">
         <is>
-          <t>images/life-extension-two-per-day-60-caps.jpg</t>
+          <t>images/le-two-per-day-60.jpg</t>
         </is>
       </c>
       <c r="Y99" s="12" t="inlineStr">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="X100" s="14" t="inlineStr">
         <is>
-          <t>images/life-extension-two-per-day-120-caps.jpg</t>
+          <t>images/le-two-per-day-120.jpg</t>
         </is>
       </c>
       <c r="Y100" s="12" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="X101" s="14" t="inlineStr">
         <is>
-          <t>images/life-extension-bioactive-b-complex-60.jpg</t>
+          <t>images/le-bioactive-b-complex.jpg</t>
         </is>
       </c>
       <c r="Y101" s="12" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="X102" s="14" t="inlineStr">
         <is>
-          <t>images/life-extension-neuro-mag-powder-93g.jpg</t>
+          <t>images/le-neuro-mag-powder.jpg</t>
         </is>
       </c>
       <c r="Y102" s="12" t="inlineStr">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="X103" s="14" t="inlineStr">
         <is>
-          <t>images/life-extension-neuro-mag-90-vegcaps.jpg</t>
+          <t>images/le-neuro-mag-caps.jpg</t>
         </is>
       </c>
       <c r="Y103" s="12" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="X104" s="14" t="inlineStr">
         <is>
-          <t>images/life-extension-inositol-1000mg-360.jpg</t>
+          <t>images/le-inositol-1000.jpg</t>
         </is>
       </c>
       <c r="Y104" s="12" t="inlineStr">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="X105" s="14" t="inlineStr">
         <is>
-          <t>images/life-extension-super-selenium-complex-100.jpg</t>
+          <t>images/le-super-selenium.jpg</t>
         </is>
       </c>
       <c r="Y105" s="12" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="X106" s="14" t="inlineStr">
         <is>
-          <t>images/natures-answer-liquid-magnesium-480ml.jpg</t>
+          <t>images/na-liquid-magnesium.jpg</t>
         </is>
       </c>
       <c r="Y106" s="12" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="X107" s="14" t="inlineStr">
         <is>
-          <t>images/natures-answer-liquid-vitamin-c-240ml.jpg</t>
+          <t>images/na-liquid-vitamin-c.jpg</t>
         </is>
       </c>
       <c r="Y107" s="12" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="X108" s="14" t="inlineStr">
         <is>
-          <t>images/natures-answer-liquid-b-complex-240ml.jpg</t>
+          <t>images/na-liquid-b-complex.jpg</t>
         </is>
       </c>
       <c r="Y108" s="12" t="inlineStr">
@@ -13962,7 +13962,7 @@
       </c>
       <c r="X109" s="14" t="inlineStr">
         <is>
-          <t>images/natures-answer-liquid-chlorophyll-480ml.jpg</t>
+          <t>images/na-liquid-chlorophyll.jpg</t>
         </is>
       </c>
       <c r="Y109" s="12" t="inlineStr">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="X110" s="14" t="inlineStr">
         <is>
-          <t>images/solaray-magnesium-citrate-400mg-90.jpg</t>
+          <t>images/solaray-mag-citrate-90.jpg</t>
         </is>
       </c>
       <c r="Y110" s="12" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="X111" s="14" t="inlineStr">
         <is>
-          <t>images/solaray-magnesium-citrate-400mg-180.jpg</t>
+          <t>images/solaray-mag-citrate-180.jpg</t>
         </is>
       </c>
       <c r="Y111" s="12" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="X112" s="14" t="inlineStr">
         <is>
-          <t>images/solaray-zinc-citrate-50mg-60.jpg</t>
+          <t>images/solaray-zinc-citrate-50.jpg</t>
         </is>
       </c>
       <c r="Y112" s="12" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="X113" s="14" t="inlineStr">
         <is>
-          <t>images/solaray-magnesium-glycinate-350mg-120.jpg</t>
+          <t>images/solaray-mag-glycinate-120.jpg</t>
         </is>
       </c>
       <c r="Y113" s="12" t="inlineStr">
@@ -14569,7 +14569,7 @@
       </c>
       <c r="X114" s="14" t="inlineStr">
         <is>
-          <t>images/solaray-magnesium-glycinate-350mg-240.jpg</t>
+          <t>images/solaray-mag-glycinate-240.jpg</t>
         </is>
       </c>
       <c r="Y114" s="12" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="X115" s="14" t="inlineStr">
         <is>
-          <t>images/solaray-vitamin-d3-k2-60-vegcaps.jpg</t>
+          <t>images/solaray-d3-k2-60.jpg</t>
         </is>
       </c>
       <c r="Y115" s="12" t="inlineStr">
@@ -14815,7 +14815,7 @@
       </c>
       <c r="X116" s="14" t="inlineStr">
         <is>
-          <t>images/solaray-vitamin-d3-k2-120-vegcaps.jpg</t>
+          <t>images/solaray-d3-k2-120.jpg</t>
         </is>
       </c>
       <c r="Y116" s="12" t="inlineStr">
@@ -14938,7 +14938,7 @@
       </c>
       <c r="X117" s="14" t="inlineStr">
         <is>
-          <t>images/solaray-selenium-200mcg-90-vegcaps.jpg</t>
+          <t>images/solaray-selenium-200.jpg</t>
         </is>
       </c>
       <c r="Y117" s="12" t="inlineStr">
@@ -15061,7 +15061,7 @@
       </c>
       <c r="X118" s="14" t="inlineStr">
         <is>
-          <t>images/solaray-vital-extracts-artichoke-600mg.jpg</t>
+          <t>images/solaray-artichoke.jpg</t>
         </is>
       </c>
       <c r="Y118" s="12" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="X119" s="14" t="inlineStr">
         <is>
-          <t>images/solaray-l-lysine-monolaurin-60.jpg</t>
+          <t>images/solaray-lysine-monolaurin.jpg</t>
         </is>
       </c>
       <c r="Y119" s="12" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="X120" s="14" t="inlineStr">
         <is>
-          <t>images/solaray-chromium-picolinate-200mcg-100.jpg</t>
+          <t>images/solaray-chromium-200.jpg</t>
         </is>
       </c>
       <c r="Y120" s="12" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="X121" s="14" t="inlineStr">
         <is>
-          <t>images/solaray-berberine-curcumin-60-vegcaps.jpg</t>
+          <t>images/solaray-berberine-curcumin.jpg</t>
         </is>
       </c>
       <c r="Y121" s="12" t="inlineStr">
@@ -15545,7 +15545,7 @@
       </c>
       <c r="X122" s="14" t="inlineStr">
         <is>
-          <t>images/lifeflo-liquid-iodine-plus-59ml.jpg</t>
+          <t>images/lifeflo-liquid-iodine.jpg</t>
         </is>
       </c>
       <c r="Y122" s="12" t="inlineStr">
@@ -15664,7 +15664,7 @@
       <c r="W123" s="12" t="n"/>
       <c r="X123" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-biotin-5000mcg-60-caps.jpg</t>
+          <t>images/ecovita-biotin-5000.jpg</t>
         </is>
       </c>
       <c r="Y123" s="12" t="inlineStr">
@@ -15779,7 +15779,7 @@
       <c r="W124" s="12" t="n"/>
       <c r="X124" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-omega-3-epa540-dha360-30.jpg</t>
+          <t>images/ecovita-omega3-30.jpg</t>
         </is>
       </c>
       <c r="Y124" s="12" t="inlineStr">
@@ -15894,7 +15894,7 @@
       <c r="W125" s="12" t="n"/>
       <c r="X125" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-omega-3-epa540-dha360-100.jpg</t>
+          <t>images/ecovita-omega3-100.jpg</t>
         </is>
       </c>
       <c r="Y125" s="12" t="inlineStr">
@@ -16007,7 +16007,7 @@
       <c r="W126" s="12" t="n"/>
       <c r="X126" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-lions-mane-mushroom-90-caps.jpg</t>
+          <t>images/ecovita-lions-mane.jpg</t>
         </is>
       </c>
       <c r="Y126" s="12" t="inlineStr">
@@ -16122,7 +16122,7 @@
       <c r="W127" s="12" t="n"/>
       <c r="X127" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-coenzyme-q10-100mg-60.jpg</t>
+          <t>images/ecovita-coq10-100.jpg</t>
         </is>
       </c>
       <c r="Y127" s="12" t="inlineStr">
@@ -16231,7 +16231,7 @@
       <c r="W128" s="12" t="n"/>
       <c r="X128" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-calcium-zinc-magnesium-d3-b6-100.jpg</t>
+          <t>images/ecovita-calcium-zinc-mag.jpg</t>
         </is>
       </c>
       <c r="Y128" s="12" t="inlineStr">
@@ -16346,7 +16346,7 @@
       <c r="W129" s="12" t="n"/>
       <c r="X129" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-calcium-citrate-210mg-90.jpg</t>
+          <t>images/ecovita-calcium-citrate.jpg</t>
         </is>
       </c>
       <c r="Y129" s="12" t="inlineStr">
@@ -16459,7 +16459,7 @@
       <c r="W130" s="12" t="n"/>
       <c r="X130" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-magnesium-citrate-b6-60.jpg</t>
+          <t>images/ecovita-mag-citrate-b6.jpg</t>
         </is>
       </c>
       <c r="Y130" s="12" t="inlineStr">
@@ -16578,7 +16578,7 @@
       <c r="W131" s="12" t="n"/>
       <c r="X131" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-vitamin-d3-k2-2000-50-100.jpg</t>
+          <t>images/ecovita-d3-k2-2000.jpg</t>
         </is>
       </c>
       <c r="Y131" s="12" t="inlineStr">
@@ -16693,7 +16693,7 @@
       <c r="W132" s="12" t="n"/>
       <c r="X132" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-vitamin-d3-2000me-100.jpg</t>
+          <t>images/ecovita-d3-2000.jpg</t>
         </is>
       </c>
       <c r="Y132" s="12" t="inlineStr">
@@ -16808,7 +16808,7 @@
       <c r="W133" s="12" t="n"/>
       <c r="X133" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-vitamin-d3-5000me-100.jpg</t>
+          <t>images/ecovita-d3-5000.jpg</t>
         </is>
       </c>
       <c r="Y133" s="12" t="inlineStr">
@@ -16923,7 +16923,7 @@
       <c r="W134" s="12" t="n"/>
       <c r="X134" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-vitamin-d3-10000me-100.jpg</t>
+          <t>images/ecovita-d3-10000.jpg</t>
         </is>
       </c>
       <c r="Y134" s="12" t="inlineStr">
@@ -17042,7 +17042,7 @@
       <c r="W135" s="12" t="n"/>
       <c r="X135" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-myo-inositol-500mg-100.jpg</t>
+          <t>images/ecovita-myo-inositol.jpg</t>
         </is>
       </c>
       <c r="Y135" s="12" t="inlineStr">
@@ -17161,7 +17161,7 @@
       <c r="W136" s="12" t="n"/>
       <c r="X136" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-selenium-100mcg-90.jpg</t>
+          <t>images/ecovita-selenium-100.jpg</t>
         </is>
       </c>
       <c r="Y136" s="12" t="inlineStr">
@@ -17280,7 +17280,7 @@
       <c r="W137" s="12" t="n"/>
       <c r="X137" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-sunflower-lecithin-1000mg-100.jpg</t>
+          <t>images/ecovita-sunflower-lecithin.jpg</t>
         </is>
       </c>
       <c r="Y137" s="12" t="inlineStr">
@@ -17399,7 +17399,7 @@
       <c r="W138" s="12" t="n"/>
       <c r="X138" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-zinc-picolinate-125mg-60.jpg</t>
+          <t>images/ecovita-zinc-picolinate.jpg</t>
         </is>
       </c>
       <c r="Y138" s="12" t="inlineStr">
@@ -17518,7 +17518,7 @@
       <c r="W139" s="12" t="n"/>
       <c r="X139" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-vitamin-c-500mg-100.jpg</t>
+          <t>images/ecovita-vitamin-c-500.jpg</t>
         </is>
       </c>
       <c r="Y139" s="12" t="inlineStr">
@@ -17631,7 +17631,7 @@
       <c r="W140" s="12" t="n"/>
       <c r="X140" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-marine-collagen-240g.jpg</t>
+          <t>images/ecovita-marine-collagen.jpg</t>
         </is>
       </c>
       <c r="Y140" s="12" t="inlineStr">
@@ -17750,7 +17750,7 @@
       <c r="W141" s="12" t="n"/>
       <c r="X141" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-type-1-3-collagen-430mg-60.jpg</t>
+          <t>images/ecovita-collagen-1-3.jpg</t>
         </is>
       </c>
       <c r="Y141" s="12" t="inlineStr">
@@ -17863,7 +17863,7 @@
       <c r="W142" s="12" t="n"/>
       <c r="X142" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-men-active-multivitamin-90.jpg</t>
+          <t>images/ecovita-men-active.jpg</t>
         </is>
       </c>
       <c r="Y142" s="12" t="inlineStr">
@@ -17976,7 +17976,7 @@
       <c r="W143" s="12" t="n"/>
       <c r="X143" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-women-balance-multivitamin-90.jpg</t>
+          <t>images/ecovita-women-balance.jpg</t>
         </is>
       </c>
       <c r="Y143" s="12" t="inlineStr">
@@ -18095,7 +18095,7 @@
       <c r="W144" s="12" t="n"/>
       <c r="X144" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-l-carnitine-850mg-90.jpg</t>
+          <t>images/ecovita-l-carnitine.jpg</t>
         </is>
       </c>
       <c r="Y144" s="12" t="inlineStr">
@@ -18214,7 +18214,7 @@
       <c r="W145" s="12" t="n"/>
       <c r="X145" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-berberine-500mg-60.jpg</t>
+          <t>images/ecovita-berberine-500.jpg</t>
         </is>
       </c>
       <c r="Y145" s="12" t="inlineStr">
@@ -18333,7 +18333,7 @@
       <c r="W146" s="12" t="n"/>
       <c r="X146" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-glucosamine-chondroitin-msm-120.jpg</t>
+          <t>images/ecovita-glucosamine-msm.jpg</t>
         </is>
       </c>
       <c r="Y146" s="12" t="inlineStr">
@@ -18446,7 +18446,7 @@
       <c r="W147" s="12" t="n"/>
       <c r="X147" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-b-complex-60-caps.jpg</t>
+          <t>images/ecovita-b-complex.jpg</t>
         </is>
       </c>
       <c r="Y147" s="12" t="inlineStr">
@@ -18565,7 +18565,7 @@
       <c r="W148" s="12" t="n"/>
       <c r="X148" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-iron-chelate-40mg-60.jpg</t>
+          <t>images/ecovita-iron-chelate.jpg</t>
         </is>
       </c>
       <c r="Y148" s="12" t="inlineStr">
@@ -18680,7 +18680,7 @@
       <c r="W149" s="12" t="n"/>
       <c r="X149" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-folic-acid-400mcg-60.jpg</t>
+          <t>images/ecovita-folic-acid.jpg</t>
         </is>
       </c>
       <c r="Y149" s="12" t="inlineStr">
@@ -18795,7 +18795,7 @@
       <c r="W150" s="12" t="n"/>
       <c r="X150" s="14" t="inlineStr">
         <is>
-          <t>images/ecovita-chromium-picolinate-200mcg-60.jpg</t>
+          <t>images/ecovita-chromium-200.jpg</t>
         </is>
       </c>
       <c r="Y150" s="12" t="inlineStr">
@@ -18914,7 +18914,7 @@
       <c r="W151" s="12" t="n"/>
       <c r="X151" s="14" t="inlineStr">
         <is>
-          <t>images/vita-garden-biotin-5000mcg-30.jpg</t>
+          <t>images/vg-biotin-5000.jpg</t>
         </is>
       </c>
       <c r="Y151" s="12" t="inlineStr">
@@ -19029,7 +19029,7 @@
       <c r="W152" s="12" t="n"/>
       <c r="X152" s="14" t="inlineStr">
         <is>
-          <t>images/vita-garden-omega-3-fish-oil-60.jpg</t>
+          <t>images/vg-omega-3.jpg</t>
         </is>
       </c>
       <c r="Y152" s="12" t="inlineStr">
@@ -19148,7 +19148,7 @@
       <c r="W153" s="12" t="n"/>
       <c r="X153" s="14" t="inlineStr">
         <is>
-          <t>images/vita-garden-magnesium-b6-60.jpg</t>
+          <t>images/vg-magnesium-b6.jpg</t>
         </is>
       </c>
       <c r="Y153" s="12" t="inlineStr">
@@ -19263,7 +19263,7 @@
       <c r="W154" s="12" t="n"/>
       <c r="X154" s="14" t="inlineStr">
         <is>
-          <t>images/vita-garden-calcium-citrate-210mg-60.jpg</t>
+          <t>images/vg-calcium-citrate.jpg</t>
         </is>
       </c>
       <c r="Y154" s="12" t="inlineStr">
@@ -19378,7 +19378,7 @@
       <c r="W155" s="12" t="n"/>
       <c r="X155" s="14" t="inlineStr">
         <is>
-          <t>images/vita-garden-vitamin-d3-2000me-60.jpg</t>
+          <t>images/vg-vitamin-d3-2000.jpg</t>
         </is>
       </c>
       <c r="Y155" s="12" t="inlineStr">
@@ -19497,7 +19497,7 @@
       <c r="W156" s="12" t="n"/>
       <c r="X156" s="14" t="inlineStr">
         <is>
-          <t>images/vita-garden-myo-inositol-500mg-60.jpg</t>
+          <t>images/vg-myo-inositol.jpg</t>
         </is>
       </c>
       <c r="Y156" s="12" t="inlineStr">
@@ -19616,7 +19616,7 @@
       <c r="W157" s="12" t="n"/>
       <c r="X157" s="14" t="inlineStr">
         <is>
-          <t>images/vita-garden-selenium-100mcg-60.jpg</t>
+          <t>images/vg-selenium-100.jpg</t>
         </is>
       </c>
       <c r="Y157" s="12" t="inlineStr">
@@ -19735,7 +19735,7 @@
       <c r="W158" s="12" t="n"/>
       <c r="X158" s="14" t="inlineStr">
         <is>
-          <t>images/vita-garden-zinc-picolinate-125mg-60.jpg</t>
+          <t>images/vg-zinc-picolinate.jpg</t>
         </is>
       </c>
       <c r="Y158" s="12" t="inlineStr">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="X159" s="14" t="inlineStr">
         <is>
-          <t>images/now-vitamin-a-10000iu-100-sgels.jpg</t>
+          <t>images/now-vitamin-a-10000.jpg</t>
         </is>
       </c>
       <c r="Y159" s="12" t="inlineStr">
@@ -19967,7 +19967,7 @@
       </c>
       <c r="X160" s="14" t="inlineStr">
         <is>
-          <t>images/now-psyllium-husk-whole.jpg</t>
+          <t>images/now-psyllium-husk.jpg</t>
         </is>
       </c>
       <c r="Y160" s="12" t="inlineStr">
@@ -20090,7 +20090,7 @@
       </c>
       <c r="X161" s="14" t="inlineStr">
         <is>
-          <t>images/now-biotin-10000mcg-120-vcaps.jpg</t>
+          <t>images/now-biotin-10000.jpg</t>
         </is>
       </c>
       <c r="Y161" s="12" t="inlineStr">
@@ -20209,7 +20209,7 @@
       </c>
       <c r="X162" s="14" t="inlineStr">
         <is>
-          <t>images/now-propolis-1500-300mg-100-caps.jpg</t>
+          <t>images/now-propolis-1500.jpg</t>
         </is>
       </c>
       <c r="Y162" s="12" t="inlineStr">
@@ -20332,7 +20332,7 @@
       </c>
       <c r="X163" s="14" t="inlineStr">
         <is>
-          <t>images/now-probiotic-10-25-billion-50-vcaps.jpg</t>
+          <t>images/now-probiotic-10.jpg</t>
         </is>
       </c>
       <c r="Y163" s="12" t="inlineStr">
@@ -20455,7 +20455,7 @@
       </c>
       <c r="X164" s="14" t="inlineStr">
         <is>
-          <t>images/now-silymarin-milk-thistle-turmeric-150mg-60-vcaps.jpg</t>
+          <t>images/now-milk-thistle-turmeric.jpg</t>
         </is>
       </c>
       <c r="Y164" s="12" t="inlineStr">
@@ -20574,7 +20574,7 @@
       </c>
       <c r="X165" s="14" t="inlineStr">
         <is>
-          <t>images/now-glutathione-250mg-60-vcaps.jpg</t>
+          <t>images/now-glutathione-250.jpg</t>
         </is>
       </c>
       <c r="Y165" s="12" t="inlineStr">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="X166" s="14" t="inlineStr">
         <is>
-          <t>images/now-kids-liquid-echinacea-orange-59ml.jpg</t>
+          <t>images/now-kids-liquid-echinacea.jpg</t>
         </is>
       </c>
       <c r="Y166" s="12" t="inlineStr">
@@ -20810,7 +20810,7 @@
       </c>
       <c r="X167" s="14" t="inlineStr">
         <is>
-          <t>images/biomagic-iodine-25ml.jpg</t>
+          <t>images/biomagic-iodine.jpg</t>
         </is>
       </c>
       <c r="Y167" s="12" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="X168" s="14" t="inlineStr">
         <is>
-          <t>images/biomagic-iodine-selenium-25ml.jpg</t>
+          <t>images/biomagic-iodine-selenium.jpg</t>
         </is>
       </c>
       <c r="Y168" s="12" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Yoshlik Yu Distribution\Web-service-catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BD0B7B-C49B-4C7B-A22D-997A7C59DCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD4645E1-C1D9-411D-B5E3-607370818EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13667" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Yoshlik Yu Distribution\Web-service-catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967973F6-ACDB-45B8-A1B1-6F361B1899A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EE3662-35CD-4173-BDD3-67343EF96A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13667" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4895,12 +4895,6 @@
     <t>solaray-magnesium-citrate-400mg-180</t>
   </si>
   <si>
-    <t>Solaray Magnesium Citrate 400 мг, 180 капсул</t>
-  </si>
-  <si>
-    <t>Solaray Magnesium Citrate 400 mg, 180 kapsula</t>
-  </si>
-  <si>
     <t>Цитрат магния, большая упаковка на длительный курс.</t>
   </si>
   <si>
@@ -7799,6 +7793,12 @@
   </si>
   <si>
     <t>images/ecovita-chromium-picolinate-200mcg-60.jpg</t>
+  </si>
+  <si>
+    <t>Solaray Magnesium Citrate 400 мг, 180/90 капсул</t>
+  </si>
+  <si>
+    <t>Solaray Magnesium Citrate 400 mg, 180/90  kapsula</t>
   </si>
 </sst>
 </file>
@@ -8639,39 +8639,39 @@
         <v>56</v>
       </c>
       <c r="Z1" s="17" t="s">
+        <v>2257</v>
+      </c>
+      <c r="AA1" s="17" t="s">
+        <v>2258</v>
+      </c>
+      <c r="AB1" s="17" t="s">
         <v>2259</v>
       </c>
-      <c r="AA1" s="17" t="s">
+      <c r="AC1" s="18" t="s">
         <v>2260</v>
       </c>
-      <c r="AB1" s="17" t="s">
+      <c r="AD1" s="17" t="s">
         <v>2261</v>
       </c>
-      <c r="AC1" s="18" t="s">
+      <c r="AE1" s="17" t="s">
         <v>2262</v>
-      </c>
-      <c r="AD1" s="17" t="s">
-        <v>2263</v>
-      </c>
-      <c r="AE1" s="17" t="s">
-        <v>2264</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="78.05" customHeight="1">
       <c r="A2" s="12" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>2162</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>2163</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>2164</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>2165</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>2166</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>2167</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>172</v>
@@ -8690,43 +8690,43 @@
         <v>1</v>
       </c>
       <c r="L2" s="12" t="s">
+        <v>2166</v>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>2167</v>
+      </c>
+      <c r="N2" s="12" t="s">
         <v>2168</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="O2" s="14" t="s">
         <v>2169</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="P2" s="12" t="s">
         <v>2170</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="Q2" s="14" t="s">
         <v>2171</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="R2" s="12" t="s">
         <v>2172</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="S2" s="14" t="s">
         <v>2173</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="T2" s="12" t="s">
         <v>2174</v>
       </c>
-      <c r="S2" s="14" t="s">
+      <c r="U2" s="14" t="s">
         <v>2175</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="V2" s="12" t="s">
         <v>2176</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="W2" s="12" t="s">
         <v>2177</v>
       </c>
-      <c r="V2" s="12" t="s">
+      <c r="X2" s="14" t="s">
         <v>2178</v>
-      </c>
-      <c r="W2" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X2" s="14" t="s">
-        <v>2180</v>
       </c>
       <c r="Y2" s="12" t="s">
         <v>77</v>
@@ -8734,19 +8734,19 @@
     </row>
     <row r="3" spans="1:31" ht="78.05" customHeight="1">
       <c r="A3" s="12" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>2180</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>2181</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>2182</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>2183</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>2184</v>
-      </c>
       <c r="E3" s="12" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>172</v>
@@ -8763,43 +8763,43 @@
         <v>1</v>
       </c>
       <c r="L3" s="12" t="s">
+        <v>2183</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>2184</v>
+      </c>
+      <c r="N3" s="12" t="s">
         <v>2185</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="O3" s="14" t="s">
         <v>2186</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="P3" s="12" t="s">
         <v>2187</v>
       </c>
-      <c r="O3" s="14" t="s">
+      <c r="Q3" s="14" t="s">
         <v>2188</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="R3" s="12" t="s">
         <v>2189</v>
       </c>
-      <c r="Q3" s="14" t="s">
+      <c r="S3" s="14" t="s">
         <v>2190</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="T3" s="12" t="s">
         <v>2191</v>
       </c>
-      <c r="S3" s="14" t="s">
+      <c r="U3" s="14" t="s">
         <v>2192</v>
       </c>
-      <c r="T3" s="12" t="s">
+      <c r="V3" s="12" t="s">
+        <v>2176</v>
+      </c>
+      <c r="W3" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X3" s="14" t="s">
         <v>2193</v>
-      </c>
-      <c r="U3" s="14" t="s">
-        <v>2194</v>
-      </c>
-      <c r="V3" s="12" t="s">
-        <v>2178</v>
-      </c>
-      <c r="W3" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X3" s="14" t="s">
-        <v>2195</v>
       </c>
       <c r="Y3" s="12" t="s">
         <v>77</v>
@@ -8959,10 +8959,10 @@
         <v>924</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>2390</v>
+        <v>2388</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>925</v>
@@ -9184,16 +9184,16 @@
     </row>
     <row r="9" spans="1:31" ht="78.05" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>925</v>
@@ -9221,16 +9221,16 @@
         <v>942</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="O9" s="14" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>2397</v>
+        <v>2395</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>2398</v>
+        <v>2396</v>
       </c>
       <c r="R9" s="12" t="s">
         <v>947</v>
@@ -9239,10 +9239,10 @@
         <v>948</v>
       </c>
       <c r="T9" s="12" t="s">
-        <v>2395</v>
+        <v>2393</v>
       </c>
       <c r="U9" s="14" t="s">
-        <v>2396</v>
+        <v>2394</v>
       </c>
       <c r="V9" s="12" t="s">
         <v>925</v>
@@ -9251,7 +9251,7 @@
         <v>75</v>
       </c>
       <c r="X9" s="14" t="s">
-        <v>2394</v>
+        <v>2392</v>
       </c>
       <c r="Y9" s="12" t="s">
         <v>77</v>
@@ -9375,10 +9375,10 @@
         <v>959</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="R11" s="12" t="s">
         <v>960</v>
@@ -9918,19 +9918,19 @@
     </row>
     <row r="19" spans="1:25" ht="78.05" customHeight="1">
       <c r="A19" s="12" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>1916</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="D19" s="13" t="s">
         <v>1917</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>1918</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>1919</v>
-      </c>
       <c r="E19" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>62</v>
@@ -9947,43 +9947,43 @@
         <v>60</v>
       </c>
       <c r="L19" s="12" t="s">
+        <v>1918</v>
+      </c>
+      <c r="M19" s="13" t="s">
+        <v>1919</v>
+      </c>
+      <c r="N19" s="12" t="s">
         <v>1920</v>
       </c>
-      <c r="M19" s="13" t="s">
+      <c r="O19" s="14" t="s">
         <v>1921</v>
       </c>
-      <c r="N19" s="12" t="s">
+      <c r="P19" s="12" t="s">
         <v>1922</v>
       </c>
-      <c r="O19" s="14" t="s">
+      <c r="Q19" s="14" t="s">
         <v>1923</v>
       </c>
-      <c r="P19" s="12" t="s">
+      <c r="R19" s="12" t="s">
+        <v>1720</v>
+      </c>
+      <c r="S19" s="14" t="s">
+        <v>1721</v>
+      </c>
+      <c r="T19" s="12" t="s">
+        <v>1757</v>
+      </c>
+      <c r="U19" s="14" t="s">
+        <v>1708</v>
+      </c>
+      <c r="V19" s="12" t="s">
+        <v>1671</v>
+      </c>
+      <c r="W19" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X19" s="14" t="s">
         <v>1924</v>
-      </c>
-      <c r="Q19" s="14" t="s">
-        <v>1925</v>
-      </c>
-      <c r="R19" s="12" t="s">
-        <v>1722</v>
-      </c>
-      <c r="S19" s="14" t="s">
-        <v>1723</v>
-      </c>
-      <c r="T19" s="12" t="s">
-        <v>1759</v>
-      </c>
-      <c r="U19" s="14" t="s">
-        <v>1710</v>
-      </c>
-      <c r="V19" s="12" t="s">
-        <v>1673</v>
-      </c>
-      <c r="W19" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X19" s="14" t="s">
-        <v>1926</v>
       </c>
       <c r="Y19" s="12" t="s">
         <v>77</v>
@@ -9991,19 +9991,19 @@
     </row>
     <row r="20" spans="1:25" ht="78.05" customHeight="1">
       <c r="A20" s="12" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>1890</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="D20" s="13" t="s">
         <v>1891</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>1892</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>1893</v>
-      </c>
       <c r="E20" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>162</v>
@@ -10024,43 +10024,43 @@
         <v>60</v>
       </c>
       <c r="L20" s="12" t="s">
+        <v>1892</v>
+      </c>
+      <c r="M20" s="13" t="s">
+        <v>1893</v>
+      </c>
+      <c r="N20" s="12" t="s">
         <v>1894</v>
       </c>
-      <c r="M20" s="13" t="s">
+      <c r="O20" s="14" t="s">
         <v>1895</v>
       </c>
-      <c r="N20" s="12" t="s">
+      <c r="P20" s="12" t="s">
         <v>1896</v>
       </c>
-      <c r="O20" s="14" t="s">
+      <c r="Q20" s="14" t="s">
         <v>1897</v>
       </c>
-      <c r="P20" s="12" t="s">
+      <c r="R20" s="12" t="s">
         <v>1898</v>
       </c>
-      <c r="Q20" s="14" t="s">
+      <c r="S20" s="14" t="s">
         <v>1899</v>
       </c>
-      <c r="R20" s="12" t="s">
+      <c r="T20" s="12" t="s">
+        <v>1864</v>
+      </c>
+      <c r="U20" s="14" t="s">
+        <v>1708</v>
+      </c>
+      <c r="V20" s="12" t="s">
+        <v>1671</v>
+      </c>
+      <c r="W20" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X20" s="14" t="s">
         <v>1900</v>
-      </c>
-      <c r="S20" s="14" t="s">
-        <v>1901</v>
-      </c>
-      <c r="T20" s="12" t="s">
-        <v>1866</v>
-      </c>
-      <c r="U20" s="14" t="s">
-        <v>1710</v>
-      </c>
-      <c r="V20" s="12" t="s">
-        <v>1673</v>
-      </c>
-      <c r="W20" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X20" s="14" t="s">
-        <v>1902</v>
       </c>
       <c r="Y20" s="12" t="s">
         <v>77</v>
@@ -10068,19 +10068,19 @@
     </row>
     <row r="21" spans="1:25" ht="78.05" customHeight="1">
       <c r="A21" s="12" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>1669</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="D21" s="13" t="s">
         <v>1670</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="E21" s="12" t="s">
         <v>1671</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>1672</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>1673</v>
       </c>
       <c r="F21" s="12" t="s">
         <v>82</v>
@@ -10101,10 +10101,10 @@
         <v>60</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="M21" s="13" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="N21" s="12" t="s">
         <v>87</v>
@@ -10113,10 +10113,10 @@
         <v>88</v>
       </c>
       <c r="P21" s="12" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="Q21" s="14" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="R21" s="12" t="s">
         <v>91</v>
@@ -10131,13 +10131,13 @@
         <v>557</v>
       </c>
       <c r="V21" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="W21" s="12" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="X21" s="14" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="Y21" s="12" t="s">
         <v>77</v>
@@ -10145,19 +10145,19 @@
     </row>
     <row r="22" spans="1:25" ht="78.05" customHeight="1">
       <c r="A22" s="12" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>1734</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="D22" s="13" t="s">
         <v>1735</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>1736</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>1737</v>
-      </c>
       <c r="E22" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F22" s="12" t="s">
         <v>172</v>
@@ -10176,43 +10176,43 @@
         <v>90</v>
       </c>
       <c r="L22" s="12" t="s">
+        <v>1736</v>
+      </c>
+      <c r="M22" s="13" t="s">
+        <v>1737</v>
+      </c>
+      <c r="N22" s="12" t="s">
         <v>1738</v>
       </c>
-      <c r="M22" s="13" t="s">
+      <c r="O22" s="14" t="s">
         <v>1739</v>
       </c>
-      <c r="N22" s="12" t="s">
+      <c r="P22" s="12" t="s">
         <v>1740</v>
       </c>
-      <c r="O22" s="14" t="s">
+      <c r="Q22" s="14" t="s">
         <v>1741</v>
       </c>
-      <c r="P22" s="12" t="s">
+      <c r="R22" s="12" t="s">
         <v>1742</v>
       </c>
-      <c r="Q22" s="14" t="s">
+      <c r="S22" s="14" t="s">
         <v>1743</v>
       </c>
-      <c r="R22" s="12" t="s">
+      <c r="T22" s="12" t="s">
         <v>1744</v>
       </c>
-      <c r="S22" s="14" t="s">
+      <c r="U22" s="14" t="s">
         <v>1745</v>
       </c>
-      <c r="T22" s="12" t="s">
+      <c r="V22" s="12" t="s">
+        <v>1671</v>
+      </c>
+      <c r="W22" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X22" s="14" t="s">
         <v>1746</v>
-      </c>
-      <c r="U22" s="14" t="s">
-        <v>1747</v>
-      </c>
-      <c r="V22" s="12" t="s">
-        <v>1673</v>
-      </c>
-      <c r="W22" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X22" s="14" t="s">
-        <v>1748</v>
       </c>
       <c r="Y22" s="12" t="s">
         <v>77</v>
@@ -10220,19 +10220,19 @@
     </row>
     <row r="23" spans="1:25" ht="78.05" customHeight="1">
       <c r="A23" s="12" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C23" s="12" t="s">
         <v>1727</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="D23" s="13" t="s">
         <v>1728</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>1729</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>1730</v>
-      </c>
       <c r="E23" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>172</v>
@@ -10247,10 +10247,10 @@
         <v>100</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="N23" s="12" t="s">
         <v>223</v>
@@ -10277,13 +10277,13 @@
         <v>186</v>
       </c>
       <c r="V23" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="W23" s="12" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="X23" s="14" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="Y23" s="12" t="s">
         <v>77</v>
@@ -10291,19 +10291,19 @@
     </row>
     <row r="24" spans="1:25" ht="78.05" customHeight="1">
       <c r="A24" s="12" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>1947</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>1948</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="D24" s="13" t="s">
         <v>1949</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>1950</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>1951</v>
-      </c>
       <c r="E24" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F24" s="12" t="s">
         <v>172</v>
@@ -10322,43 +10322,43 @@
         <v>60</v>
       </c>
       <c r="L24" s="12" t="s">
+        <v>1950</v>
+      </c>
+      <c r="M24" s="13" t="s">
+        <v>1951</v>
+      </c>
+      <c r="N24" s="12" t="s">
         <v>1952</v>
       </c>
-      <c r="M24" s="13" t="s">
+      <c r="O24" s="14" t="s">
         <v>1953</v>
       </c>
-      <c r="N24" s="12" t="s">
+      <c r="P24" s="12" t="s">
         <v>1954</v>
       </c>
-      <c r="O24" s="14" t="s">
+      <c r="Q24" s="14" t="s">
         <v>1955</v>
       </c>
-      <c r="P24" s="12" t="s">
-        <v>1956</v>
-      </c>
-      <c r="Q24" s="14" t="s">
-        <v>1957</v>
-      </c>
       <c r="R24" s="12" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="S24" s="14" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="T24" s="12" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="U24" s="14" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="V24" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="W24" s="12" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="X24" s="14" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="Y24" s="12" t="s">
         <v>77</v>
@@ -10366,19 +10366,19 @@
     </row>
     <row r="25" spans="1:25" ht="78.05" customHeight="1">
       <c r="A25" s="12" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>1841</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="D25" s="13" t="s">
         <v>1842</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>1843</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>1844</v>
-      </c>
       <c r="E25" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>689</v>
@@ -10399,43 +10399,43 @@
         <v>60</v>
       </c>
       <c r="L25" s="12" t="s">
+        <v>1843</v>
+      </c>
+      <c r="M25" s="13" t="s">
+        <v>1844</v>
+      </c>
+      <c r="N25" s="12" t="s">
         <v>1845</v>
       </c>
-      <c r="M25" s="13" t="s">
+      <c r="O25" s="14" t="s">
         <v>1846</v>
       </c>
-      <c r="N25" s="12" t="s">
+      <c r="P25" s="12" t="s">
         <v>1847</v>
       </c>
-      <c r="O25" s="14" t="s">
+      <c r="Q25" s="14" t="s">
         <v>1848</v>
       </c>
-      <c r="P25" s="12" t="s">
+      <c r="R25" s="12" t="s">
         <v>1849</v>
       </c>
-      <c r="Q25" s="14" t="s">
+      <c r="S25" s="14" t="s">
         <v>1850</v>
       </c>
-      <c r="R25" s="12" t="s">
+      <c r="T25" s="12" t="s">
         <v>1851</v>
       </c>
-      <c r="S25" s="14" t="s">
+      <c r="U25" s="14" t="s">
         <v>1852</v>
       </c>
-      <c r="T25" s="12" t="s">
+      <c r="V25" s="12" t="s">
+        <v>1671</v>
+      </c>
+      <c r="W25" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X25" s="14" t="s">
         <v>1853</v>
-      </c>
-      <c r="U25" s="14" t="s">
-        <v>1854</v>
-      </c>
-      <c r="V25" s="12" t="s">
-        <v>1673</v>
-      </c>
-      <c r="W25" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X25" s="14" t="s">
-        <v>1855</v>
       </c>
       <c r="Y25" s="12" t="s">
         <v>77</v>
@@ -10443,19 +10443,19 @@
     </row>
     <row r="26" spans="1:25" ht="78.05" customHeight="1">
       <c r="A26" s="12" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>1712</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="D26" s="13" t="s">
         <v>1713</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>1714</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>1715</v>
-      </c>
       <c r="E26" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>98</v>
@@ -10474,43 +10474,43 @@
         <v>60</v>
       </c>
       <c r="L26" s="12" t="s">
+        <v>1714</v>
+      </c>
+      <c r="M26" s="13" t="s">
+        <v>1715</v>
+      </c>
+      <c r="N26" s="12" t="s">
         <v>1716</v>
       </c>
-      <c r="M26" s="13" t="s">
+      <c r="O26" s="14" t="s">
         <v>1717</v>
       </c>
-      <c r="N26" s="12" t="s">
+      <c r="P26" s="12" t="s">
         <v>1718</v>
       </c>
-      <c r="O26" s="14" t="s">
+      <c r="Q26" s="14" t="s">
         <v>1719</v>
       </c>
-      <c r="P26" s="12" t="s">
+      <c r="R26" s="12" t="s">
         <v>1720</v>
       </c>
-      <c r="Q26" s="14" t="s">
+      <c r="S26" s="14" t="s">
         <v>1721</v>
       </c>
-      <c r="R26" s="12" t="s">
+      <c r="T26" s="12" t="s">
         <v>1722</v>
       </c>
-      <c r="S26" s="14" t="s">
+      <c r="U26" s="14" t="s">
         <v>1723</v>
       </c>
-      <c r="T26" s="12" t="s">
+      <c r="V26" s="12" t="s">
+        <v>1671</v>
+      </c>
+      <c r="W26" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X26" s="14" t="s">
         <v>1724</v>
-      </c>
-      <c r="U26" s="14" t="s">
-        <v>1725</v>
-      </c>
-      <c r="V26" s="12" t="s">
-        <v>1673</v>
-      </c>
-      <c r="W26" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X26" s="14" t="s">
-        <v>1726</v>
       </c>
       <c r="Y26" s="12" t="s">
         <v>77</v>
@@ -10518,19 +10518,19 @@
     </row>
     <row r="27" spans="1:25" ht="78.05" customHeight="1">
       <c r="A27" s="12" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C27" s="12" t="s">
         <v>1782</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="D27" s="13" t="s">
         <v>1783</v>
       </c>
-      <c r="C27" s="12" t="s">
-        <v>1784</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>1785</v>
-      </c>
       <c r="E27" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>271</v>
@@ -10549,10 +10549,10 @@
         <v>100</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="N27" s="12" t="s">
         <v>300</v>
@@ -10573,19 +10573,19 @@
         <v>326</v>
       </c>
       <c r="T27" s="12" t="s">
+        <v>1786</v>
+      </c>
+      <c r="U27" s="14" t="s">
+        <v>1787</v>
+      </c>
+      <c r="V27" s="12" t="s">
+        <v>1671</v>
+      </c>
+      <c r="W27" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X27" s="14" t="s">
         <v>1788</v>
-      </c>
-      <c r="U27" s="14" t="s">
-        <v>1789</v>
-      </c>
-      <c r="V27" s="12" t="s">
-        <v>1673</v>
-      </c>
-      <c r="W27" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X27" s="14" t="s">
-        <v>1790</v>
       </c>
       <c r="Y27" s="12" t="s">
         <v>77</v>
@@ -10593,19 +10593,19 @@
     </row>
     <row r="28" spans="1:25" ht="78.05" customHeight="1">
       <c r="A28" s="12" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>1770</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="D28" s="13" t="s">
         <v>1771</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>1772</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>1773</v>
-      </c>
       <c r="E28" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>271</v>
@@ -10654,13 +10654,13 @@
         <v>373</v>
       </c>
       <c r="V28" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="W28" s="12" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="X28" s="14" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="Y28" s="12" t="s">
         <v>77</v>
@@ -10668,19 +10668,19 @@
     </row>
     <row r="29" spans="1:25" ht="78.05" customHeight="1">
       <c r="A29" s="12" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C29" s="12" t="s">
         <v>1775</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="D29" s="13" t="s">
         <v>1776</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>1777</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>1778</v>
-      </c>
       <c r="E29" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>271</v>
@@ -10699,10 +10699,10 @@
         <v>100</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="M29" s="13" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="N29" s="12" t="s">
         <v>300</v>
@@ -10729,13 +10729,13 @@
         <v>373</v>
       </c>
       <c r="V29" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="W29" s="12" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="X29" s="14" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="Y29" s="12" t="s">
         <v>77</v>
@@ -10743,19 +10743,19 @@
     </row>
     <row r="30" spans="1:25" ht="78.05" customHeight="1">
       <c r="A30" s="12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C30" s="12" t="s">
         <v>1761</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="D30" s="13" t="s">
         <v>1762</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>1763</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>1764</v>
-      </c>
       <c r="E30" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>271</v>
@@ -10776,22 +10776,22 @@
         <v>100</v>
       </c>
       <c r="L30" s="12" t="s">
+        <v>1763</v>
+      </c>
+      <c r="M30" s="13" t="s">
+        <v>1764</v>
+      </c>
+      <c r="N30" s="12" t="s">
         <v>1765</v>
       </c>
-      <c r="M30" s="13" t="s">
+      <c r="O30" s="14" t="s">
         <v>1766</v>
       </c>
-      <c r="N30" s="12" t="s">
-        <v>1767</v>
-      </c>
-      <c r="O30" s="14" t="s">
-        <v>1768</v>
-      </c>
       <c r="P30" s="12" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="Q30" s="14" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
       <c r="R30" s="12" t="s">
         <v>142</v>
@@ -10806,13 +10806,13 @@
         <v>294</v>
       </c>
       <c r="V30" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="W30" s="12" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="X30" s="14" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="Y30" s="12" t="s">
         <v>77</v>
@@ -10820,19 +10820,19 @@
     </row>
     <row r="31" spans="1:25" ht="78.05" customHeight="1">
       <c r="A31" s="12" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C31" s="12" t="s">
         <v>1938</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="D31" s="13" t="s">
         <v>1939</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>1940</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>1941</v>
-      </c>
       <c r="E31" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F31" s="12" t="s">
         <v>62</v>
@@ -10851,43 +10851,43 @@
         <v>60</v>
       </c>
       <c r="L31" s="12" t="s">
+        <v>1940</v>
+      </c>
+      <c r="M31" s="13" t="s">
+        <v>1941</v>
+      </c>
+      <c r="N31" s="12" t="s">
         <v>1942</v>
       </c>
-      <c r="M31" s="13" t="s">
+      <c r="O31" s="14" t="s">
         <v>1943</v>
       </c>
-      <c r="N31" s="12" t="s">
+      <c r="P31" s="12" t="s">
         <v>1944</v>
       </c>
-      <c r="O31" s="14" t="s">
+      <c r="Q31" s="14" t="s">
         <v>1945</v>
       </c>
-      <c r="P31" s="12" t="s">
-        <v>1946</v>
-      </c>
-      <c r="Q31" s="14" t="s">
-        <v>1947</v>
-      </c>
       <c r="R31" s="12" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="S31" s="14" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="T31" s="12" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="U31" s="14" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="V31" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="W31" s="12" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="X31" s="14" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="Y31" s="12" t="s">
         <v>77</v>
@@ -10895,19 +10895,19 @@
     </row>
     <row r="32" spans="1:25" ht="78.05" customHeight="1">
       <c r="A32" s="12" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C32" s="12" t="s">
         <v>1903</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="D32" s="13" t="s">
         <v>1904</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>1905</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>1906</v>
-      </c>
       <c r="E32" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>161</v>
@@ -10928,43 +10928,43 @@
         <v>120</v>
       </c>
       <c r="L32" s="12" t="s">
+        <v>1905</v>
+      </c>
+      <c r="M32" s="13" t="s">
+        <v>1906</v>
+      </c>
+      <c r="N32" s="12" t="s">
         <v>1907</v>
       </c>
-      <c r="M32" s="13" t="s">
+      <c r="O32" s="14" t="s">
         <v>1908</v>
       </c>
-      <c r="N32" s="12" t="s">
+      <c r="P32" s="12" t="s">
         <v>1909</v>
       </c>
-      <c r="O32" s="14" t="s">
+      <c r="Q32" s="14" t="s">
         <v>1910</v>
       </c>
-      <c r="P32" s="12" t="s">
+      <c r="R32" s="12" t="s">
         <v>1911</v>
       </c>
-      <c r="Q32" s="14" t="s">
+      <c r="S32" s="14" t="s">
         <v>1912</v>
       </c>
-      <c r="R32" s="12" t="s">
+      <c r="T32" s="12" t="s">
+        <v>1744</v>
+      </c>
+      <c r="U32" s="14" t="s">
+        <v>1745</v>
+      </c>
+      <c r="V32" s="12" t="s">
+        <v>1671</v>
+      </c>
+      <c r="W32" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X32" s="14" t="s">
         <v>1913</v>
-      </c>
-      <c r="S32" s="14" t="s">
-        <v>1914</v>
-      </c>
-      <c r="T32" s="12" t="s">
-        <v>1746</v>
-      </c>
-      <c r="U32" s="14" t="s">
-        <v>1747</v>
-      </c>
-      <c r="V32" s="12" t="s">
-        <v>1673</v>
-      </c>
-      <c r="W32" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X32" s="14" t="s">
-        <v>1915</v>
       </c>
       <c r="Y32" s="12" t="s">
         <v>77</v>
@@ -10972,19 +10972,19 @@
     </row>
     <row r="33" spans="1:25" ht="78.05" customHeight="1">
       <c r="A33" s="12" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C33" s="12" t="s">
         <v>1927</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="D33" s="13" t="s">
         <v>1928</v>
       </c>
-      <c r="C33" s="12" t="s">
-        <v>1929</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>1930</v>
-      </c>
       <c r="E33" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>350</v>
@@ -11005,43 +11005,43 @@
         <v>60</v>
       </c>
       <c r="L33" s="12" t="s">
+        <v>1929</v>
+      </c>
+      <c r="M33" s="13" t="s">
+        <v>1930</v>
+      </c>
+      <c r="N33" s="12" t="s">
         <v>1931</v>
       </c>
-      <c r="M33" s="13" t="s">
+      <c r="O33" s="14" t="s">
         <v>1932</v>
       </c>
-      <c r="N33" s="12" t="s">
+      <c r="P33" s="12" t="s">
         <v>1933</v>
       </c>
-      <c r="O33" s="14" t="s">
+      <c r="Q33" s="14" t="s">
         <v>1934</v>
       </c>
-      <c r="P33" s="12" t="s">
+      <c r="R33" s="12" t="s">
+        <v>1720</v>
+      </c>
+      <c r="S33" s="14" t="s">
+        <v>1721</v>
+      </c>
+      <c r="T33" s="12" t="s">
+        <v>1757</v>
+      </c>
+      <c r="U33" s="14" t="s">
+        <v>1708</v>
+      </c>
+      <c r="V33" s="12" t="s">
+        <v>1671</v>
+      </c>
+      <c r="W33" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X33" s="14" t="s">
         <v>1935</v>
-      </c>
-      <c r="Q33" s="14" t="s">
-        <v>1936</v>
-      </c>
-      <c r="R33" s="12" t="s">
-        <v>1722</v>
-      </c>
-      <c r="S33" s="14" t="s">
-        <v>1723</v>
-      </c>
-      <c r="T33" s="12" t="s">
-        <v>1759</v>
-      </c>
-      <c r="U33" s="14" t="s">
-        <v>1710</v>
-      </c>
-      <c r="V33" s="12" t="s">
-        <v>1673</v>
-      </c>
-      <c r="W33" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X33" s="14" t="s">
-        <v>1937</v>
       </c>
       <c r="Y33" s="12" t="s">
         <v>77</v>
@@ -11049,19 +11049,19 @@
     </row>
     <row r="34" spans="1:25" ht="78.05" customHeight="1">
       <c r="A34" s="12" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C34" s="12" t="s">
         <v>1877</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="D34" s="13" t="s">
         <v>1878</v>
       </c>
-      <c r="C34" s="12" t="s">
-        <v>1879</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>1880</v>
-      </c>
       <c r="E34" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F34" s="12" t="s">
         <v>161</v>
@@ -11082,43 +11082,43 @@
         <v>90</v>
       </c>
       <c r="L34" s="12" t="s">
+        <v>1879</v>
+      </c>
+      <c r="M34" s="13" t="s">
+        <v>1880</v>
+      </c>
+      <c r="N34" s="12" t="s">
         <v>1881</v>
       </c>
-      <c r="M34" s="13" t="s">
+      <c r="O34" s="14" t="s">
         <v>1882</v>
       </c>
-      <c r="N34" s="12" t="s">
+      <c r="P34" s="12" t="s">
         <v>1883</v>
       </c>
-      <c r="O34" s="14" t="s">
+      <c r="Q34" s="14" t="s">
         <v>1884</v>
       </c>
-      <c r="P34" s="12" t="s">
+      <c r="R34" s="12" t="s">
         <v>1885</v>
       </c>
-      <c r="Q34" s="14" t="s">
+      <c r="S34" s="14" t="s">
         <v>1886</v>
       </c>
-      <c r="R34" s="12" t="s">
+      <c r="T34" s="12" t="s">
+        <v>1757</v>
+      </c>
+      <c r="U34" s="14" t="s">
+        <v>1708</v>
+      </c>
+      <c r="V34" s="12" t="s">
+        <v>1671</v>
+      </c>
+      <c r="W34" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X34" s="14" t="s">
         <v>1887</v>
-      </c>
-      <c r="S34" s="14" t="s">
-        <v>1888</v>
-      </c>
-      <c r="T34" s="12" t="s">
-        <v>1759</v>
-      </c>
-      <c r="U34" s="14" t="s">
-        <v>1710</v>
-      </c>
-      <c r="V34" s="12" t="s">
-        <v>1673</v>
-      </c>
-      <c r="W34" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X34" s="14" t="s">
-        <v>1889</v>
       </c>
       <c r="Y34" s="12" t="s">
         <v>77</v>
@@ -11126,19 +11126,19 @@
     </row>
     <row r="35" spans="1:25" ht="78.05" customHeight="1">
       <c r="A35" s="12" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C35" s="12" t="s">
         <v>1697</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="D35" s="13" t="s">
         <v>1698</v>
       </c>
-      <c r="C35" s="12" t="s">
-        <v>1699</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>1700</v>
-      </c>
       <c r="E35" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F35" s="12" t="s">
         <v>162</v>
@@ -11155,43 +11155,43 @@
         <v>90</v>
       </c>
       <c r="L35" s="12" t="s">
+        <v>1699</v>
+      </c>
+      <c r="M35" s="13" t="s">
+        <v>1700</v>
+      </c>
+      <c r="N35" s="12" t="s">
         <v>1701</v>
       </c>
-      <c r="M35" s="13" t="s">
+      <c r="O35" s="14" t="s">
         <v>1702</v>
       </c>
-      <c r="N35" s="12" t="s">
+      <c r="P35" s="12" t="s">
         <v>1703</v>
       </c>
-      <c r="O35" s="14" t="s">
+      <c r="Q35" s="14" t="s">
         <v>1704</v>
       </c>
-      <c r="P35" s="12" t="s">
+      <c r="R35" s="12" t="s">
         <v>1705</v>
       </c>
-      <c r="Q35" s="14" t="s">
+      <c r="S35" s="14" t="s">
         <v>1706</v>
       </c>
-      <c r="R35" s="12" t="s">
+      <c r="T35" s="12" t="s">
         <v>1707</v>
       </c>
-      <c r="S35" s="14" t="s">
+      <c r="U35" s="14" t="s">
         <v>1708</v>
       </c>
-      <c r="T35" s="12" t="s">
+      <c r="V35" s="12" t="s">
+        <v>1671</v>
+      </c>
+      <c r="W35" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X35" s="14" t="s">
         <v>1709</v>
-      </c>
-      <c r="U35" s="14" t="s">
-        <v>1710</v>
-      </c>
-      <c r="V35" s="12" t="s">
-        <v>1673</v>
-      </c>
-      <c r="W35" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X35" s="14" t="s">
-        <v>1711</v>
       </c>
       <c r="Y35" s="12" t="s">
         <v>77</v>
@@ -11199,19 +11199,19 @@
     </row>
     <row r="36" spans="1:25" ht="78.05" customHeight="1">
       <c r="A36" s="12" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C36" s="12" t="s">
         <v>1749</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="D36" s="13" t="s">
         <v>1750</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>1751</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>1752</v>
-      </c>
       <c r="E36" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F36" s="12" t="s">
         <v>172</v>
@@ -11228,43 +11228,43 @@
         <v>60</v>
       </c>
       <c r="L36" s="12" t="s">
+        <v>1751</v>
+      </c>
+      <c r="M36" s="13" t="s">
+        <v>1752</v>
+      </c>
+      <c r="N36" s="12" t="s">
         <v>1753</v>
       </c>
-      <c r="M36" s="13" t="s">
+      <c r="O36" s="14" t="s">
         <v>1754</v>
       </c>
-      <c r="N36" s="12" t="s">
+      <c r="P36" s="12" t="s">
         <v>1755</v>
       </c>
-      <c r="O36" s="14" t="s">
+      <c r="Q36" s="14" t="s">
         <v>1756</v>
       </c>
-      <c r="P36" s="12" t="s">
+      <c r="R36" s="12" t="s">
+        <v>1742</v>
+      </c>
+      <c r="S36" s="14" t="s">
+        <v>1743</v>
+      </c>
+      <c r="T36" s="12" t="s">
         <v>1757</v>
       </c>
-      <c r="Q36" s="14" t="s">
+      <c r="U36" s="14" t="s">
+        <v>1708</v>
+      </c>
+      <c r="V36" s="12" t="s">
+        <v>1671</v>
+      </c>
+      <c r="W36" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X36" s="14" t="s">
         <v>1758</v>
-      </c>
-      <c r="R36" s="12" t="s">
-        <v>1744</v>
-      </c>
-      <c r="S36" s="14" t="s">
-        <v>1745</v>
-      </c>
-      <c r="T36" s="12" t="s">
-        <v>1759</v>
-      </c>
-      <c r="U36" s="14" t="s">
-        <v>1710</v>
-      </c>
-      <c r="V36" s="12" t="s">
-        <v>1673</v>
-      </c>
-      <c r="W36" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X36" s="14" t="s">
-        <v>1760</v>
       </c>
       <c r="Y36" s="12" t="s">
         <v>77</v>
@@ -11272,19 +11272,19 @@
     </row>
     <row r="37" spans="1:25" ht="78.05" customHeight="1">
       <c r="A37" s="12" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C37" s="12" t="s">
         <v>1830</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="D37" s="13" t="s">
         <v>1831</v>
       </c>
-      <c r="C37" s="12" t="s">
-        <v>1832</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>1833</v>
-      </c>
       <c r="E37" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F37" s="12" t="s">
         <v>689</v>
@@ -11301,22 +11301,22 @@
         <v>1</v>
       </c>
       <c r="L37" s="12" t="s">
+        <v>1832</v>
+      </c>
+      <c r="M37" s="13" t="s">
+        <v>1833</v>
+      </c>
+      <c r="N37" s="12" t="s">
         <v>1834</v>
       </c>
-      <c r="M37" s="13" t="s">
+      <c r="O37" s="14" t="s">
         <v>1835</v>
       </c>
-      <c r="N37" s="12" t="s">
+      <c r="P37" s="12" t="s">
         <v>1836</v>
       </c>
-      <c r="O37" s="14" t="s">
+      <c r="Q37" s="14" t="s">
         <v>1837</v>
-      </c>
-      <c r="P37" s="12" t="s">
-        <v>1838</v>
-      </c>
-      <c r="Q37" s="14" t="s">
-        <v>1839</v>
       </c>
       <c r="R37" s="12" t="s">
         <v>696</v>
@@ -11331,13 +11331,13 @@
         <v>423</v>
       </c>
       <c r="V37" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="W37" s="12" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="X37" s="14" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="Y37" s="12" t="s">
         <v>77</v>
@@ -11345,19 +11345,19 @@
     </row>
     <row r="38" spans="1:25" ht="78.05" customHeight="1">
       <c r="A38" s="12" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C38" s="12" t="s">
         <v>1856</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="D38" s="13" t="s">
         <v>1857</v>
       </c>
-      <c r="C38" s="12" t="s">
-        <v>1858</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>1859</v>
-      </c>
       <c r="E38" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F38" s="12" t="s">
         <v>838</v>
@@ -11374,43 +11374,43 @@
         <v>90</v>
       </c>
       <c r="L38" s="12" t="s">
+        <v>1858</v>
+      </c>
+      <c r="M38" s="13" t="s">
+        <v>1859</v>
+      </c>
+      <c r="N38" s="12" t="s">
         <v>1860</v>
       </c>
-      <c r="M38" s="13" t="s">
+      <c r="O38" s="14" t="s">
         <v>1861</v>
       </c>
-      <c r="N38" s="12" t="s">
+      <c r="P38" s="12" t="s">
+        <v>2411</v>
+      </c>
+      <c r="Q38" s="14" t="s">
+        <v>2412</v>
+      </c>
+      <c r="R38" s="12" t="s">
         <v>1862</v>
       </c>
-      <c r="O38" s="14" t="s">
+      <c r="S38" s="14" t="s">
         <v>1863</v>
       </c>
-      <c r="P38" s="12" t="s">
-        <v>2413</v>
-      </c>
-      <c r="Q38" s="14" t="s">
-        <v>2414</v>
-      </c>
-      <c r="R38" s="12" t="s">
+      <c r="T38" s="12" t="s">
         <v>1864</v>
       </c>
-      <c r="S38" s="14" t="s">
+      <c r="U38" s="14" t="s">
+        <v>1708</v>
+      </c>
+      <c r="V38" s="12" t="s">
+        <v>1671</v>
+      </c>
+      <c r="W38" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X38" s="14" t="s">
         <v>1865</v>
-      </c>
-      <c r="T38" s="12" t="s">
-        <v>1866</v>
-      </c>
-      <c r="U38" s="14" t="s">
-        <v>1710</v>
-      </c>
-      <c r="V38" s="12" t="s">
-        <v>1673</v>
-      </c>
-      <c r="W38" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X38" s="14" t="s">
-        <v>1867</v>
       </c>
       <c r="Y38" s="12" t="s">
         <v>77</v>
@@ -11418,19 +11418,19 @@
     </row>
     <row r="39" spans="1:25" ht="78.05" customHeight="1">
       <c r="A39" s="12" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C39" s="12" t="s">
         <v>1791</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="D39" s="13" t="s">
         <v>1792</v>
       </c>
-      <c r="C39" s="12" t="s">
-        <v>1793</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>1794</v>
-      </c>
       <c r="E39" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F39" s="12" t="s">
         <v>62</v>
@@ -11481,13 +11481,13 @@
         <v>373</v>
       </c>
       <c r="V39" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="W39" s="12" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="X39" s="14" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="Y39" s="12" t="s">
         <v>77</v>
@@ -11495,19 +11495,19 @@
     </row>
     <row r="40" spans="1:25" ht="78.05" customHeight="1">
       <c r="A40" s="12" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C40" s="12" t="s">
         <v>1688</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="D40" s="13" t="s">
         <v>1689</v>
       </c>
-      <c r="C40" s="12" t="s">
-        <v>1690</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>1691</v>
-      </c>
       <c r="E40" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F40" s="12" t="s">
         <v>113</v>
@@ -11526,10 +11526,10 @@
         <v>100</v>
       </c>
       <c r="L40" s="12" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="M40" s="13" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="N40" s="12" t="s">
         <v>115</v>
@@ -11538,10 +11538,10 @@
         <v>116</v>
       </c>
       <c r="P40" s="12" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="Q40" s="14" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="R40" s="12" t="s">
         <v>119</v>
@@ -11556,13 +11556,13 @@
         <v>505</v>
       </c>
       <c r="V40" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="W40" s="12" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="X40" s="14" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="Y40" s="12" t="s">
         <v>77</v>
@@ -11570,19 +11570,19 @@
     </row>
     <row r="41" spans="1:25" ht="78.05" customHeight="1">
       <c r="A41" s="12" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C41" s="12" t="s">
         <v>1679</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="D41" s="13" t="s">
         <v>1680</v>
       </c>
-      <c r="C41" s="12" t="s">
-        <v>1681</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>1682</v>
-      </c>
       <c r="E41" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>113</v>
@@ -11601,10 +11601,10 @@
         <v>30</v>
       </c>
       <c r="L41" s="12" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="M41" s="13" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="N41" s="12" t="s">
         <v>115</v>
@@ -11613,10 +11613,10 @@
         <v>116</v>
       </c>
       <c r="P41" s="12" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="R41" s="12" t="s">
         <v>119</v>
@@ -11631,13 +11631,13 @@
         <v>505</v>
       </c>
       <c r="V41" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="W41" s="12" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="X41" s="14" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="Y41" s="12" t="s">
         <v>77</v>
@@ -11645,19 +11645,19 @@
     </row>
     <row r="42" spans="1:25" ht="78.05" customHeight="1">
       <c r="A42" s="12" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C42" s="12" t="s">
         <v>1796</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="D42" s="13" t="s">
         <v>1797</v>
       </c>
-      <c r="C42" s="12" t="s">
-        <v>1798</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>1799</v>
-      </c>
       <c r="E42" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F42" s="12" t="s">
         <v>172</v>
@@ -11678,10 +11678,10 @@
         <v>90</v>
       </c>
       <c r="L42" s="12" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="M42" s="13" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="N42" s="12" t="s">
         <v>396</v>
@@ -11690,10 +11690,10 @@
         <v>397</v>
       </c>
       <c r="P42" s="12" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="Q42" s="14" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="R42" s="12" t="s">
         <v>91</v>
@@ -11708,13 +11708,13 @@
         <v>186</v>
       </c>
       <c r="V42" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="W42" s="12" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="X42" s="14" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="Y42" s="12" t="s">
         <v>77</v>
@@ -11722,19 +11722,19 @@
     </row>
     <row r="43" spans="1:25" ht="78.05" customHeight="1">
       <c r="A43" s="12" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C43" s="12" t="s">
         <v>1805</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="D43" s="13" t="s">
         <v>1806</v>
       </c>
-      <c r="C43" s="12" t="s">
-        <v>1807</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>1808</v>
-      </c>
       <c r="E43" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F43" s="12" t="s">
         <v>151</v>
@@ -11755,10 +11755,10 @@
         <v>100</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="M43" s="13" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="N43" s="12" t="s">
         <v>432</v>
@@ -11767,16 +11767,16 @@
         <v>433</v>
       </c>
       <c r="P43" s="12" t="s">
+        <v>1809</v>
+      </c>
+      <c r="Q43" s="14" t="s">
+        <v>1810</v>
+      </c>
+      <c r="R43" s="12" t="s">
         <v>1811</v>
       </c>
-      <c r="Q43" s="14" t="s">
+      <c r="S43" s="14" t="s">
         <v>1812</v>
-      </c>
-      <c r="R43" s="12" t="s">
-        <v>1813</v>
-      </c>
-      <c r="S43" s="14" t="s">
-        <v>1814</v>
       </c>
       <c r="T43" s="12" t="s">
         <v>438</v>
@@ -11785,13 +11785,13 @@
         <v>439</v>
       </c>
       <c r="V43" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="W43" s="12" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="X43" s="14" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="Y43" s="12" t="s">
         <v>77</v>
@@ -11799,19 +11799,19 @@
     </row>
     <row r="44" spans="1:25" ht="78.05" customHeight="1">
       <c r="A44" s="12" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C44" s="12" t="s">
         <v>1823</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="D44" s="13" t="s">
         <v>1824</v>
       </c>
-      <c r="C44" s="12" t="s">
-        <v>1825</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>1826</v>
-      </c>
       <c r="E44" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F44" s="12" t="s">
         <v>62</v>
@@ -11832,10 +11832,10 @@
         <v>100</v>
       </c>
       <c r="L44" s="12" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="M44" s="13" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="N44" s="12" t="s">
         <v>522</v>
@@ -11862,13 +11862,13 @@
         <v>529</v>
       </c>
       <c r="V44" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="W44" s="12" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="X44" s="14" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="Y44" s="12" t="s">
         <v>77</v>
@@ -11876,19 +11876,19 @@
     </row>
     <row r="45" spans="1:25" ht="78.05" customHeight="1">
       <c r="A45" s="12" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C45" s="12" t="s">
         <v>1868</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="D45" s="13" t="s">
         <v>1869</v>
       </c>
-      <c r="C45" s="12" t="s">
-        <v>1870</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>1871</v>
-      </c>
       <c r="E45" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F45" s="12" t="s">
         <v>838</v>
@@ -11905,43 +11905,43 @@
         <v>90</v>
       </c>
       <c r="L45" s="12" t="s">
+        <v>1870</v>
+      </c>
+      <c r="M45" s="13" t="s">
+        <v>1871</v>
+      </c>
+      <c r="N45" s="12" t="s">
         <v>1872</v>
       </c>
-      <c r="M45" s="13" t="s">
+      <c r="O45" s="14" t="s">
         <v>1873</v>
       </c>
-      <c r="N45" s="12" t="s">
+      <c r="P45" s="12" t="s">
+        <v>2413</v>
+      </c>
+      <c r="Q45" s="14" t="s">
+        <v>2414</v>
+      </c>
+      <c r="R45" s="12" t="s">
+        <v>1862</v>
+      </c>
+      <c r="S45" s="14" t="s">
+        <v>1863</v>
+      </c>
+      <c r="T45" s="12" t="s">
+        <v>1757</v>
+      </c>
+      <c r="U45" s="14" t="s">
+        <v>1708</v>
+      </c>
+      <c r="V45" s="12" t="s">
+        <v>1671</v>
+      </c>
+      <c r="W45" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X45" s="14" t="s">
         <v>1874</v>
-      </c>
-      <c r="O45" s="14" t="s">
-        <v>1875</v>
-      </c>
-      <c r="P45" s="12" t="s">
-        <v>2415</v>
-      </c>
-      <c r="Q45" s="14" t="s">
-        <v>2416</v>
-      </c>
-      <c r="R45" s="12" t="s">
-        <v>1864</v>
-      </c>
-      <c r="S45" s="14" t="s">
-        <v>1865</v>
-      </c>
-      <c r="T45" s="12" t="s">
-        <v>1759</v>
-      </c>
-      <c r="U45" s="14" t="s">
-        <v>1710</v>
-      </c>
-      <c r="V45" s="12" t="s">
-        <v>1673</v>
-      </c>
-      <c r="W45" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X45" s="14" t="s">
-        <v>1876</v>
       </c>
       <c r="Y45" s="12" t="s">
         <v>77</v>
@@ -11949,19 +11949,19 @@
     </row>
     <row r="46" spans="1:25" ht="78.05" customHeight="1">
       <c r="A46" s="12" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C46" s="12" t="s">
         <v>1816</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="D46" s="13" t="s">
         <v>1817</v>
       </c>
-      <c r="C46" s="12" t="s">
-        <v>1818</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>1819</v>
-      </c>
       <c r="E46" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="F46" s="12" t="s">
         <v>172</v>
@@ -11982,10 +11982,10 @@
         <v>60</v>
       </c>
       <c r="L46" s="12" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M46" s="13" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="N46" s="12" t="s">
         <v>463</v>
@@ -11994,10 +11994,10 @@
         <v>464</v>
       </c>
       <c r="P46" s="12" t="s">
-        <v>2411</v>
+        <v>2409</v>
       </c>
       <c r="Q46" s="14" t="s">
-        <v>2412</v>
+        <v>2410</v>
       </c>
       <c r="R46" s="12" t="s">
         <v>91</v>
@@ -12012,13 +12012,13 @@
         <v>468</v>
       </c>
       <c r="V46" s="12" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="W46" s="12" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="X46" s="14" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="Y46" s="12" t="s">
         <v>77</v>
@@ -12065,10 +12065,10 @@
         <v>1371</v>
       </c>
       <c r="P47" s="12" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="Q47" s="14" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="R47" s="12" t="s">
         <v>1372</v>
@@ -12359,10 +12359,10 @@
         <v>1429</v>
       </c>
       <c r="P51" s="12" t="s">
-        <v>2405</v>
+        <v>2403</v>
       </c>
       <c r="Q51" s="14" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="R51" s="12" t="s">
         <v>1430</v>
@@ -12537,19 +12537,19 @@
     </row>
     <row r="54" spans="1:25" ht="78.05" customHeight="1">
       <c r="A54" s="12" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>1652</v>
+      </c>
+      <c r="C54" s="12" t="s">
         <v>1653</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="D54" s="13" t="s">
         <v>1654</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="E54" s="12" t="s">
         <v>1655</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>1656</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>1657</v>
       </c>
       <c r="F54" s="12" t="s">
         <v>172</v>
@@ -12568,43 +12568,43 @@
         <v>1</v>
       </c>
       <c r="L54" s="12" t="s">
+        <v>1656</v>
+      </c>
+      <c r="M54" s="13" t="s">
+        <v>1657</v>
+      </c>
+      <c r="N54" s="12" t="s">
         <v>1658</v>
       </c>
-      <c r="M54" s="13" t="s">
+      <c r="O54" s="14" t="s">
         <v>1659</v>
       </c>
-      <c r="N54" s="12" t="s">
+      <c r="P54" s="12" t="s">
         <v>1660</v>
       </c>
-      <c r="O54" s="14" t="s">
+      <c r="Q54" s="14" t="s">
         <v>1661</v>
       </c>
-      <c r="P54" s="12" t="s">
+      <c r="R54" s="12" t="s">
         <v>1662</v>
       </c>
-      <c r="Q54" s="14" t="s">
+      <c r="S54" s="14" t="s">
         <v>1663</v>
       </c>
-      <c r="R54" s="12" t="s">
+      <c r="T54" s="12" t="s">
         <v>1664</v>
       </c>
-      <c r="S54" s="14" t="s">
+      <c r="U54" s="14" t="s">
         <v>1665</v>
       </c>
-      <c r="T54" s="12" t="s">
-        <v>1666</v>
-      </c>
-      <c r="U54" s="14" t="s">
-        <v>1667</v>
-      </c>
       <c r="V54" s="12" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="W54" s="12" t="s">
         <v>75</v>
       </c>
       <c r="X54" s="14" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="Y54" s="12" t="s">
         <v>77</v>
@@ -12904,10 +12904,10 @@
         <v>745</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>2375</v>
+        <v>2373</v>
       </c>
       <c r="E59" s="12" t="s">
         <v>61</v>
@@ -12981,10 +12981,10 @@
         <v>712</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>2360</v>
+        <v>2358</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>61</v>
@@ -13018,10 +13018,10 @@
         <v>716</v>
       </c>
       <c r="P60" s="12" t="s">
-        <v>2358</v>
+        <v>2356</v>
       </c>
       <c r="Q60" s="14" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
       <c r="R60" s="12" t="s">
         <v>385</v>
@@ -13050,16 +13050,16 @@
     </row>
     <row r="61" spans="1:25" ht="78.05" customHeight="1">
       <c r="A61" s="12" t="s">
+        <v>2360</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>2361</v>
+      </c>
+      <c r="C61" s="12" t="s">
         <v>2362</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="D61" s="13" t="s">
         <v>2363</v>
-      </c>
-      <c r="C61" s="12" t="s">
-        <v>2364</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>2365</v>
       </c>
       <c r="E61" s="12" t="s">
         <v>61</v>
@@ -13093,10 +13093,10 @@
         <v>716</v>
       </c>
       <c r="P61" s="12" t="s">
-        <v>2366</v>
+        <v>2364</v>
       </c>
       <c r="Q61" s="14" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
       <c r="R61" s="12" t="s">
         <v>385</v>
@@ -13117,7 +13117,7 @@
         <v>75</v>
       </c>
       <c r="X61" s="14" t="s">
-        <v>2368</v>
+        <v>2366</v>
       </c>
       <c r="Y61" s="12" t="s">
         <v>77</v>
@@ -13125,16 +13125,16 @@
     </row>
     <row r="62" spans="1:25" ht="78.05" customHeight="1">
       <c r="A62" s="12" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>2368</v>
+      </c>
+      <c r="C62" s="12" t="s">
         <v>2369</v>
       </c>
-      <c r="B62" s="12" t="s">
+      <c r="D62" s="13" t="s">
         <v>2370</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>2371</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>2372</v>
       </c>
       <c r="E62" s="12" t="s">
         <v>61</v>
@@ -13192,7 +13192,7 @@
         <v>75</v>
       </c>
       <c r="X62" s="14" t="s">
-        <v>2373</v>
+        <v>2371</v>
       </c>
       <c r="Y62" s="12" t="s">
         <v>77</v>
@@ -13203,10 +13203,10 @@
         <v>96</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>97</v>
@@ -13243,10 +13243,10 @@
         <v>103</v>
       </c>
       <c r="P63" s="12" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
       <c r="Q63" s="14" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="R63" s="12" t="s">
         <v>104</v>
@@ -13383,10 +13383,10 @@
         <v>512</v>
       </c>
       <c r="N65" s="12" t="s">
-        <v>2341</v>
+        <v>2339</v>
       </c>
       <c r="O65" s="14" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="P65" s="12" t="s">
         <v>513</v>
@@ -13496,7 +13496,7 @@
         <v>77</v>
       </c>
       <c r="Z66" s="19" t="s">
-        <v>2265</v>
+        <v>2263</v>
       </c>
       <c r="AA66">
         <v>120</v>
@@ -13547,10 +13547,10 @@
         <v>252</v>
       </c>
       <c r="P67" s="12" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
       <c r="Q67" s="14" t="s">
-        <v>2311</v>
+        <v>2309</v>
       </c>
       <c r="R67" s="12" t="s">
         <v>253</v>
@@ -13579,16 +13579,16 @@
     </row>
     <row r="68" spans="1:27" ht="78.05" customHeight="1">
       <c r="A68" s="12" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>2094</v>
+      </c>
+      <c r="C68" s="12" t="s">
         <v>2095</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="D68" s="13" t="s">
         <v>2096</v>
-      </c>
-      <c r="C68" s="12" t="s">
-        <v>2097</v>
-      </c>
-      <c r="D68" s="13" t="s">
-        <v>2098</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>61</v>
@@ -13612,22 +13612,22 @@
         <v>120</v>
       </c>
       <c r="L68" s="12" t="s">
+        <v>2097</v>
+      </c>
+      <c r="M68" s="13" t="s">
+        <v>2098</v>
+      </c>
+      <c r="N68" s="12" t="s">
         <v>2099</v>
       </c>
-      <c r="M68" s="13" t="s">
+      <c r="O68" s="14" t="s">
         <v>2100</v>
       </c>
-      <c r="N68" s="12" t="s">
+      <c r="P68" s="12" t="s">
         <v>2101</v>
       </c>
-      <c r="O68" s="14" t="s">
+      <c r="Q68" s="14" t="s">
         <v>2102</v>
-      </c>
-      <c r="P68" s="12" t="s">
-        <v>2103</v>
-      </c>
-      <c r="Q68" s="14" t="s">
-        <v>2104</v>
       </c>
       <c r="R68" s="12" t="s">
         <v>91</v>
@@ -13636,10 +13636,10 @@
         <v>92</v>
       </c>
       <c r="T68" s="12" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="U68" s="14" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="V68" s="12" t="s">
         <v>61</v>
@@ -13648,7 +13648,7 @@
         <v>75</v>
       </c>
       <c r="X68" s="14" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="Y68" s="12" t="s">
         <v>77</v>
@@ -14027,7 +14027,7 @@
         <v>77</v>
       </c>
       <c r="Z73" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
       <c r="AA73">
         <v>100</v>
@@ -14041,10 +14041,10 @@
         <v>638</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>2348</v>
+        <v>2346</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>61</v>
@@ -14074,10 +14074,10 @@
         <v>640</v>
       </c>
       <c r="N74" s="12" t="s">
-        <v>2349</v>
+        <v>2347</v>
       </c>
       <c r="O74" s="14" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
       <c r="P74" s="12" t="s">
         <v>641</v>
@@ -15037,10 +15037,10 @@
         <v>263</v>
       </c>
       <c r="N87" s="12" t="s">
-        <v>2312</v>
+        <v>2310</v>
       </c>
       <c r="O87" s="14" t="s">
-        <v>2313</v>
+        <v>2311</v>
       </c>
       <c r="P87" s="12" t="s">
         <v>264</v>
@@ -15152,16 +15152,16 @@
     </row>
     <row r="89" spans="1:25" ht="78.05" customHeight="1">
       <c r="A89" s="12" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C89" s="12" t="s">
         <v>2151</v>
       </c>
-      <c r="B89" s="12" t="s">
+      <c r="D89" s="13" t="s">
         <v>2152</v>
-      </c>
-      <c r="C89" s="12" t="s">
-        <v>2153</v>
-      </c>
-      <c r="D89" s="13" t="s">
-        <v>2154</v>
       </c>
       <c r="E89" s="12" t="s">
         <v>61</v>
@@ -15183,22 +15183,22 @@
         <v>60</v>
       </c>
       <c r="L89" s="12" t="s">
+        <v>2153</v>
+      </c>
+      <c r="M89" s="13" t="s">
+        <v>2154</v>
+      </c>
+      <c r="N89" s="12" t="s">
         <v>2155</v>
       </c>
-      <c r="M89" s="13" t="s">
+      <c r="O89" s="14" t="s">
         <v>2156</v>
       </c>
-      <c r="N89" s="12" t="s">
+      <c r="P89" s="12" t="s">
         <v>2157</v>
       </c>
-      <c r="O89" s="14" t="s">
+      <c r="Q89" s="14" t="s">
         <v>2158</v>
-      </c>
-      <c r="P89" s="12" t="s">
-        <v>2159</v>
-      </c>
-      <c r="Q89" s="14" t="s">
-        <v>2160</v>
       </c>
       <c r="R89" s="12" t="s">
         <v>541</v>
@@ -15207,7 +15207,7 @@
         <v>542</v>
       </c>
       <c r="T89" s="12" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="U89" s="14" t="s">
         <v>107</v>
@@ -15219,7 +15219,7 @@
         <v>75</v>
       </c>
       <c r="X89" s="14" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="Y89" s="12" t="s">
         <v>77</v>
@@ -15341,10 +15341,10 @@
         <v>365</v>
       </c>
       <c r="N91" s="12" t="s">
-        <v>2324</v>
+        <v>2322</v>
       </c>
       <c r="O91" s="14" t="s">
-        <v>2325</v>
+        <v>2323</v>
       </c>
       <c r="P91" s="12" t="s">
         <v>368</v>
@@ -15647,10 +15647,10 @@
         <v>858</v>
       </c>
       <c r="P95" s="12" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="Q95" s="14" t="s">
-        <v>2379</v>
+        <v>2377</v>
       </c>
       <c r="R95" s="12" t="s">
         <v>859</v>
@@ -15941,16 +15941,16 @@
         <v>616</v>
       </c>
       <c r="N99" s="12" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
       <c r="O99" s="14" t="s">
-        <v>2346</v>
+        <v>2344</v>
       </c>
       <c r="P99" s="12" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
       <c r="Q99" s="14" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="R99" s="12" t="s">
         <v>617</v>
@@ -16056,22 +16056,22 @@
     </row>
     <row r="101" spans="1:27" ht="78.05" customHeight="1">
       <c r="A101" s="12" t="s">
+        <v>2269</v>
+      </c>
+      <c r="B101" s="12" t="s">
+        <v>2270</v>
+      </c>
+      <c r="C101" s="23" t="s">
         <v>2271</v>
       </c>
-      <c r="B101" s="12" t="s">
+      <c r="D101" s="23" t="s">
         <v>2272</v>
-      </c>
-      <c r="C101" s="23" t="s">
-        <v>2273</v>
-      </c>
-      <c r="D101" s="23" t="s">
-        <v>2274</v>
       </c>
       <c r="E101" s="12" t="s">
         <v>61</v>
       </c>
       <c r="F101" s="12" t="s">
-        <v>2275</v>
+        <v>2273</v>
       </c>
       <c r="G101" s="12"/>
       <c r="H101" s="12" t="s">
@@ -16087,34 +16087,34 @@
         <v>60</v>
       </c>
       <c r="L101" s="23" t="s">
-        <v>2273</v>
+        <v>2271</v>
       </c>
       <c r="M101" s="23" t="s">
+        <v>2272</v>
+      </c>
+      <c r="N101" s="12" t="s">
         <v>2274</v>
       </c>
-      <c r="N101" s="12" t="s">
+      <c r="O101" s="14" t="s">
+        <v>2275</v>
+      </c>
+      <c r="P101" s="12" t="s">
         <v>2276</v>
       </c>
-      <c r="O101" s="14" t="s">
+      <c r="Q101" s="14" t="s">
         <v>2277</v>
       </c>
-      <c r="P101" s="12" t="s">
+      <c r="R101" s="12" t="s">
         <v>2278</v>
       </c>
-      <c r="Q101" s="14" t="s">
+      <c r="S101" s="14" t="s">
         <v>2279</v>
       </c>
-      <c r="R101" s="12" t="s">
+      <c r="T101" s="12" t="s">
         <v>2280</v>
       </c>
-      <c r="S101" s="14" t="s">
+      <c r="U101" s="14" t="s">
         <v>2281</v>
-      </c>
-      <c r="T101" s="12" t="s">
-        <v>2282</v>
-      </c>
-      <c r="U101" s="14" t="s">
-        <v>2283</v>
       </c>
       <c r="V101" s="12" t="s">
         <v>61</v>
@@ -16123,7 +16123,7 @@
         <v>75</v>
       </c>
       <c r="X101" s="14" t="s">
-        <v>2284</v>
+        <v>2282</v>
       </c>
       <c r="Y101" s="12" t="s">
         <v>77</v>
@@ -16168,10 +16168,10 @@
         <v>825</v>
       </c>
       <c r="N102" s="12" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="O102" s="14" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
       <c r="P102" s="12" t="s">
         <v>826</v>
@@ -16312,16 +16312,16 @@
         <v>180</v>
       </c>
       <c r="L104" s="12" t="s">
-        <v>2305</v>
+        <v>2303</v>
       </c>
       <c r="M104" s="13" t="s">
-        <v>2306</v>
+        <v>2304</v>
       </c>
       <c r="N104" s="12" t="s">
-        <v>2303</v>
+        <v>2301</v>
       </c>
       <c r="O104" s="14" t="s">
-        <v>2304</v>
+        <v>2302</v>
       </c>
       <c r="P104" s="12" t="s">
         <v>183</v>
@@ -16354,7 +16354,7 @@
         <v>77</v>
       </c>
       <c r="Z104" t="s">
-        <v>2309</v>
+        <v>2307</v>
       </c>
       <c r="AA104">
         <v>60</v>
@@ -16399,10 +16399,10 @@
         <v>193</v>
       </c>
       <c r="N105" s="12" t="s">
-        <v>2307</v>
+        <v>2305</v>
       </c>
       <c r="O105" s="14" t="s">
-        <v>2308</v>
+        <v>2306</v>
       </c>
       <c r="P105" s="12" t="s">
         <v>194</v>
@@ -16440,13 +16440,13 @@
         <v>171</v>
       </c>
       <c r="B106" s="12" t="s">
+        <v>2283</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>2284</v>
+      </c>
+      <c r="D106" s="13" t="s">
         <v>2285</v>
-      </c>
-      <c r="C106" s="12" t="s">
-        <v>2286</v>
-      </c>
-      <c r="D106" s="13" t="s">
-        <v>2287</v>
       </c>
       <c r="E106" s="12" t="s">
         <v>61</v>
@@ -16476,22 +16476,22 @@
         <v>175</v>
       </c>
       <c r="N106" s="12" t="s">
+        <v>2288</v>
+      </c>
+      <c r="O106" s="14" t="s">
+        <v>2289</v>
+      </c>
+      <c r="P106" s="12" t="s">
+        <v>2286</v>
+      </c>
+      <c r="Q106" s="14" t="s">
+        <v>2287</v>
+      </c>
+      <c r="R106" s="12" t="s">
         <v>2290</v>
       </c>
-      <c r="O106" s="14" t="s">
+      <c r="S106" s="14" t="s">
         <v>2291</v>
-      </c>
-      <c r="P106" s="12" t="s">
-        <v>2288</v>
-      </c>
-      <c r="Q106" s="14" t="s">
-        <v>2289</v>
-      </c>
-      <c r="R106" s="12" t="s">
-        <v>2292</v>
-      </c>
-      <c r="S106" s="14" t="s">
-        <v>2293</v>
       </c>
       <c r="T106" s="12" t="s">
         <v>106</v>
@@ -16595,10 +16595,10 @@
         <v>270</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>2314</v>
+        <v>2312</v>
       </c>
       <c r="D108" s="13" t="s">
-        <v>2315</v>
+        <v>2313</v>
       </c>
       <c r="E108" s="12" t="s">
         <v>61</v>
@@ -16664,7 +16664,7 @@
         <v>77</v>
       </c>
       <c r="Z108" t="s">
-        <v>2337</v>
+        <v>2335</v>
       </c>
       <c r="AA108">
         <v>60</v>
@@ -16745,7 +16745,7 @@
         <v>77</v>
       </c>
       <c r="Z109" t="s">
-        <v>2338</v>
+        <v>2336</v>
       </c>
       <c r="AA109">
         <v>60</v>
@@ -16756,10 +16756,10 @@
         <v>485</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>2339</v>
+        <v>2337</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
       <c r="D110" s="13" t="s">
         <v>486</v>
@@ -16980,16 +16980,16 @@
     </row>
     <row r="113" spans="1:31" ht="78.05" customHeight="1">
       <c r="A113" s="12" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C113" s="12" t="s">
         <v>2136</v>
       </c>
-      <c r="B113" s="12" t="s">
+      <c r="D113" s="13" t="s">
         <v>2137</v>
-      </c>
-      <c r="C113" s="12" t="s">
-        <v>2138</v>
-      </c>
-      <c r="D113" s="13" t="s">
-        <v>2139</v>
       </c>
       <c r="E113" s="12" t="s">
         <v>61</v>
@@ -17013,34 +17013,34 @@
         <v>60</v>
       </c>
       <c r="L113" s="12" t="s">
+        <v>2138</v>
+      </c>
+      <c r="M113" s="13" t="s">
+        <v>2139</v>
+      </c>
+      <c r="N113" s="12" t="s">
         <v>2140</v>
       </c>
-      <c r="M113" s="13" t="s">
+      <c r="O113" s="14" t="s">
         <v>2141</v>
       </c>
-      <c r="N113" s="12" t="s">
+      <c r="P113" s="12" t="s">
         <v>2142</v>
       </c>
-      <c r="O113" s="14" t="s">
+      <c r="Q113" s="14" t="s">
         <v>2143</v>
       </c>
-      <c r="P113" s="12" t="s">
+      <c r="R113" s="12" t="s">
         <v>2144</v>
       </c>
-      <c r="Q113" s="14" t="s">
+      <c r="S113" s="14" t="s">
         <v>2145</v>
       </c>
-      <c r="R113" s="12" t="s">
+      <c r="T113" s="12" t="s">
         <v>2146</v>
       </c>
-      <c r="S113" s="14" t="s">
+      <c r="U113" s="14" t="s">
         <v>2147</v>
-      </c>
-      <c r="T113" s="12" t="s">
-        <v>2148</v>
-      </c>
-      <c r="U113" s="14" t="s">
-        <v>2149</v>
       </c>
       <c r="V113" s="12" t="s">
         <v>61</v>
@@ -17049,25 +17049,25 @@
         <v>75</v>
       </c>
       <c r="X113" s="14" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
       <c r="Y113" s="12" t="s">
         <v>77</v>
       </c>
       <c r="Z113" t="s">
-        <v>2299</v>
+        <v>2297</v>
       </c>
       <c r="AA113">
         <v>200</v>
       </c>
       <c r="AB113" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
       <c r="AC113">
         <v>100</v>
       </c>
       <c r="AD113" t="s">
-        <v>2301</v>
+        <v>2299</v>
       </c>
       <c r="AE113">
         <v>500</v>
@@ -17106,7 +17106,7 @@
         <v>30</v>
       </c>
       <c r="L114" s="12" t="s">
-        <v>2302</v>
+        <v>2300</v>
       </c>
       <c r="M114" s="13" t="s">
         <v>114</v>
@@ -17150,16 +17150,16 @@
     </row>
     <row r="115" spans="1:31" ht="78.05" customHeight="1">
       <c r="A115" s="20" t="s">
+        <v>2264</v>
+      </c>
+      <c r="B115" s="20" t="s">
+        <v>2265</v>
+      </c>
+      <c r="C115" s="20" t="s">
         <v>2266</v>
       </c>
-      <c r="B115" s="20" t="s">
+      <c r="D115" s="21" t="s">
         <v>2267</v>
-      </c>
-      <c r="C115" s="20" t="s">
-        <v>2268</v>
-      </c>
-      <c r="D115" s="21" t="s">
-        <v>2269</v>
       </c>
       <c r="E115" s="12" t="s">
         <v>61</v>
@@ -17217,7 +17217,7 @@
         <v>75</v>
       </c>
       <c r="X115" s="22" t="s">
-        <v>2270</v>
+        <v>2268</v>
       </c>
       <c r="Y115" s="12" t="s">
         <v>77</v>
@@ -17300,16 +17300,16 @@
     </row>
     <row r="117" spans="1:31" ht="78.05" customHeight="1">
       <c r="A117" s="12" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B117" s="12" t="s">
+        <v>2120</v>
+      </c>
+      <c r="C117" s="12" t="s">
         <v>2121</v>
       </c>
-      <c r="B117" s="12" t="s">
+      <c r="D117" s="13" t="s">
         <v>2122</v>
-      </c>
-      <c r="C117" s="12" t="s">
-        <v>2123</v>
-      </c>
-      <c r="D117" s="13" t="s">
-        <v>2124</v>
       </c>
       <c r="E117" s="12" t="s">
         <v>61</v>
@@ -17333,34 +17333,34 @@
         <v>50</v>
       </c>
       <c r="L117" s="12" t="s">
+        <v>2123</v>
+      </c>
+      <c r="M117" s="13" t="s">
+        <v>2124</v>
+      </c>
+      <c r="N117" s="12" t="s">
         <v>2125</v>
       </c>
-      <c r="M117" s="13" t="s">
+      <c r="O117" s="14" t="s">
         <v>2126</v>
       </c>
-      <c r="N117" s="12" t="s">
+      <c r="P117" s="12" t="s">
         <v>2127</v>
       </c>
-      <c r="O117" s="14" t="s">
+      <c r="Q117" s="14" t="s">
         <v>2128</v>
       </c>
-      <c r="P117" s="12" t="s">
+      <c r="R117" s="12" t="s">
         <v>2129</v>
       </c>
-      <c r="Q117" s="14" t="s">
+      <c r="S117" s="14" t="s">
         <v>2130</v>
       </c>
-      <c r="R117" s="12" t="s">
+      <c r="T117" s="12" t="s">
         <v>2131</v>
       </c>
-      <c r="S117" s="14" t="s">
+      <c r="U117" s="14" t="s">
         <v>2132</v>
-      </c>
-      <c r="T117" s="12" t="s">
-        <v>2133</v>
-      </c>
-      <c r="U117" s="14" t="s">
-        <v>2134</v>
       </c>
       <c r="V117" s="12" t="s">
         <v>61</v>
@@ -17369,7 +17369,7 @@
         <v>75</v>
       </c>
       <c r="X117" s="14" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="Y117" s="12" t="s">
         <v>77</v>
@@ -17377,16 +17377,16 @@
     </row>
     <row r="118" spans="1:31" ht="78.05" customHeight="1">
       <c r="A118" s="12" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B118" s="12" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C118" s="12" t="s">
         <v>2108</v>
       </c>
-      <c r="B118" s="12" t="s">
+      <c r="D118" s="13" t="s">
         <v>2109</v>
-      </c>
-      <c r="C118" s="12" t="s">
-        <v>2110</v>
-      </c>
-      <c r="D118" s="13" t="s">
-        <v>2111</v>
       </c>
       <c r="E118" s="12" t="s">
         <v>61</v>
@@ -17408,34 +17408,34 @@
         <v>100</v>
       </c>
       <c r="L118" s="12" t="s">
+        <v>2110</v>
+      </c>
+      <c r="M118" s="13" t="s">
+        <v>2111</v>
+      </c>
+      <c r="N118" s="12" t="s">
+        <v>2333</v>
+      </c>
+      <c r="O118" s="14" t="s">
+        <v>2334</v>
+      </c>
+      <c r="P118" s="12" t="s">
         <v>2112</v>
       </c>
-      <c r="M118" s="13" t="s">
+      <c r="Q118" s="14" t="s">
         <v>2113</v>
       </c>
-      <c r="N118" s="12" t="s">
-        <v>2335</v>
-      </c>
-      <c r="O118" s="14" t="s">
-        <v>2336</v>
-      </c>
-      <c r="P118" s="12" t="s">
+      <c r="R118" s="12" t="s">
         <v>2114</v>
       </c>
-      <c r="Q118" s="14" t="s">
+      <c r="S118" s="14" t="s">
         <v>2115</v>
       </c>
-      <c r="R118" s="12" t="s">
+      <c r="T118" s="12" t="s">
         <v>2116</v>
       </c>
-      <c r="S118" s="14" t="s">
+      <c r="U118" s="14" t="s">
         <v>2117</v>
-      </c>
-      <c r="T118" s="12" t="s">
-        <v>2118</v>
-      </c>
-      <c r="U118" s="14" t="s">
-        <v>2119</v>
       </c>
       <c r="V118" s="12" t="s">
         <v>61</v>
@@ -17444,13 +17444,13 @@
         <v>75</v>
       </c>
       <c r="X118" s="14" t="s">
-        <v>2120</v>
+        <v>2118</v>
       </c>
       <c r="Y118" s="12" t="s">
         <v>77</v>
       </c>
       <c r="Z118" t="s">
-        <v>2326</v>
+        <v>2324</v>
       </c>
       <c r="AA118">
         <v>180</v>
@@ -17458,16 +17458,16 @@
     </row>
     <row r="119" spans="1:31" ht="78.05" customHeight="1">
       <c r="A119" s="12" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="C119" s="12" t="s">
+        <v>2385</v>
+      </c>
+      <c r="D119" s="13" t="s">
         <v>2387</v>
-      </c>
-      <c r="D119" s="13" t="s">
-        <v>2389</v>
       </c>
       <c r="E119" s="12" t="s">
         <v>61</v>
@@ -17485,34 +17485,34 @@
         <v>1</v>
       </c>
       <c r="L119" s="12" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
       <c r="M119" s="13" t="s">
-        <v>2388</v>
+        <v>2386</v>
       </c>
       <c r="N119" s="12" t="s">
+        <v>2084</v>
+      </c>
+      <c r="O119" s="14" t="s">
+        <v>2085</v>
+      </c>
+      <c r="P119" s="12" t="s">
         <v>2086</v>
       </c>
-      <c r="O119" s="14" t="s">
+      <c r="Q119" s="14" t="s">
         <v>2087</v>
       </c>
-      <c r="P119" s="12" t="s">
+      <c r="R119" s="12" t="s">
         <v>2088</v>
       </c>
-      <c r="Q119" s="14" t="s">
+      <c r="S119" s="14" t="s">
         <v>2089</v>
       </c>
-      <c r="R119" s="12" t="s">
+      <c r="T119" s="12" t="s">
         <v>2090</v>
       </c>
-      <c r="S119" s="14" t="s">
+      <c r="U119" s="14" t="s">
         <v>2091</v>
-      </c>
-      <c r="T119" s="12" t="s">
-        <v>2092</v>
-      </c>
-      <c r="U119" s="14" t="s">
-        <v>2093</v>
       </c>
       <c r="V119" s="12" t="s">
         <v>61</v>
@@ -17521,7 +17521,7 @@
         <v>75</v>
       </c>
       <c r="X119" s="14" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="Y119" s="12" t="s">
         <v>77</v>
@@ -17529,16 +17529,16 @@
     </row>
     <row r="120" spans="1:31" ht="78.05" customHeight="1">
       <c r="A120" s="12" t="s">
+        <v>2378</v>
+      </c>
+      <c r="B120" s="12" t="s">
+        <v>2379</v>
+      </c>
+      <c r="C120" s="12" t="s">
         <v>2380</v>
       </c>
-      <c r="B120" s="12" t="s">
+      <c r="D120" s="13" t="s">
         <v>2381</v>
-      </c>
-      <c r="C120" s="12" t="s">
-        <v>2382</v>
-      </c>
-      <c r="D120" s="13" t="s">
-        <v>2383</v>
       </c>
       <c r="E120" s="12" t="s">
         <v>61</v>
@@ -17556,34 +17556,34 @@
         <v>1</v>
       </c>
       <c r="L120" s="12" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
       <c r="M120" s="13" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
       <c r="N120" s="12" t="s">
+        <v>2084</v>
+      </c>
+      <c r="O120" s="14" t="s">
+        <v>2085</v>
+      </c>
+      <c r="P120" s="12" t="s">
         <v>2086</v>
       </c>
-      <c r="O120" s="14" t="s">
+      <c r="Q120" s="14" t="s">
         <v>2087</v>
       </c>
-      <c r="P120" s="12" t="s">
+      <c r="R120" s="12" t="s">
         <v>2088</v>
       </c>
-      <c r="Q120" s="14" t="s">
+      <c r="S120" s="14" t="s">
         <v>2089</v>
       </c>
-      <c r="R120" s="12" t="s">
+      <c r="T120" s="12" t="s">
         <v>2090</v>
       </c>
-      <c r="S120" s="14" t="s">
+      <c r="U120" s="14" t="s">
         <v>2091</v>
-      </c>
-      <c r="T120" s="12" t="s">
-        <v>2092</v>
-      </c>
-      <c r="U120" s="14" t="s">
-        <v>2093</v>
       </c>
       <c r="V120" s="12" t="s">
         <v>61</v>
@@ -17592,7 +17592,7 @@
         <v>75</v>
       </c>
       <c r="X120" s="14" t="s">
-        <v>2384</v>
+        <v>2382</v>
       </c>
       <c r="Y120" s="12" t="s">
         <v>77</v>
@@ -17722,16 +17722,16 @@
         <v>408</v>
       </c>
       <c r="P122" s="12" t="s">
-        <v>2329</v>
+        <v>2327</v>
       </c>
       <c r="Q122" s="14" t="s">
-        <v>2330</v>
+        <v>2328</v>
       </c>
       <c r="R122" s="12" t="s">
-        <v>2327</v>
+        <v>2325</v>
       </c>
       <c r="S122" s="14" t="s">
-        <v>2328</v>
+        <v>2326</v>
       </c>
       <c r="T122" s="12" t="s">
         <v>255</v>
@@ -17858,16 +17858,16 @@
         <v>100</v>
       </c>
       <c r="L124" s="12" t="s">
+        <v>2349</v>
+      </c>
+      <c r="M124" s="13" t="s">
+        <v>2350</v>
+      </c>
+      <c r="N124" s="12" t="s">
         <v>2351</v>
       </c>
-      <c r="M124" s="13" t="s">
+      <c r="O124" s="14" t="s">
         <v>2352</v>
-      </c>
-      <c r="N124" s="12" t="s">
-        <v>2353</v>
-      </c>
-      <c r="O124" s="14" t="s">
-        <v>2354</v>
       </c>
       <c r="P124" s="12" t="s">
         <v>652</v>
@@ -17900,7 +17900,7 @@
         <v>77</v>
       </c>
       <c r="Z124" t="s">
-        <v>2356</v>
+        <v>2354</v>
       </c>
       <c r="AA124">
         <v>120</v>
@@ -17908,16 +17908,16 @@
     </row>
     <row r="125" spans="1:31" ht="78.05" customHeight="1">
       <c r="A125" s="12" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B125" s="12" t="s">
+        <v>2294</v>
+      </c>
+      <c r="C125" s="12" t="s">
         <v>2295</v>
       </c>
-      <c r="B125" s="12" t="s">
+      <c r="D125" s="13" t="s">
         <v>2296</v>
-      </c>
-      <c r="C125" s="12" t="s">
-        <v>2297</v>
-      </c>
-      <c r="D125" s="13" t="s">
-        <v>2298</v>
       </c>
       <c r="E125" s="12" t="s">
         <v>61</v>
@@ -17977,7 +17977,7 @@
         <v>75</v>
       </c>
       <c r="X125" s="14" t="s">
-        <v>2294</v>
+        <v>2292</v>
       </c>
       <c r="Y125" s="12" t="s">
         <v>77</v>
@@ -17991,7 +17991,7 @@
         <v>700</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>2357</v>
+        <v>2355</v>
       </c>
       <c r="D126" s="13" t="s">
         <v>701</v>
@@ -18135,16 +18135,16 @@
     </row>
     <row r="128" spans="1:31" ht="78.05" customHeight="1">
       <c r="A128" s="12" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B128" s="12" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C128" s="12" t="s">
         <v>2071</v>
       </c>
-      <c r="B128" s="12" t="s">
+      <c r="D128" s="13" t="s">
         <v>2072</v>
-      </c>
-      <c r="C128" s="12" t="s">
-        <v>2073</v>
-      </c>
-      <c r="D128" s="13" t="s">
-        <v>2074</v>
       </c>
       <c r="E128" s="12" t="s">
         <v>61</v>
@@ -18166,22 +18166,22 @@
         <v>100</v>
       </c>
       <c r="L128" s="12" t="s">
+        <v>2073</v>
+      </c>
+      <c r="M128" s="13" t="s">
+        <v>2074</v>
+      </c>
+      <c r="N128" s="12" t="s">
         <v>2075</v>
       </c>
-      <c r="M128" s="13" t="s">
+      <c r="O128" s="14" t="s">
         <v>2076</v>
       </c>
-      <c r="N128" s="12" t="s">
+      <c r="P128" s="12" t="s">
         <v>2077</v>
       </c>
-      <c r="O128" s="14" t="s">
+      <c r="Q128" s="14" t="s">
         <v>2078</v>
-      </c>
-      <c r="P128" s="12" t="s">
-        <v>2079</v>
-      </c>
-      <c r="Q128" s="14" t="s">
-        <v>2080</v>
       </c>
       <c r="R128" s="12" t="s">
         <v>91</v>
@@ -18190,10 +18190,10 @@
         <v>92</v>
       </c>
       <c r="T128" s="12" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="U128" s="14" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="V128" s="12" t="s">
         <v>61</v>
@@ -18202,13 +18202,13 @@
         <v>75</v>
       </c>
       <c r="X128" s="14" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="Y128" s="12" t="s">
         <v>77</v>
       </c>
       <c r="Z128" t="s">
-        <v>2323</v>
+        <v>2321</v>
       </c>
       <c r="AA128">
         <v>30</v>
@@ -18289,13 +18289,13 @@
         <v>77</v>
       </c>
       <c r="Z129" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
       <c r="AA129">
         <v>120</v>
       </c>
       <c r="AB129" t="s">
-        <v>2319</v>
+        <v>2317</v>
       </c>
       <c r="AC129">
         <v>240</v>
@@ -18340,7 +18340,7 @@
         <v>322</v>
       </c>
       <c r="N130" s="12" t="s">
-        <v>2322</v>
+        <v>2320</v>
       </c>
       <c r="O130" s="14" t="s">
         <v>301</v>
@@ -18376,13 +18376,13 @@
         <v>77</v>
       </c>
       <c r="Z130" t="s">
-        <v>2320</v>
+        <v>2318</v>
       </c>
       <c r="AA130">
         <v>30</v>
       </c>
       <c r="AB130" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="AC130">
         <v>240</v>
@@ -18393,10 +18393,10 @@
         <v>296</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>2316</v>
+        <v>2314</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>2317</v>
+        <v>2315</v>
       </c>
       <c r="D131" s="13" t="s">
         <v>297</v>
@@ -18427,7 +18427,7 @@
         <v>299</v>
       </c>
       <c r="N131" s="12" t="s">
-        <v>2322</v>
+        <v>2320</v>
       </c>
       <c r="O131" s="14" t="s">
         <v>301</v>
@@ -18502,7 +18502,7 @@
         <v>312</v>
       </c>
       <c r="N132" s="12" t="s">
-        <v>2322</v>
+        <v>2320</v>
       </c>
       <c r="O132" s="14" t="s">
         <v>301</v>
@@ -18538,7 +18538,7 @@
         <v>77</v>
       </c>
       <c r="Z132" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
       <c r="AA132">
         <v>250</v>
@@ -18621,7 +18621,7 @@
         <v>77</v>
       </c>
       <c r="Z133" t="s">
-        <v>2332</v>
+        <v>2330</v>
       </c>
       <c r="AA133">
         <v>60</v>
@@ -18745,10 +18745,10 @@
         <v>462</v>
       </c>
       <c r="N135" s="12" t="s">
-        <v>2333</v>
+        <v>2331</v>
       </c>
       <c r="O135" s="14" t="s">
-        <v>2334</v>
+        <v>2332</v>
       </c>
       <c r="P135" s="12" t="s">
         <v>465</v>
@@ -19894,16 +19894,16 @@
     </row>
     <row r="151" spans="1:27" ht="78.05" customHeight="1">
       <c r="A151" s="12" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="D151" s="13" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="E151" s="12" t="s">
         <v>1496</v>
@@ -19927,34 +19927,34 @@
         <v>60</v>
       </c>
       <c r="L151" s="12" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M151" s="13" t="s">
+        <v>1598</v>
+      </c>
+      <c r="N151" s="12" t="s">
         <v>1599</v>
       </c>
-      <c r="M151" s="13" t="s">
+      <c r="O151" s="14" t="s">
         <v>1600</v>
       </c>
-      <c r="N151" s="12" t="s">
+      <c r="P151" s="12" t="s">
         <v>1601</v>
       </c>
-      <c r="O151" s="14" t="s">
+      <c r="Q151" s="14" t="s">
         <v>1602</v>
       </c>
-      <c r="P151" s="12" t="s">
+      <c r="R151" s="12" t="s">
         <v>1603</v>
       </c>
-      <c r="Q151" s="14" t="s">
+      <c r="S151" s="14" t="s">
         <v>1604</v>
       </c>
-      <c r="R151" s="12" t="s">
+      <c r="T151" s="12" t="s">
         <v>1605</v>
       </c>
-      <c r="S151" s="14" t="s">
+      <c r="U151" s="14" t="s">
         <v>1606</v>
-      </c>
-      <c r="T151" s="12" t="s">
-        <v>1607</v>
-      </c>
-      <c r="U151" s="14" t="s">
-        <v>1608</v>
       </c>
       <c r="V151" s="12" t="s">
         <v>1496</v>
@@ -19963,7 +19963,7 @@
         <v>75</v>
       </c>
       <c r="X151" s="14" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="Y151" s="12" t="s">
         <v>77</v>
@@ -19971,16 +19971,16 @@
     </row>
     <row r="152" spans="1:27" ht="78.05" customHeight="1">
       <c r="A152" s="12" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B152" s="12" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C152" s="12" t="s">
         <v>1640</v>
       </c>
-      <c r="B152" s="12" t="s">
+      <c r="D152" s="13" t="s">
         <v>1641</v>
-      </c>
-      <c r="C152" s="12" t="s">
-        <v>1642</v>
-      </c>
-      <c r="D152" s="13" t="s">
-        <v>1643</v>
       </c>
       <c r="E152" s="12" t="s">
         <v>1496</v>
@@ -20004,34 +20004,34 @@
         <v>60</v>
       </c>
       <c r="L152" s="12" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M152" s="13" t="s">
+        <v>1643</v>
+      </c>
+      <c r="N152" s="12" t="s">
         <v>1644</v>
       </c>
-      <c r="M152" s="13" t="s">
+      <c r="O152" s="14" t="s">
         <v>1645</v>
       </c>
-      <c r="N152" s="12" t="s">
+      <c r="P152" s="12" t="s">
         <v>1646</v>
       </c>
-      <c r="O152" s="14" t="s">
+      <c r="Q152" s="14" t="s">
         <v>1647</v>
       </c>
-      <c r="P152" s="12" t="s">
+      <c r="R152" s="12" t="s">
+        <v>1590</v>
+      </c>
+      <c r="S152" s="14" t="s">
+        <v>1591</v>
+      </c>
+      <c r="T152" s="12" t="s">
         <v>1648</v>
       </c>
-      <c r="Q152" s="14" t="s">
+      <c r="U152" s="14" t="s">
         <v>1649</v>
-      </c>
-      <c r="R152" s="12" t="s">
-        <v>1592</v>
-      </c>
-      <c r="S152" s="14" t="s">
-        <v>1593</v>
-      </c>
-      <c r="T152" s="12" t="s">
-        <v>1650</v>
-      </c>
-      <c r="U152" s="14" t="s">
-        <v>1651</v>
       </c>
       <c r="V152" s="12" t="s">
         <v>1496</v>
@@ -20040,7 +20040,7 @@
         <v>75</v>
       </c>
       <c r="X152" s="14" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="Y152" s="12" t="s">
         <v>77</v>
@@ -20048,16 +20048,16 @@
     </row>
     <row r="153" spans="1:27" ht="78.05" customHeight="1">
       <c r="A153" s="12" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B153" s="12" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C153" s="12" t="s">
         <v>1625</v>
       </c>
-      <c r="B153" s="12" t="s">
+      <c r="D153" s="13" t="s">
         <v>1626</v>
-      </c>
-      <c r="C153" s="12" t="s">
-        <v>1627</v>
-      </c>
-      <c r="D153" s="13" t="s">
-        <v>1628</v>
       </c>
       <c r="E153" s="12" t="s">
         <v>1496</v>
@@ -20079,34 +20079,34 @@
         <v>100</v>
       </c>
       <c r="L153" s="12" t="s">
+        <v>1627</v>
+      </c>
+      <c r="M153" s="13" t="s">
+        <v>1628</v>
+      </c>
+      <c r="N153" s="12" t="s">
         <v>1629</v>
       </c>
-      <c r="M153" s="13" t="s">
+      <c r="O153" s="14" t="s">
         <v>1630</v>
       </c>
-      <c r="N153" s="12" t="s">
+      <c r="P153" s="12" t="s">
         <v>1631</v>
       </c>
-      <c r="O153" s="14" t="s">
+      <c r="Q153" s="14" t="s">
         <v>1632</v>
       </c>
-      <c r="P153" s="12" t="s">
+      <c r="R153" s="12" t="s">
         <v>1633</v>
       </c>
-      <c r="Q153" s="14" t="s">
+      <c r="S153" s="14" t="s">
         <v>1634</v>
       </c>
-      <c r="R153" s="12" t="s">
+      <c r="T153" s="12" t="s">
         <v>1635</v>
       </c>
-      <c r="S153" s="14" t="s">
+      <c r="U153" s="14" t="s">
         <v>1636</v>
-      </c>
-      <c r="T153" s="12" t="s">
-        <v>1637</v>
-      </c>
-      <c r="U153" s="14" t="s">
-        <v>1638</v>
       </c>
       <c r="V153" s="12" t="s">
         <v>1496</v>
@@ -20115,7 +20115,7 @@
         <v>75</v>
       </c>
       <c r="X153" s="14" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="Y153" s="12" t="s">
         <v>77</v>
@@ -20123,16 +20123,16 @@
     </row>
     <row r="154" spans="1:27" ht="78.05" customHeight="1">
       <c r="A154" s="12" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B154" s="12" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C154" s="12" t="s">
         <v>1569</v>
       </c>
-      <c r="B154" s="12" t="s">
+      <c r="D154" s="13" t="s">
         <v>1570</v>
-      </c>
-      <c r="C154" s="12" t="s">
-        <v>1571</v>
-      </c>
-      <c r="D154" s="13" t="s">
-        <v>1572</v>
       </c>
       <c r="E154" s="12" t="s">
         <v>1496</v>
@@ -20156,34 +20156,34 @@
         <v>120</v>
       </c>
       <c r="L154" s="12" t="s">
+        <v>1571</v>
+      </c>
+      <c r="M154" s="13" t="s">
+        <v>1572</v>
+      </c>
+      <c r="N154" s="12" t="s">
         <v>1573</v>
       </c>
-      <c r="M154" s="13" t="s">
+      <c r="O154" s="14" t="s">
         <v>1574</v>
       </c>
-      <c r="N154" s="12" t="s">
+      <c r="P154" s="12" t="s">
+        <v>1560</v>
+      </c>
+      <c r="Q154" s="14" t="s">
+        <v>1561</v>
+      </c>
+      <c r="R154" s="12" t="s">
         <v>1575</v>
       </c>
-      <c r="O154" s="14" t="s">
+      <c r="S154" s="14" t="s">
         <v>1576</v>
       </c>
-      <c r="P154" s="12" t="s">
-        <v>1562</v>
-      </c>
-      <c r="Q154" s="14" t="s">
-        <v>1563</v>
-      </c>
-      <c r="R154" s="12" t="s">
+      <c r="T154" s="12" t="s">
         <v>1577</v>
       </c>
-      <c r="S154" s="14" t="s">
+      <c r="U154" s="14" t="s">
         <v>1578</v>
-      </c>
-      <c r="T154" s="12" t="s">
-        <v>1579</v>
-      </c>
-      <c r="U154" s="14" t="s">
-        <v>1580</v>
       </c>
       <c r="V154" s="12" t="s">
         <v>1496</v>
@@ -20192,7 +20192,7 @@
         <v>75</v>
       </c>
       <c r="X154" s="14" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="Y154" s="12" t="s">
         <v>77</v>
@@ -20200,16 +20200,16 @@
     </row>
     <row r="155" spans="1:27" ht="78.05" customHeight="1">
       <c r="A155" s="12" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B155" s="12" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C155" s="12" t="s">
         <v>1554</v>
       </c>
-      <c r="B155" s="12" t="s">
+      <c r="D155" s="13" t="s">
         <v>1555</v>
-      </c>
-      <c r="C155" s="12" t="s">
-        <v>1556</v>
-      </c>
-      <c r="D155" s="13" t="s">
-        <v>1557</v>
       </c>
       <c r="E155" s="12" t="s">
         <v>1496</v>
@@ -20233,34 +20233,34 @@
         <v>60</v>
       </c>
       <c r="L155" s="12" t="s">
+        <v>1556</v>
+      </c>
+      <c r="M155" s="13" t="s">
+        <v>1557</v>
+      </c>
+      <c r="N155" s="12" t="s">
         <v>1558</v>
       </c>
-      <c r="M155" s="13" t="s">
+      <c r="O155" s="14" t="s">
         <v>1559</v>
       </c>
-      <c r="N155" s="12" t="s">
+      <c r="P155" s="12" t="s">
         <v>1560</v>
       </c>
-      <c r="O155" s="14" t="s">
+      <c r="Q155" s="14" t="s">
         <v>1561</v>
       </c>
-      <c r="P155" s="12" t="s">
+      <c r="R155" s="12" t="s">
         <v>1562</v>
       </c>
-      <c r="Q155" s="14" t="s">
+      <c r="S155" s="14" t="s">
         <v>1563</v>
       </c>
-      <c r="R155" s="12" t="s">
+      <c r="T155" s="12" t="s">
         <v>1564</v>
       </c>
-      <c r="S155" s="14" t="s">
+      <c r="U155" s="14" t="s">
         <v>1565</v>
-      </c>
-      <c r="T155" s="12" t="s">
-        <v>1566</v>
-      </c>
-      <c r="U155" s="14" t="s">
-        <v>1567</v>
       </c>
       <c r="V155" s="12" t="s">
         <v>1496</v>
@@ -20269,30 +20269,24 @@
         <v>75</v>
       </c>
       <c r="X155" s="14" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="Y155" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="Z155" t="s">
-        <v>1499</v>
-      </c>
-      <c r="AA155">
-        <v>90</v>
-      </c>
     </row>
     <row r="156" spans="1:27" ht="78.05" customHeight="1">
       <c r="A156" s="12" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B156" s="12" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C156" s="12" t="s">
         <v>1610</v>
       </c>
-      <c r="B156" s="12" t="s">
+      <c r="D156" s="13" t="s">
         <v>1611</v>
-      </c>
-      <c r="C156" s="12" t="s">
-        <v>1612</v>
-      </c>
-      <c r="D156" s="13" t="s">
-        <v>1613</v>
       </c>
       <c r="E156" s="12" t="s">
         <v>1496</v>
@@ -20316,34 +20310,34 @@
         <v>60</v>
       </c>
       <c r="L156" s="12" t="s">
+        <v>1612</v>
+      </c>
+      <c r="M156" s="13" t="s">
+        <v>1613</v>
+      </c>
+      <c r="N156" s="12" t="s">
         <v>1614</v>
       </c>
-      <c r="M156" s="13" t="s">
+      <c r="O156" s="14" t="s">
         <v>1615</v>
       </c>
-      <c r="N156" s="12" t="s">
+      <c r="P156" s="12" t="s">
         <v>1616</v>
       </c>
-      <c r="O156" s="14" t="s">
+      <c r="Q156" s="14" t="s">
         <v>1617</v>
       </c>
-      <c r="P156" s="12" t="s">
+      <c r="R156" s="12" t="s">
         <v>1618</v>
       </c>
-      <c r="Q156" s="14" t="s">
+      <c r="S156" s="14" t="s">
         <v>1619</v>
       </c>
-      <c r="R156" s="12" t="s">
+      <c r="T156" s="12" t="s">
         <v>1620</v>
       </c>
-      <c r="S156" s="14" t="s">
+      <c r="U156" s="14" t="s">
         <v>1621</v>
-      </c>
-      <c r="T156" s="12" t="s">
-        <v>1622</v>
-      </c>
-      <c r="U156" s="14" t="s">
-        <v>1623</v>
       </c>
       <c r="V156" s="12" t="s">
         <v>1496</v>
@@ -20352,7 +20346,7 @@
         <v>75</v>
       </c>
       <c r="X156" s="14" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="Y156" s="12" t="s">
         <v>77</v>
@@ -20366,10 +20360,10 @@
         <v>1501</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>1502</v>
+        <v>2419</v>
       </c>
       <c r="D157" s="13" t="s">
-        <v>1503</v>
+        <v>2420</v>
       </c>
       <c r="E157" s="12" t="s">
         <v>1496</v>
@@ -20391,22 +20385,22 @@
         <v>180</v>
       </c>
       <c r="L157" s="12" t="s">
+        <v>1502</v>
+      </c>
+      <c r="M157" s="13" t="s">
+        <v>1503</v>
+      </c>
+      <c r="N157" s="12" t="s">
         <v>1504</v>
       </c>
-      <c r="M157" s="13" t="s">
+      <c r="O157" s="14" t="s">
         <v>1505</v>
       </c>
-      <c r="N157" s="12" t="s">
+      <c r="P157" s="12" t="s">
         <v>1506</v>
       </c>
-      <c r="O157" s="14" t="s">
+      <c r="Q157" s="14" t="s">
         <v>1507</v>
-      </c>
-      <c r="P157" s="12" t="s">
-        <v>1508</v>
-      </c>
-      <c r="Q157" s="14" t="s">
-        <v>1509</v>
       </c>
       <c r="R157" s="12" t="s">
         <v>1497</v>
@@ -20415,10 +20409,10 @@
         <v>1498</v>
       </c>
       <c r="T157" s="12" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="U157" s="14" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="V157" s="12" t="s">
         <v>1496</v>
@@ -20427,24 +20421,30 @@
         <v>75</v>
       </c>
       <c r="X157" s="14" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="Y157" s="12" t="s">
         <v>77</v>
       </c>
+      <c r="Z157" t="s">
+        <v>1499</v>
+      </c>
+      <c r="AA157">
+        <v>90</v>
+      </c>
     </row>
     <row r="158" spans="1:27" ht="78.05" customHeight="1">
       <c r="A158" s="12" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B158" s="12" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C158" s="12" t="s">
         <v>1528</v>
       </c>
-      <c r="B158" s="12" t="s">
+      <c r="D158" s="13" t="s">
         <v>1529</v>
-      </c>
-      <c r="C158" s="12" t="s">
-        <v>1530</v>
-      </c>
-      <c r="D158" s="13" t="s">
-        <v>1531</v>
       </c>
       <c r="E158" s="12" t="s">
         <v>1496</v>
@@ -20468,34 +20468,34 @@
         <v>120</v>
       </c>
       <c r="L158" s="12" t="s">
+        <v>1530</v>
+      </c>
+      <c r="M158" s="13" t="s">
+        <v>1531</v>
+      </c>
+      <c r="N158" s="12" t="s">
         <v>1532</v>
       </c>
-      <c r="M158" s="13" t="s">
+      <c r="O158" s="14" t="s">
         <v>1533</v>
       </c>
-      <c r="N158" s="12" t="s">
+      <c r="P158" s="12" t="s">
         <v>1534</v>
       </c>
-      <c r="O158" s="14" t="s">
+      <c r="Q158" s="14" t="s">
         <v>1535</v>
       </c>
-      <c r="P158" s="12" t="s">
+      <c r="R158" s="12" t="s">
         <v>1536</v>
       </c>
-      <c r="Q158" s="14" t="s">
+      <c r="S158" s="14" t="s">
         <v>1537</v>
       </c>
-      <c r="R158" s="12" t="s">
+      <c r="T158" s="12" t="s">
         <v>1538</v>
       </c>
-      <c r="S158" s="14" t="s">
+      <c r="U158" s="14" t="s">
         <v>1539</v>
-      </c>
-      <c r="T158" s="12" t="s">
-        <v>1540</v>
-      </c>
-      <c r="U158" s="14" t="s">
-        <v>1541</v>
       </c>
       <c r="V158" s="12" t="s">
         <v>1496</v>
@@ -20504,7 +20504,7 @@
         <v>75</v>
       </c>
       <c r="X158" s="14" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="Y158" s="12" t="s">
         <v>77</v>
@@ -20512,16 +20512,16 @@
     </row>
     <row r="159" spans="1:27" ht="78.05" customHeight="1">
       <c r="A159" s="12" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B159" s="12" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C159" s="12" t="s">
         <v>1543</v>
       </c>
-      <c r="B159" s="12" t="s">
+      <c r="D159" s="13" t="s">
         <v>1544</v>
-      </c>
-      <c r="C159" s="12" t="s">
-        <v>1545</v>
-      </c>
-      <c r="D159" s="13" t="s">
-        <v>1546</v>
       </c>
       <c r="E159" s="12" t="s">
         <v>1496</v>
@@ -20545,34 +20545,34 @@
         <v>240</v>
       </c>
       <c r="L159" s="12" t="s">
+        <v>1545</v>
+      </c>
+      <c r="M159" s="13" t="s">
+        <v>1546</v>
+      </c>
+      <c r="N159" s="12" t="s">
         <v>1547</v>
       </c>
-      <c r="M159" s="13" t="s">
+      <c r="O159" s="14" t="s">
         <v>1548</v>
       </c>
-      <c r="N159" s="12" t="s">
+      <c r="P159" s="12" t="s">
+        <v>1534</v>
+      </c>
+      <c r="Q159" s="14" t="s">
+        <v>1535</v>
+      </c>
+      <c r="R159" s="12" t="s">
         <v>1549</v>
       </c>
-      <c r="O159" s="14" t="s">
+      <c r="S159" s="14" t="s">
         <v>1550</v>
       </c>
-      <c r="P159" s="12" t="s">
-        <v>1536</v>
-      </c>
-      <c r="Q159" s="14" t="s">
-        <v>1537</v>
-      </c>
-      <c r="R159" s="12" t="s">
-        <v>1551</v>
-      </c>
-      <c r="S159" s="14" t="s">
-        <v>1552</v>
-      </c>
       <c r="T159" s="12" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="U159" s="14" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="V159" s="12" t="s">
         <v>1496</v>
@@ -20581,7 +20581,7 @@
         <v>75</v>
       </c>
       <c r="X159" s="14" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="Y159" s="12" t="s">
         <v>77</v>
@@ -20589,16 +20589,16 @@
     </row>
     <row r="160" spans="1:27" ht="78.05" customHeight="1">
       <c r="A160" s="12" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B160" s="12" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C160" s="12" t="s">
         <v>1582</v>
       </c>
-      <c r="B160" s="12" t="s">
+      <c r="D160" s="13" t="s">
         <v>1583</v>
-      </c>
-      <c r="C160" s="12" t="s">
-        <v>1584</v>
-      </c>
-      <c r="D160" s="13" t="s">
-        <v>1585</v>
       </c>
       <c r="E160" s="12" t="s">
         <v>1496</v>
@@ -20622,34 +20622,34 @@
         <v>90</v>
       </c>
       <c r="L160" s="12" t="s">
+        <v>1584</v>
+      </c>
+      <c r="M160" s="13" t="s">
+        <v>1585</v>
+      </c>
+      <c r="N160" s="12" t="s">
         <v>1586</v>
       </c>
-      <c r="M160" s="13" t="s">
+      <c r="O160" s="14" t="s">
         <v>1587</v>
       </c>
-      <c r="N160" s="12" t="s">
+      <c r="P160" s="12" t="s">
         <v>1588</v>
       </c>
-      <c r="O160" s="14" t="s">
+      <c r="Q160" s="14" t="s">
         <v>1589</v>
       </c>
-      <c r="P160" s="12" t="s">
+      <c r="R160" s="12" t="s">
         <v>1590</v>
       </c>
-      <c r="Q160" s="14" t="s">
+      <c r="S160" s="14" t="s">
         <v>1591</v>
       </c>
-      <c r="R160" s="12" t="s">
+      <c r="T160" s="12" t="s">
         <v>1592</v>
       </c>
-      <c r="S160" s="14" t="s">
+      <c r="U160" s="14" t="s">
         <v>1593</v>
-      </c>
-      <c r="T160" s="12" t="s">
-        <v>1594</v>
-      </c>
-      <c r="U160" s="14" t="s">
-        <v>1595</v>
       </c>
       <c r="V160" s="12" t="s">
         <v>1496</v>
@@ -20658,7 +20658,7 @@
         <v>75</v>
       </c>
       <c r="X160" s="14" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="Y160" s="12" t="s">
         <v>77</v>
@@ -20666,16 +20666,16 @@
     </row>
     <row r="161" spans="1:25" ht="78.05" customHeight="1">
       <c r="A161" s="12" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B161" s="12" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C161" s="12" t="s">
         <v>1513</v>
       </c>
-      <c r="B161" s="12" t="s">
+      <c r="D161" s="13" t="s">
         <v>1514</v>
-      </c>
-      <c r="C161" s="12" t="s">
-        <v>1515</v>
-      </c>
-      <c r="D161" s="13" t="s">
-        <v>1516</v>
       </c>
       <c r="E161" s="12" t="s">
         <v>1496</v>
@@ -20699,34 +20699,34 @@
         <v>60</v>
       </c>
       <c r="L161" s="12" t="s">
+        <v>1515</v>
+      </c>
+      <c r="M161" s="13" t="s">
+        <v>1516</v>
+      </c>
+      <c r="N161" s="12" t="s">
         <v>1517</v>
       </c>
-      <c r="M161" s="13" t="s">
+      <c r="O161" s="14" t="s">
         <v>1518</v>
       </c>
-      <c r="N161" s="12" t="s">
+      <c r="P161" s="12" t="s">
         <v>1519</v>
       </c>
-      <c r="O161" s="14" t="s">
+      <c r="Q161" s="14" t="s">
         <v>1520</v>
       </c>
-      <c r="P161" s="12" t="s">
+      <c r="R161" s="12" t="s">
         <v>1521</v>
       </c>
-      <c r="Q161" s="14" t="s">
+      <c r="S161" s="14" t="s">
         <v>1522</v>
       </c>
-      <c r="R161" s="12" t="s">
+      <c r="T161" s="12" t="s">
         <v>1523</v>
       </c>
-      <c r="S161" s="14" t="s">
+      <c r="U161" s="14" t="s">
         <v>1524</v>
-      </c>
-      <c r="T161" s="12" t="s">
-        <v>1525</v>
-      </c>
-      <c r="U161" s="14" t="s">
-        <v>1526</v>
       </c>
       <c r="V161" s="12" t="s">
         <v>1496</v>
@@ -20735,7 +20735,7 @@
         <v>75</v>
       </c>
       <c r="X161" s="14" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="Y161" s="12" t="s">
         <v>77</v>
@@ -20743,19 +20743,19 @@
     </row>
     <row r="162" spans="1:25" ht="78.05" customHeight="1">
       <c r="A162" s="12" t="s">
+        <v>1956</v>
+      </c>
+      <c r="B162" s="12" t="s">
+        <v>1957</v>
+      </c>
+      <c r="C162" s="12" t="s">
         <v>1958</v>
       </c>
-      <c r="B162" s="12" t="s">
+      <c r="D162" s="13" t="s">
         <v>1959</v>
       </c>
-      <c r="C162" s="12" t="s">
+      <c r="E162" s="12" t="s">
         <v>1960</v>
-      </c>
-      <c r="D162" s="13" t="s">
-        <v>1961</v>
-      </c>
-      <c r="E162" s="12" t="s">
-        <v>1962</v>
       </c>
       <c r="F162" s="12" t="s">
         <v>82</v>
@@ -20776,43 +20776,43 @@
         <v>30</v>
       </c>
       <c r="L162" s="12" t="s">
+        <v>1961</v>
+      </c>
+      <c r="M162" s="13" t="s">
+        <v>1962</v>
+      </c>
+      <c r="N162" s="12" t="s">
         <v>1963</v>
       </c>
-      <c r="M162" s="13" t="s">
+      <c r="O162" s="14" t="s">
         <v>1964</v>
       </c>
-      <c r="N162" s="12" t="s">
+      <c r="P162" s="12" t="s">
         <v>1965</v>
       </c>
-      <c r="O162" s="14" t="s">
+      <c r="Q162" s="14" t="s">
         <v>1966</v>
       </c>
-      <c r="P162" s="12" t="s">
+      <c r="R162" s="12" t="s">
         <v>1967</v>
       </c>
-      <c r="Q162" s="14" t="s">
+      <c r="S162" s="14" t="s">
         <v>1968</v>
       </c>
-      <c r="R162" s="12" t="s">
+      <c r="T162" s="12" t="s">
         <v>1969</v>
       </c>
-      <c r="S162" s="14" t="s">
+      <c r="U162" s="14" t="s">
         <v>1970</v>
       </c>
-      <c r="T162" s="12" t="s">
+      <c r="V162" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="W162" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X162" s="14" t="s">
         <v>1971</v>
-      </c>
-      <c r="U162" s="14" t="s">
-        <v>1972</v>
-      </c>
-      <c r="V162" s="12" t="s">
-        <v>1962</v>
-      </c>
-      <c r="W162" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X162" s="14" t="s">
-        <v>1973</v>
       </c>
       <c r="Y162" s="12" t="s">
         <v>77</v>
@@ -20820,19 +20820,19 @@
     </row>
     <row r="163" spans="1:25" ht="78.05" customHeight="1">
       <c r="A163" s="12" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B163" s="12" t="s">
+        <v>1999</v>
+      </c>
+      <c r="C163" s="12" t="s">
         <v>2000</v>
       </c>
-      <c r="B163" s="12" t="s">
+      <c r="D163" s="13" t="s">
         <v>2001</v>
       </c>
-      <c r="C163" s="12" t="s">
-        <v>2002</v>
-      </c>
-      <c r="D163" s="13" t="s">
-        <v>2003</v>
-      </c>
       <c r="E163" s="12" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="F163" s="12" t="s">
         <v>172</v>
@@ -20851,43 +20851,43 @@
         <v>60</v>
       </c>
       <c r="L163" s="12" t="s">
+        <v>2002</v>
+      </c>
+      <c r="M163" s="13" t="s">
+        <v>2003</v>
+      </c>
+      <c r="N163" s="12" t="s">
         <v>2004</v>
       </c>
-      <c r="M163" s="13" t="s">
+      <c r="O163" s="14" t="s">
         <v>2005</v>
       </c>
-      <c r="N163" s="12" t="s">
+      <c r="P163" s="12" t="s">
         <v>2006</v>
       </c>
-      <c r="O163" s="14" t="s">
+      <c r="Q163" s="14" t="s">
         <v>2007</v>
       </c>
-      <c r="P163" s="12" t="s">
+      <c r="R163" s="12" t="s">
         <v>2008</v>
       </c>
-      <c r="Q163" s="14" t="s">
+      <c r="S163" s="14" t="s">
         <v>2009</v>
       </c>
-      <c r="R163" s="12" t="s">
+      <c r="T163" s="12" t="s">
         <v>2010</v>
       </c>
-      <c r="S163" s="14" t="s">
+      <c r="U163" s="14" t="s">
         <v>2011</v>
       </c>
-      <c r="T163" s="12" t="s">
+      <c r="V163" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="W163" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X163" s="14" t="s">
         <v>2012</v>
-      </c>
-      <c r="U163" s="14" t="s">
-        <v>2013</v>
-      </c>
-      <c r="V163" s="12" t="s">
-        <v>1962</v>
-      </c>
-      <c r="W163" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X163" s="14" t="s">
-        <v>2014</v>
       </c>
       <c r="Y163" s="12" t="s">
         <v>77</v>
@@ -20895,19 +20895,19 @@
     </row>
     <row r="164" spans="1:25" ht="78.05" customHeight="1">
       <c r="A164" s="12" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B164" s="12" t="s">
+        <v>1986</v>
+      </c>
+      <c r="C164" s="12" t="s">
         <v>1987</v>
       </c>
-      <c r="B164" s="12" t="s">
+      <c r="D164" s="13" t="s">
         <v>1988</v>
       </c>
-      <c r="C164" s="12" t="s">
-        <v>1989</v>
-      </c>
-      <c r="D164" s="13" t="s">
-        <v>1990</v>
-      </c>
       <c r="E164" s="12" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="F164" s="12" t="s">
         <v>172</v>
@@ -20928,43 +20928,43 @@
         <v>60</v>
       </c>
       <c r="L164" s="12" t="s">
+        <v>1989</v>
+      </c>
+      <c r="M164" s="13" t="s">
+        <v>1990</v>
+      </c>
+      <c r="N164" s="12" t="s">
         <v>1991</v>
       </c>
-      <c r="M164" s="13" t="s">
+      <c r="O164" s="14" t="s">
         <v>1992</v>
       </c>
-      <c r="N164" s="12" t="s">
+      <c r="P164" s="12" t="s">
         <v>1993</v>
       </c>
-      <c r="O164" s="14" t="s">
+      <c r="Q164" s="14" t="s">
         <v>1994</v>
       </c>
-      <c r="P164" s="12" t="s">
+      <c r="R164" s="12" t="s">
+        <v>1849</v>
+      </c>
+      <c r="S164" s="14" t="s">
+        <v>1850</v>
+      </c>
+      <c r="T164" s="12" t="s">
         <v>1995</v>
       </c>
-      <c r="Q164" s="14" t="s">
+      <c r="U164" s="14" t="s">
         <v>1996</v>
       </c>
-      <c r="R164" s="12" t="s">
-        <v>1851</v>
-      </c>
-      <c r="S164" s="14" t="s">
-        <v>1852</v>
-      </c>
-      <c r="T164" s="12" t="s">
+      <c r="V164" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="W164" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X164" s="14" t="s">
         <v>1997</v>
-      </c>
-      <c r="U164" s="14" t="s">
-        <v>1998</v>
-      </c>
-      <c r="V164" s="12" t="s">
-        <v>1962</v>
-      </c>
-      <c r="W164" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X164" s="14" t="s">
-        <v>1999</v>
       </c>
       <c r="Y164" s="12" t="s">
         <v>77</v>
@@ -20972,19 +20972,19 @@
     </row>
     <row r="165" spans="1:25" ht="78.05" customHeight="1">
       <c r="A165" s="12" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B165" s="12" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C165" s="12" t="s">
         <v>2030</v>
       </c>
-      <c r="B165" s="12" t="s">
+      <c r="D165" s="13" t="s">
         <v>2031</v>
       </c>
-      <c r="C165" s="12" t="s">
-        <v>2032</v>
-      </c>
-      <c r="D165" s="13" t="s">
-        <v>2033</v>
-      </c>
       <c r="E165" s="12" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="F165" s="12" t="s">
         <v>62</v>
@@ -21005,43 +21005,43 @@
         <v>60</v>
       </c>
       <c r="L165" s="12" t="s">
+        <v>2032</v>
+      </c>
+      <c r="M165" s="13" t="s">
+        <v>2033</v>
+      </c>
+      <c r="N165" s="12" t="s">
         <v>2034</v>
       </c>
-      <c r="M165" s="13" t="s">
+      <c r="O165" s="14" t="s">
         <v>2035</v>
       </c>
-      <c r="N165" s="12" t="s">
+      <c r="P165" s="12" t="s">
         <v>2036</v>
       </c>
-      <c r="O165" s="14" t="s">
+      <c r="Q165" s="14" t="s">
         <v>2037</v>
       </c>
-      <c r="P165" s="12" t="s">
+      <c r="R165" s="12" t="s">
         <v>2038</v>
       </c>
-      <c r="Q165" s="14" t="s">
+      <c r="S165" s="14" t="s">
         <v>2039</v>
       </c>
-      <c r="R165" s="12" t="s">
+      <c r="T165" s="12" t="s">
         <v>2040</v>
       </c>
-      <c r="S165" s="14" t="s">
+      <c r="U165" s="14" t="s">
         <v>2041</v>
       </c>
-      <c r="T165" s="12" t="s">
+      <c r="V165" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="W165" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X165" s="14" t="s">
         <v>2042</v>
-      </c>
-      <c r="U165" s="14" t="s">
-        <v>2043</v>
-      </c>
-      <c r="V165" s="12" t="s">
-        <v>1962</v>
-      </c>
-      <c r="W165" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X165" s="14" t="s">
-        <v>2044</v>
       </c>
       <c r="Y165" s="12" t="s">
         <v>77</v>
@@ -21049,19 +21049,19 @@
     </row>
     <row r="166" spans="1:25" ht="78.05" customHeight="1">
       <c r="A166" s="12" t="s">
+        <v>1972</v>
+      </c>
+      <c r="B166" s="12" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C166" s="12" t="s">
         <v>1974</v>
       </c>
-      <c r="B166" s="12" t="s">
+      <c r="D166" s="13" t="s">
         <v>1975</v>
       </c>
-      <c r="C166" s="12" t="s">
-        <v>1976</v>
-      </c>
-      <c r="D166" s="13" t="s">
-        <v>1977</v>
-      </c>
       <c r="E166" s="12" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="F166" s="12" t="s">
         <v>113</v>
@@ -21080,43 +21080,43 @@
         <v>60</v>
       </c>
       <c r="L166" s="12" t="s">
+        <v>1976</v>
+      </c>
+      <c r="M166" s="13" t="s">
+        <v>1977</v>
+      </c>
+      <c r="N166" s="12" t="s">
         <v>1978</v>
       </c>
-      <c r="M166" s="13" t="s">
+      <c r="O166" s="14" t="s">
         <v>1979</v>
       </c>
-      <c r="N166" s="12" t="s">
+      <c r="P166" s="12" t="s">
         <v>1980</v>
       </c>
-      <c r="O166" s="14" t="s">
+      <c r="Q166" s="14" t="s">
         <v>1981</v>
       </c>
-      <c r="P166" s="12" t="s">
+      <c r="R166" s="12" t="s">
+        <v>1849</v>
+      </c>
+      <c r="S166" s="14" t="s">
+        <v>1850</v>
+      </c>
+      <c r="T166" s="12" t="s">
         <v>1982</v>
       </c>
-      <c r="Q166" s="14" t="s">
+      <c r="U166" s="14" t="s">
         <v>1983</v>
       </c>
-      <c r="R166" s="12" t="s">
-        <v>1851</v>
-      </c>
-      <c r="S166" s="14" t="s">
-        <v>1852</v>
-      </c>
-      <c r="T166" s="12" t="s">
+      <c r="V166" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="W166" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X166" s="14" t="s">
         <v>1984</v>
-      </c>
-      <c r="U166" s="14" t="s">
-        <v>1985</v>
-      </c>
-      <c r="V166" s="12" t="s">
-        <v>1962</v>
-      </c>
-      <c r="W166" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X166" s="14" t="s">
-        <v>1986</v>
       </c>
       <c r="Y166" s="12" t="s">
         <v>77</v>
@@ -21124,19 +21124,19 @@
     </row>
     <row r="167" spans="1:25" ht="78.05" customHeight="1">
       <c r="A167" s="12" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B167" s="12" t="s">
+        <v>2044</v>
+      </c>
+      <c r="C167" s="12" t="s">
         <v>2045</v>
       </c>
-      <c r="B167" s="12" t="s">
+      <c r="D167" s="13" t="s">
         <v>2046</v>
       </c>
-      <c r="C167" s="12" t="s">
-        <v>2047</v>
-      </c>
-      <c r="D167" s="13" t="s">
-        <v>2048</v>
-      </c>
       <c r="E167" s="12" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="F167" s="12" t="s">
         <v>172</v>
@@ -21157,43 +21157,43 @@
         <v>60</v>
       </c>
       <c r="L167" s="12" t="s">
+        <v>2047</v>
+      </c>
+      <c r="M167" s="13" t="s">
+        <v>2048</v>
+      </c>
+      <c r="N167" s="12" t="s">
         <v>2049</v>
       </c>
-      <c r="M167" s="13" t="s">
+      <c r="O167" s="14" t="s">
         <v>2050</v>
       </c>
-      <c r="N167" s="12" t="s">
+      <c r="P167" s="12" t="s">
         <v>2051</v>
       </c>
-      <c r="O167" s="14" t="s">
+      <c r="Q167" s="14" t="s">
         <v>2052</v>
       </c>
-      <c r="P167" s="12" t="s">
+      <c r="R167" s="12" t="s">
+        <v>2008</v>
+      </c>
+      <c r="S167" s="14" t="s">
+        <v>2009</v>
+      </c>
+      <c r="T167" s="12" t="s">
         <v>2053</v>
       </c>
-      <c r="Q167" s="14" t="s">
+      <c r="U167" s="14" t="s">
         <v>2054</v>
       </c>
-      <c r="R167" s="12" t="s">
-        <v>2010</v>
-      </c>
-      <c r="S167" s="14" t="s">
-        <v>2011</v>
-      </c>
-      <c r="T167" s="12" t="s">
+      <c r="V167" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="W167" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X167" s="14" t="s">
         <v>2055</v>
-      </c>
-      <c r="U167" s="14" t="s">
-        <v>2056</v>
-      </c>
-      <c r="V167" s="12" t="s">
-        <v>1962</v>
-      </c>
-      <c r="W167" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X167" s="14" t="s">
-        <v>2057</v>
       </c>
       <c r="Y167" s="12" t="s">
         <v>77</v>
@@ -21201,19 +21201,19 @@
     </row>
     <row r="168" spans="1:25" ht="70.7" customHeight="1">
       <c r="A168" s="12" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B168" s="12" t="s">
+        <v>2014</v>
+      </c>
+      <c r="C168" s="12" t="s">
         <v>2015</v>
       </c>
-      <c r="B168" s="12" t="s">
+      <c r="D168" s="13" t="s">
         <v>2016</v>
       </c>
-      <c r="C168" s="12" t="s">
-        <v>2017</v>
-      </c>
-      <c r="D168" s="13" t="s">
-        <v>2018</v>
-      </c>
       <c r="E168" s="12" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="F168" s="12" t="s">
         <v>271</v>
@@ -21232,43 +21232,43 @@
         <v>60</v>
       </c>
       <c r="L168" s="12" t="s">
+        <v>2017</v>
+      </c>
+      <c r="M168" s="13" t="s">
+        <v>2018</v>
+      </c>
+      <c r="N168" s="12" t="s">
         <v>2019</v>
       </c>
-      <c r="M168" s="13" t="s">
+      <c r="O168" s="14" t="s">
         <v>2020</v>
       </c>
-      <c r="N168" s="12" t="s">
+      <c r="P168" s="12" t="s">
         <v>2021</v>
       </c>
-      <c r="O168" s="14" t="s">
+      <c r="Q168" s="14" t="s">
         <v>2022</v>
       </c>
-      <c r="P168" s="12" t="s">
+      <c r="R168" s="12" t="s">
         <v>2023</v>
       </c>
-      <c r="Q168" s="14" t="s">
+      <c r="S168" s="14" t="s">
         <v>2024</v>
       </c>
-      <c r="R168" s="12" t="s">
+      <c r="T168" s="12" t="s">
         <v>2025</v>
       </c>
-      <c r="S168" s="14" t="s">
+      <c r="U168" s="14" t="s">
         <v>2026</v>
       </c>
-      <c r="T168" s="12" t="s">
+      <c r="V168" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="W168" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X168" s="14" t="s">
         <v>2027</v>
-      </c>
-      <c r="U168" s="14" t="s">
-        <v>2028</v>
-      </c>
-      <c r="V168" s="12" t="s">
-        <v>1962</v>
-      </c>
-      <c r="W168" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X168" s="14" t="s">
-        <v>2029</v>
       </c>
       <c r="Y168" s="12" t="s">
         <v>77</v>
@@ -21276,19 +21276,19 @@
     </row>
     <row r="169" spans="1:25" ht="87.05">
       <c r="A169" s="12" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B169" s="12" t="s">
+        <v>2057</v>
+      </c>
+      <c r="C169" s="24" t="s">
         <v>2058</v>
       </c>
-      <c r="B169" s="12" t="s">
+      <c r="D169" s="25" t="s">
         <v>2059</v>
       </c>
-      <c r="C169" s="24" t="s">
-        <v>2060</v>
-      </c>
-      <c r="D169" s="25" t="s">
-        <v>2061</v>
-      </c>
       <c r="E169" s="12" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="F169" s="12" t="s">
         <v>172</v>
@@ -21309,49 +21309,49 @@
         <v>60</v>
       </c>
       <c r="L169" s="24" t="s">
+        <v>2060</v>
+      </c>
+      <c r="M169" s="25" t="s">
+        <v>2061</v>
+      </c>
+      <c r="N169" s="12" t="s">
         <v>2062</v>
       </c>
-      <c r="M169" s="25" t="s">
+      <c r="O169" s="14" t="s">
         <v>2063</v>
       </c>
-      <c r="N169" s="12" t="s">
+      <c r="P169" s="12" t="s">
         <v>2064</v>
       </c>
-      <c r="O169" s="14" t="s">
+      <c r="Q169" s="14" t="s">
         <v>2065</v>
       </c>
-      <c r="P169" s="12" t="s">
+      <c r="R169" s="12" t="s">
+        <v>2008</v>
+      </c>
+      <c r="S169" s="14" t="s">
+        <v>2009</v>
+      </c>
+      <c r="T169" s="12" t="s">
         <v>2066</v>
       </c>
-      <c r="Q169" s="14" t="s">
+      <c r="U169" s="14" t="s">
         <v>2067</v>
       </c>
-      <c r="R169" s="12" t="s">
-        <v>2010</v>
-      </c>
-      <c r="S169" s="14" t="s">
-        <v>2011</v>
-      </c>
-      <c r="T169" s="12" t="s">
+      <c r="V169" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="W169" s="12" t="s">
+        <v>2177</v>
+      </c>
+      <c r="X169" s="14" t="s">
         <v>2068</v>
-      </c>
-      <c r="U169" s="14" t="s">
-        <v>2069</v>
-      </c>
-      <c r="V169" s="12" t="s">
-        <v>1962</v>
-      </c>
-      <c r="W169" s="12" t="s">
-        <v>2179</v>
-      </c>
-      <c r="X169" s="14" t="s">
-        <v>2070</v>
       </c>
       <c r="Y169" s="12" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="124.4">
+    <row r="170" spans="1:25">
       <c r="A170" s="12"/>
       <c r="B170" s="12"/>
       <c r="C170" s="12"/>
@@ -21378,7 +21378,7 @@
       <c r="X170" s="14"/>
       <c r="Y170" s="12"/>
     </row>
-    <row r="171" spans="1:25" ht="124.4">
+    <row r="171" spans="1:25">
       <c r="A171" s="12"/>
       <c r="B171" s="12"/>
       <c r="C171" s="12"/>
@@ -21448,27 +21448,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="15" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>2196</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="D1" s="15" t="s">
         <v>2197</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>2198</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>2199</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>62</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="D2" s="3">
         <v>29</v>
@@ -21476,13 +21476,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>271</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="D3" s="3">
         <v>16</v>
@@ -21490,13 +21490,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>838</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="D4" s="3">
         <v>11</v>
@@ -21504,13 +21504,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>172</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="D5" s="3">
         <v>52</v>
@@ -21518,13 +21518,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>350</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="D6" s="3">
         <v>8</v>
@@ -21532,13 +21532,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>113</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>2211</v>
+        <v>2209</v>
       </c>
       <c r="D7" s="3">
         <v>7</v>
@@ -21546,13 +21546,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>586</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="D8" s="3">
         <v>10</v>
@@ -21560,13 +21560,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>161</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
       <c r="D9" s="3">
         <v>9</v>
@@ -21574,13 +21574,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>837</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
       <c r="D10" s="3">
         <v>20</v>
@@ -21588,13 +21588,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>689</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
       <c r="D11" s="3">
         <v>9</v>
@@ -21602,13 +21602,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>969</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
       <c r="D12" s="3">
         <v>3</v>
@@ -21616,13 +21616,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>162</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
       <c r="D13" s="3">
         <v>12</v>
@@ -21630,13 +21630,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3" t="s">
-        <v>2224</v>
+        <v>2222</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>82</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="D14" s="3">
         <v>14</v>
@@ -21644,13 +21644,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>173</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="D15" s="3">
         <v>19</v>
@@ -21658,13 +21658,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>248</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
       <c r="D16" s="3">
         <v>13</v>
@@ -21672,13 +21672,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>445</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
       <c r="D17" s="3">
         <v>17</v>
@@ -21686,13 +21686,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>2232</v>
+        <v>2230</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>2233</v>
+        <v>2231</v>
       </c>
       <c r="D18" s="3">
         <v>13</v>
@@ -21700,13 +21700,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>883</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="D19" s="3">
         <v>3</v>
@@ -21714,13 +21714,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>2236</v>
+        <v>2234</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>151</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="D20" s="3">
         <v>8</v>
@@ -21742,12 +21742,12 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="4" t="s">
-        <v>2238</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="16" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -21755,7 +21755,7 @@
         <v>83</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2240</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -21763,7 +21763,7 @@
         <v>205</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2241</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -21779,7 +21779,7 @@
         <v>429</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2242</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -21787,7 +21787,7 @@
         <v>334</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -21795,12 +21795,12 @@
         <v>839</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>2244</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="16" t="s">
-        <v>2245</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -21808,7 +21808,7 @@
         <v>64</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>2246</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -21816,7 +21816,7 @@
         <v>99</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>2247</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -21824,15 +21824,15 @@
         <v>84</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>2248</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>2249</v>
+        <v>2247</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>2250</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -21840,12 +21840,12 @@
         <v>970</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="16" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -21853,7 +21853,7 @@
         <v>75</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
     </row>
   </sheetData>
@@ -21872,10 +21872,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="15" t="s">
-        <v>2254</v>
+        <v>2252</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -21888,7 +21888,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="B3" s="3">
         <v>28</v>
@@ -21912,7 +21912,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="B6" s="3">
         <v>8</v>
@@ -21952,7 +21952,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -21960,7 +21960,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Yoshlik Yu Distribution\Web-service-catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EE3662-35CD-4173-BDD3-67343EF96A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953B486E-992B-4078-826A-EFEAB4B18A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13667" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13495,12 +13495,6 @@
       <c r="Y66" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="Z66" s="19" t="s">
-        <v>2263</v>
-      </c>
-      <c r="AA66">
-        <v>120</v>
-      </c>
     </row>
     <row r="67" spans="1:27" ht="78.05" customHeight="1">
       <c r="A67" s="12" t="s">
@@ -13729,6 +13723,12 @@
       </c>
       <c r="Y69" s="12" t="s">
         <v>77</v>
+      </c>
+      <c r="Z69" s="19" t="s">
+        <v>2263</v>
+      </c>
+      <c r="AA69">
+        <v>120</v>
       </c>
     </row>
     <row r="70" spans="1:27" ht="78.05" customHeight="1">
@@ -14026,12 +14026,6 @@
       <c r="Y73" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="Z73" t="s">
-        <v>2353</v>
-      </c>
-      <c r="AA73">
-        <v>100</v>
-      </c>
     </row>
     <row r="74" spans="1:27" ht="78.05" customHeight="1">
       <c r="A74" s="12" t="s">
@@ -14257,6 +14251,12 @@
       <c r="Y76" s="12" t="s">
         <v>77</v>
       </c>
+      <c r="Z76" t="s">
+        <v>2353</v>
+      </c>
+      <c r="AA76">
+        <v>100</v>
+      </c>
     </row>
     <row r="77" spans="1:27" ht="78.05" customHeight="1">
       <c r="A77" s="12" t="s">
@@ -16663,12 +16663,6 @@
       <c r="Y108" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="Z108" t="s">
-        <v>2335</v>
-      </c>
-      <c r="AA108">
-        <v>60</v>
-      </c>
     </row>
     <row r="109" spans="1:27" ht="78.05" customHeight="1">
       <c r="A109" s="12" t="s">
@@ -16745,7 +16739,7 @@
         <v>77</v>
       </c>
       <c r="Z109" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="AA109">
         <v>60</v>
@@ -16825,6 +16819,12 @@
       <c r="Y110" s="12" t="s">
         <v>77</v>
       </c>
+      <c r="Z110" t="s">
+        <v>2336</v>
+      </c>
+      <c r="AA110">
+        <v>60</v>
+      </c>
     </row>
     <row r="111" spans="1:27" ht="78.05" customHeight="1">
       <c r="A111" s="12" t="s">
@@ -17054,24 +17054,6 @@
       <c r="Y113" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="Z113" t="s">
-        <v>2297</v>
-      </c>
-      <c r="AA113">
-        <v>200</v>
-      </c>
-      <c r="AB113" t="s">
-        <v>2298</v>
-      </c>
-      <c r="AC113">
-        <v>100</v>
-      </c>
-      <c r="AD113" t="s">
-        <v>2299</v>
-      </c>
-      <c r="AE113">
-        <v>500</v>
-      </c>
     </row>
     <row r="114" spans="1:31" ht="78.05" customHeight="1">
       <c r="A114" s="12" t="s">
@@ -17147,6 +17129,24 @@
       <c r="Y114" s="12" t="s">
         <v>77</v>
       </c>
+      <c r="Z114" t="s">
+        <v>2297</v>
+      </c>
+      <c r="AA114">
+        <v>200</v>
+      </c>
+      <c r="AB114" t="s">
+        <v>2298</v>
+      </c>
+      <c r="AC114">
+        <v>100</v>
+      </c>
+      <c r="AD114" t="s">
+        <v>2299</v>
+      </c>
+      <c r="AE114">
+        <v>500</v>
+      </c>
     </row>
     <row r="115" spans="1:31" ht="78.05" customHeight="1">
       <c r="A115" s="20" t="s">
@@ -17448,12 +17448,6 @@
       </c>
       <c r="Y118" s="12" t="s">
         <v>77</v>
-      </c>
-      <c r="Z118" t="s">
-        <v>2324</v>
-      </c>
-      <c r="AA118">
-        <v>180</v>
       </c>
     </row>
     <row r="119" spans="1:31" ht="78.05" customHeight="1">
@@ -17674,6 +17668,12 @@
       <c r="Y121" s="12" t="s">
         <v>77</v>
       </c>
+      <c r="Z121" t="s">
+        <v>2324</v>
+      </c>
+      <c r="AA121">
+        <v>180</v>
+      </c>
     </row>
     <row r="122" spans="1:31" ht="78.05" customHeight="1">
       <c r="A122" s="12" t="s">
@@ -17899,12 +17899,6 @@
       <c r="Y124" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="Z124" t="s">
-        <v>2354</v>
-      </c>
-      <c r="AA124">
-        <v>120</v>
-      </c>
     </row>
     <row r="125" spans="1:31" ht="78.05" customHeight="1">
       <c r="A125" s="12" t="s">
@@ -18057,6 +18051,12 @@
       <c r="Y126" s="12" t="s">
         <v>77</v>
       </c>
+      <c r="Z126" t="s">
+        <v>2354</v>
+      </c>
+      <c r="AA126">
+        <v>120</v>
+      </c>
     </row>
     <row r="127" spans="1:31" ht="78.05" customHeight="1">
       <c r="A127" s="12" t="s">
@@ -18207,12 +18207,6 @@
       <c r="Y128" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="Z128" t="s">
-        <v>2321</v>
-      </c>
-      <c r="AA128">
-        <v>30</v>
-      </c>
     </row>
     <row r="129" spans="1:29" ht="78.05" customHeight="1">
       <c r="A129" s="12" t="s">
@@ -18288,18 +18282,6 @@
       <c r="Y129" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="Z129" t="s">
-        <v>2316</v>
-      </c>
-      <c r="AA129">
-        <v>120</v>
-      </c>
-      <c r="AB129" t="s">
-        <v>2317</v>
-      </c>
-      <c r="AC129">
-        <v>240</v>
-      </c>
     </row>
     <row r="130" spans="1:29" ht="78.05" customHeight="1">
       <c r="A130" s="12" t="s">
@@ -18376,16 +18358,10 @@
         <v>77</v>
       </c>
       <c r="Z130" t="s">
-        <v>2318</v>
+        <v>2321</v>
       </c>
       <c r="AA130">
         <v>30</v>
-      </c>
-      <c r="AB130" t="s">
-        <v>2319</v>
-      </c>
-      <c r="AC130">
-        <v>240</v>
       </c>
     </row>
     <row r="131" spans="1:29" ht="78.05" customHeight="1">
@@ -18462,6 +18438,18 @@
       <c r="Y131" s="12" t="s">
         <v>77</v>
       </c>
+      <c r="Z131" t="s">
+        <v>2316</v>
+      </c>
+      <c r="AA131">
+        <v>120</v>
+      </c>
+      <c r="AB131" t="s">
+        <v>2317</v>
+      </c>
+      <c r="AC131">
+        <v>240</v>
+      </c>
     </row>
     <row r="132" spans="1:29" ht="78.05" customHeight="1">
       <c r="A132" s="12" t="s">
@@ -18538,10 +18526,16 @@
         <v>77</v>
       </c>
       <c r="Z132" t="s">
-        <v>2329</v>
+        <v>2318</v>
       </c>
       <c r="AA132">
-        <v>250</v>
+        <v>30</v>
+      </c>
+      <c r="AB132" t="s">
+        <v>2319</v>
+      </c>
+      <c r="AC132">
+        <v>240</v>
       </c>
     </row>
     <row r="133" spans="1:29" ht="78.05" customHeight="1">
@@ -18620,12 +18614,6 @@
       <c r="Y133" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="Z133" t="s">
-        <v>2330</v>
-      </c>
-      <c r="AA133">
-        <v>60</v>
-      </c>
     </row>
     <row r="134" spans="1:29" ht="78.05" customHeight="1">
       <c r="A134" s="12" t="s">
@@ -18703,6 +18691,12 @@
       <c r="Y134" s="12" t="s">
         <v>77</v>
       </c>
+      <c r="Z134" t="s">
+        <v>2329</v>
+      </c>
+      <c r="AA134">
+        <v>250</v>
+      </c>
     </row>
     <row r="135" spans="1:29" ht="78.05" customHeight="1">
       <c r="A135" s="12" t="s">
@@ -18779,6 +18773,12 @@
       </c>
       <c r="Y135" s="12" t="s">
         <v>77</v>
+      </c>
+      <c r="Z135" t="s">
+        <v>2330</v>
+      </c>
+      <c r="AA135">
+        <v>60</v>
       </c>
     </row>
     <row r="136" spans="1:29" ht="78.05" customHeight="1">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Yoshlik Yu Distribution\Web-service-catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953B486E-992B-4078-826A-EFEAB4B18A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9971E420-3EF8-4B6F-B593-172170797F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13667" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17130,16 +17130,16 @@
         <v>77</v>
       </c>
       <c r="Z114" t="s">
+        <v>2298</v>
+      </c>
+      <c r="AA114">
+        <v>100</v>
+      </c>
+      <c r="AB114" t="s">
         <v>2297</v>
       </c>
-      <c r="AA114">
+      <c r="AC114">
         <v>200</v>
-      </c>
-      <c r="AB114" t="s">
-        <v>2298</v>
-      </c>
-      <c r="AC114">
-        <v>100</v>
       </c>
       <c r="AD114" t="s">
         <v>2299</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -21631,17 +21631,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>carlson-kids-chewable-dha-120sg</t>
+          <t>carlson-kids-chewable-dha-60sg</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Carlson Kid's Chewable DHA, апельсин, 100 мг, 120 капсул</t>
+          <t>Carlson Kid's Chewable DHA, апельсин, 100 мг, 60 капсул</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Carlson Kid's Chewable DHA, apelsin, 100 mg, 120 kapsula</t>
+          <t>Carlson Kid's Chewable DHA, apelsin, 100 mg, 60 kapsula</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -21673,7 +21673,7 @@
         </is>
       </c>
       <c r="K172" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -22610,17 +22610,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>carlson-cod-liver-oil-gems-1000-250sg</t>
+          <t>carlson-cod-liver-oil-gems-1000-100sg</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Carlson Wild Norwegian Cod Liver Oil Gems Super, 1000 мг, 250 капсул</t>
+          <t>Carlson Wild Norwegian Cod Liver Oil Gems Super, 1000 мг, 100 капсул</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Carlson Wild Norwegian Cod Liver Oil Gems Super, 1000 mg, 250 kapsula</t>
+          <t>Carlson Wild Norwegian Cod Liver Oil Gems Super, 1000 mg, 100 kapsula</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -22652,7 +22652,7 @@
         </is>
       </c>
       <c r="K180" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -22733,17 +22733,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>carlson-baby-super-daily-d3-90drops</t>
+          <t>carlson-baby-super-daily-d3-365drops</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Carlson Baby's Super Daily D3, 400 МЕ, 90 капель (2,54 мл)</t>
+          <t>Carlson Baby's Super Daily D3, 400 МЕ, 10,3 мл</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Carlson Baby's Super Daily D3, 400 XB, 90 tomchi (2,54 ml)</t>
+          <t>Carlson Baby's Super Daily D3, 400 XB, 10,3 ml</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
